--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,30 +477,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>DOMRF EY%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>OZON EY%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROSN EY%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>VTBR EY%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Portfolio EY%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OFZ 10Y%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ERP Proxy%</t>
         </is>
@@ -517,20 +523,20 @@
       <c r="C2" s="2" t="n">
         <v>3.066760990596794</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>19.08913342354207</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>7.851244304880336</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>11.45849213585805</v>
-      </c>
       <c r="I2" s="2" t="n">
+        <v>12.23925949930118</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>8.77</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>2.688492135858052</v>
+      <c r="K2" s="3" t="n">
+        <v>3.469259499301183</v>
       </c>
     </row>
     <row r="3">
@@ -545,20 +551,20 @@
       <c r="C3" s="2" t="n">
         <v>3.072316717029035</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>19.68507051261704</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>8.260208841095547</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>11.95097965396368</v>
-      </c>
       <c r="I3" s="2" t="n">
+        <v>12.77733465514106</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>8.23</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>3.720979653963679</v>
+      <c r="K3" s="3" t="n">
+        <v>4.547334655141062</v>
       </c>
     </row>
     <row r="4">
@@ -573,20 +579,20 @@
       <c r="C4" s="2" t="n">
         <v>2.957654042204442</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>19.05438378745552</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>8.319301371730404</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>11.5764750409802</v>
-      </c>
       <c r="I4" s="2" t="n">
+        <v>12.3800683677762</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>8.43</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>3.146475040980198</v>
+      <c r="K4" s="3" t="n">
+        <v>3.950068367776199</v>
       </c>
     </row>
     <row r="5">
@@ -601,20 +607,20 @@
       <c r="C5" s="2" t="n">
         <v>2.837170770054416</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>18.30785009429028</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>8.353281616769864</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>11.03891615747081</v>
-      </c>
       <c r="I5" s="2" t="n">
+        <v>11.80558571554623</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>2.648916157470813</v>
+      <c r="K5" s="3" t="n">
+        <v>3.415585715546234</v>
       </c>
     </row>
     <row r="6">
@@ -629,20 +635,20 @@
       <c r="C6" s="2" t="n">
         <v>3.085643634085686</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>20.72341951426353</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>7.672385559350714</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>10.99937014892159</v>
-      </c>
       <c r="I6" s="2" t="n">
+        <v>11.73804810697836</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>8.25</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>2.749370148921589</v>
+      <c r="K6" s="3" t="n">
+        <v>3.488048106978356</v>
       </c>
     </row>
     <row r="7">
@@ -657,20 +663,20 @@
       <c r="C7" s="2" t="n">
         <v>2.997387093790893</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>21.64834897388687</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>7.06155747131314</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>10.76026315621285</v>
-      </c>
       <c r="I7" s="2" t="n">
+        <v>11.48402245659083</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>8.01</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>2.750263156212855</v>
+      <c r="K7" s="3" t="n">
+        <v>3.474022456590832</v>
       </c>
     </row>
     <row r="8">
@@ -685,20 +691,20 @@
       <c r="C8" s="2" t="n">
         <v>2.895548158797034</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>21.26612311808534</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>6.626233222493365</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>10.90627378305441</v>
-      </c>
       <c r="I8" s="2" t="n">
+        <v>11.65037186760847</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>7.45</v>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>3.456273783054413</v>
+      <c r="K8" s="3" t="n">
+        <v>4.200371867608472</v>
       </c>
     </row>
     <row r="9">
@@ -713,20 +719,20 @@
       <c r="C9" s="2" t="n">
         <v>3.020222040544225</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>21.42395840799424</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>6.736086902573284</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>11.75142093793744</v>
-      </c>
       <c r="I9" s="2" t="n">
+        <v>12.55957143229307</v>
+      </c>
+      <c r="J9" s="2" t="n">
         <v>7.43</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>4.321420937937441</v>
+      <c r="K9" s="3" t="n">
+        <v>5.129571432293069</v>
       </c>
     </row>
     <row r="10">
@@ -741,20 +747,20 @@
       <c r="C10" s="2" t="n">
         <v>3.286296209884386</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>20.7929403151282</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>6.116958361111272</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>11.69266239245662</v>
-      </c>
       <c r="I10" s="2" t="n">
+        <v>12.46725560875859</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>7.21</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>4.482662392456615</v>
+      <c r="K10" s="3" t="n">
+        <v>5.257255608758594</v>
       </c>
     </row>
     <row r="11">
@@ -772,20 +778,20 @@
       <c r="D11" s="2" t="n">
         <v>12.71603192951652</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>20.4659151974959</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>6.046689287341252</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>11.70689381248403</v>
-      </c>
       <c r="I11" s="2" t="n">
+        <v>12.29566940986691</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>7.16</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>4.546893812484033</v>
+      <c r="K11" s="3" t="n">
+        <v>5.135669409866914</v>
       </c>
     </row>
     <row r="12">
@@ -803,20 +809,20 @@
       <c r="D12" s="2" t="n">
         <v>14.05538572689876</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>19.66281621935698</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>6.113764313350083</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>11.11729991149756</v>
-      </c>
       <c r="I12" s="2" t="n">
+        <v>11.64737438454345</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>6.51</v>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>4.607299911497561</v>
+      <c r="K12" s="3" t="n">
+        <v>5.137374384543445</v>
       </c>
     </row>
     <row r="13">
@@ -834,20 +840,20 @@
       <c r="D13" s="2" t="n">
         <v>12.71116259529938</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>19.2824148381953</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>6.037841749981683</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>10.26778407843677</v>
-      </c>
       <c r="I13" s="2" t="n">
+        <v>10.75212148143339</v>
+      </c>
+      <c r="J13" s="2" t="n">
         <v>6.6</v>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>3.667784078436767</v>
+      <c r="K13" s="3" t="n">
+        <v>4.152121481433392</v>
       </c>
     </row>
     <row r="14">
@@ -865,20 +871,20 @@
       <c r="D14" s="2" t="n">
         <v>11.9557080937257</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>18.02677704153395</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>7.220235293944389</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>10.37074889915268</v>
-      </c>
       <c r="I14" s="2" t="n">
+        <v>10.92140634135686</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>6.42</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>3.950748899152682</v>
+      <c r="K14" s="3" t="n">
+        <v>4.50140634135686</v>
       </c>
     </row>
     <row r="15">
@@ -896,20 +902,20 @@
       <c r="D15" s="2" t="n">
         <v>12.28659460181416</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>21.47215262384002</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>7.731800545557801</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>11.10868395941125</v>
-      </c>
       <c r="I15" s="2" t="n">
+        <v>11.71584479325076</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>4.738683959411252</v>
+      <c r="K15" s="3" t="n">
+        <v>5.34584479325076</v>
       </c>
     </row>
     <row r="16">
@@ -927,20 +933,20 @@
       <c r="D16" s="2" t="n">
         <v>20.12544195777159</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>27.55484768079231</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>10.27665391530735</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>14.52184022124011</v>
-      </c>
       <c r="I16" s="2" t="n">
+        <v>15.24672225810425</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>6.55</v>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>7.971840221240106</v>
+      <c r="K16" s="3" t="n">
+        <v>8.696722258104248</v>
       </c>
     </row>
     <row r="17">
@@ -958,20 +964,20 @@
       <c r="D17" s="2" t="n">
         <v>17.67111976779945</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>25.80624569777168</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>9.599395920888814</v>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>13.51064203969213</v>
-      </c>
       <c r="I17" s="2" t="n">
+        <v>14.21658726275516</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>6.89</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>6.620642039692126</v>
+      <c r="K17" s="3" t="n">
+        <v>7.326587262755161</v>
       </c>
     </row>
     <row r="18">
@@ -989,20 +995,20 @@
       <c r="D18" s="2" t="n">
         <v>15.18441243806729</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>17.80772152671224</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>8.920597742609777</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>11.69434157466767</v>
-      </c>
       <c r="I18" s="2" t="n">
+        <v>12.28282631735969</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>6.18</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>5.514341574667673</v>
+      <c r="K18" s="3" t="n">
+        <v>6.102826317359694</v>
       </c>
     </row>
     <row r="19">
@@ -1020,20 +1026,20 @@
       <c r="D19" s="2" t="n">
         <v>13.23460544302887</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>18.51648656260129</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>9.241281142201457</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>11.06075097511171</v>
-      </c>
       <c r="I19" s="2" t="n">
+        <v>11.68845373373323</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>5.67</v>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>5.390750975111706</v>
+      <c r="K19" s="3" t="n">
+        <v>6.018453733733232</v>
       </c>
     </row>
     <row r="20">
@@ -1051,20 +1057,20 @@
       <c r="D20" s="2" t="n">
         <v>10.17436833417022</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>18.77070562720411</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>8.357809419021057</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>9.734372298398988</v>
-      </c>
       <c r="I20" s="2" t="n">
+        <v>10.34673278058047</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <v>6.01</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>3.724372298398988</v>
+      <c r="K20" s="3" t="n">
+        <v>4.336732780580475</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1088,20 @@
       <c r="D21" s="2" t="n">
         <v>10.57861699875991</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>10.71995641599881</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>7.834259684075175</v>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>8.633100017417984</v>
-      </c>
       <c r="I21" s="2" t="n">
+        <v>9.145835752639334</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>6.01</v>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>2.623100017417984</v>
+      <c r="K21" s="3" t="n">
+        <v>3.135835752639334</v>
       </c>
     </row>
     <row r="22">
@@ -1113,20 +1119,20 @@
       <c r="D22" s="2" t="n">
         <v>9.79344485891454</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>10.44565988107247</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>8.038779878873365</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>8.40535405956282</v>
-      </c>
       <c r="I22" s="2" t="n">
+        <v>8.920395552516448</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>6.22</v>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>2.18535405956282</v>
+      <c r="K22" s="3" t="n">
+        <v>2.700395552516448</v>
       </c>
     </row>
     <row r="23">
@@ -1144,20 +1150,20 @@
       <c r="D23" s="2" t="n">
         <v>10.69840477804295</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>11.43707185377575</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>8.484216633220857</v>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>9.471926498629941</v>
-      </c>
       <c r="I23" s="2" t="n">
+        <v>10.06302454718287</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>6.39</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>3.081926498629941</v>
+      <c r="K23" s="3" t="n">
+        <v>3.673024547182872</v>
       </c>
     </row>
     <row r="24">
@@ -1175,23 +1181,23 @@
       <c r="D24" s="2" t="n">
         <v>9.103646675531737</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>-2.98949185620984</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>5.667647954234813</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>5.932480880226692</v>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>7.792969848531673</v>
-      </c>
       <c r="I24" s="2" t="n">
+        <v>8.517832735490186</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>6.52</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.272969848531673</v>
+      <c r="K24" s="3" t="n">
+        <v>1.997832735490187</v>
       </c>
     </row>
     <row r="25">
@@ -1209,23 +1215,23 @@
       <c r="D25" s="2" t="n">
         <v>9.102103946049354</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>-2.790919437732307</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>5.855223524312912</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>5.825243793461807</v>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>7.333094532610114</v>
-      </c>
       <c r="I25" s="2" t="n">
+        <v>7.991778046485789</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>6.16</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.173094532610114</v>
+      <c r="K25" s="3" t="n">
+        <v>1.831778046485788</v>
       </c>
     </row>
     <row r="26">
@@ -1243,23 +1249,23 @@
       <c r="D26" s="2" t="n">
         <v>7.17516842119741</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>-2.908552689446972</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>3.411173174992418</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>3.395338119139771</v>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>7.211491815147722</v>
-      </c>
       <c r="I26" s="2" t="n">
+        <v>7.897926171050143</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>6.25</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>0.9614918151477223</v>
+      <c r="K26" s="3" t="n">
+        <v>1.647926171050143</v>
       </c>
     </row>
     <row r="27">
@@ -1277,23 +1283,23 @@
       <c r="D27" s="2" t="n">
         <v>5.749808285257184</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>-2.377482131418484</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3.082994003575836</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>3.355042804981403</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>6.740681317363648</v>
-      </c>
       <c r="I27" s="2" t="n">
+        <v>7.398964980146275</v>
+      </c>
+      <c r="J27" s="2" t="n">
         <v>6.58</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>0.1606813173636477</v>
+      <c r="K27" s="3" t="n">
+        <v>0.8189649801462746</v>
       </c>
     </row>
     <row r="28">
@@ -1311,23 +1317,23 @@
       <c r="D28" s="2" t="n">
         <v>4.999326094733308</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>-2.515022420012942</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>2.817822060376203</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>2.912049912084408</v>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>6.199485678044664</v>
-      </c>
       <c r="I28" s="2" t="n">
+        <v>6.815466901936662</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>7.02</v>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>-0.8205143219553355</v>
+      <c r="K28" s="4" t="n">
+        <v>-0.2045330980633375</v>
       </c>
     </row>
     <row r="29">
@@ -1345,23 +1351,23 @@
       <c r="D29" s="2" t="n">
         <v>5.084837565056395</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>-2.280997954546485</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3.072134256990506</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>2.410624263462897</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>6.110691919605395</v>
-      </c>
       <c r="I29" s="2" t="n">
+        <v>6.706209647393882</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>7.27</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>-1.159308080394604</v>
+      <c r="K29" s="4" t="n">
+        <v>-0.5637903526061177</v>
       </c>
     </row>
     <row r="30">
@@ -1379,23 +1385,23 @@
       <c r="D30" s="2" t="n">
         <v>4.494437429755661</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>-2.828859702311609</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>5.61092328242254</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>4.092691118758473</v>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>6.899792963941055</v>
-      </c>
       <c r="I30" s="2" t="n">
+        <v>7.647082482300239</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>7.17</v>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>-0.2702070360589452</v>
+      <c r="K30" s="3" t="n">
+        <v>0.4770824823002391</v>
       </c>
     </row>
     <row r="31">
@@ -1413,23 +1419,23 @@
       <c r="D31" s="2" t="n">
         <v>3.858594576432185</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>-2.584584909075788</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5.219966092926011</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>4.115909067343487</v>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>6.87038514848787</v>
-      </c>
       <c r="I31" s="2" t="n">
+        <v>7.631384545223767</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>7.26</v>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>-0.38961485151213</v>
+      <c r="K31" s="3" t="n">
+        <v>0.3713845452237674</v>
       </c>
     </row>
     <row r="32">
@@ -1447,23 +1453,23 @@
       <c r="D32" s="2" t="n">
         <v>4.052477309573597</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>-2.916289101178233</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5.475931372413843</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>4.117183079642499</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>6.912857616801444</v>
-      </c>
       <c r="I32" s="2" t="n">
+        <v>7.678787980894248</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>7.21</v>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>-0.2971423831985556</v>
+      <c r="K32" s="3" t="n">
+        <v>0.4687879808942483</v>
       </c>
     </row>
     <row r="33">
@@ -1481,23 +1487,23 @@
       <c r="D33" s="2" t="n">
         <v>4.298737711928412</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>-4.372500928076589</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>11.26399397667822</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>6.411812180253669</v>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>7.387903681338463</v>
-      </c>
       <c r="I33" s="2" t="n">
+        <v>8.270628595767322</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>6.97</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>0.4179036813384629</v>
+      <c r="K33" s="3" t="n">
+        <v>1.300628595767322</v>
       </c>
     </row>
     <row r="34">
@@ -1515,23 +1521,23 @@
       <c r="D34" s="2" t="n">
         <v>4.184466155468061</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>-4.580715257984998</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>9.783457615293401</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>6.538385596624072</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>7.079505847795136</v>
-      </c>
       <c r="I34" s="2" t="n">
+        <v>7.93386177927357</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>7.09</v>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>-0.01049415220486427</v>
+      <c r="K34" s="3" t="n">
+        <v>0.8438617792735696</v>
       </c>
     </row>
     <row r="35">
@@ -1549,23 +1555,23 @@
       <c r="D35" s="2" t="n">
         <v>3.794297601218126</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>-5.277156292506229</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>9.448934422190694</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>6.406948298455638</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>6.684462964325174</v>
-      </c>
       <c r="I35" s="2" t="n">
+        <v>7.519675884255697</v>
+      </c>
+      <c r="J35" s="2" t="n">
         <v>7.45</v>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>-0.7655370356748259</v>
+      <c r="K35" s="3" t="n">
+        <v>0.06967588425569726</v>
       </c>
     </row>
     <row r="36">
@@ -1583,23 +1589,23 @@
       <c r="D36" s="2" t="n">
         <v>4.173898019958425</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>-7.241321261031714</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>14.38422404715066</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>9.61123734309326</v>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>7.845201804966403</v>
-      </c>
       <c r="I36" s="2" t="n">
+        <v>8.902873610914304</v>
+      </c>
+      <c r="J36" s="2" t="n">
         <v>8.32</v>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>-0.4747981950335971</v>
+      <c r="K36" s="3" t="n">
+        <v>0.5828736109143033</v>
       </c>
     </row>
     <row r="37">
@@ -1617,23 +1623,23 @@
       <c r="D37" s="2" t="n">
         <v>4.853401522390362</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>-9.357606386746573</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>13.59417234239063</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>9.411813391581832</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>8.361012451181235</v>
-      </c>
       <c r="I37" s="2" t="n">
+        <v>9.510095029909841</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>8.35</v>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>0.01101245118123551</v>
+      <c r="K37" s="3" t="n">
+        <v>1.160095029909842</v>
       </c>
     </row>
     <row r="38">
@@ -1651,23 +1657,23 @@
       <c r="D38" s="2" t="n">
         <v>5.693657258914006</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="F38" s="2" t="n">
         <v>-16.91755984264491</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>17.28644177708432</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>12.32327862399001</v>
       </c>
-      <c r="H38" s="2" t="n">
-        <v>9.172272075654703</v>
-      </c>
       <c r="I38" s="2" t="n">
+        <v>10.61763349983536</v>
+      </c>
+      <c r="J38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>0.8022720756547042</v>
+      <c r="K38" s="3" t="n">
+        <v>2.247633499835365</v>
       </c>
     </row>
     <row r="39">
@@ -1685,23 +1691,23 @@
       <c r="D39" s="2" t="n">
         <v>10.41429468179818</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="F39" s="2" t="n">
         <v>-27.02939819712486</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>32.38646722938399</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>26.82810234501654</v>
       </c>
-      <c r="H39" s="2" t="n">
-        <v>19.15999362106068</v>
-      </c>
       <c r="I39" s="2" t="n">
+        <v>22.01360330393863</v>
+      </c>
+      <c r="J39" s="2" t="n">
         <v>9.42</v>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>9.739993621060682</v>
+      <c r="K39" s="3" t="n">
+        <v>12.59360330393863</v>
       </c>
     </row>
     <row r="40">
@@ -1719,17 +1725,17 @@
       <c r="D40" s="2" t="n">
         <v>9.585795722631477</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="F40" s="2" t="n">
         <v>-19.07232272786599</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>22.79637161894582</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>27.24813829082235</v>
       </c>
-      <c r="H40" s="2" t="n">
-        <v>17.85089377768945</v>
+      <c r="I40" s="2" t="n">
+        <v>20.36024961236827</v>
       </c>
     </row>
     <row r="41">
@@ -1747,23 +1753,23 @@
       <c r="D41" s="2" t="n">
         <v>12.197263460718</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="F41" s="2" t="n">
         <v>-26.59301358826716</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>24.3848718417819</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>26.84812829849628</v>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>19.79817555489395</v>
-      </c>
       <c r="I41" s="2" t="n">
+        <v>22.65014683908102</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>11.36</v>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>8.438175554893949</v>
+      <c r="K41" s="3" t="n">
+        <v>11.29014683908102</v>
       </c>
     </row>
     <row r="42">
@@ -1781,23 +1787,23 @@
       <c r="D42" s="2" t="n">
         <v>12.02375628984552</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="F42" s="2" t="n">
         <v>-36.44510884856396</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>27.38071406266658</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>29.46549088794553</v>
       </c>
-      <c r="H42" s="2" t="n">
-        <v>20.11024599687705</v>
-      </c>
       <c r="I42" s="2" t="n">
+        <v>23.42802201234696</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>10.32</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>9.790245996877051</v>
+      <c r="K42" s="3" t="n">
+        <v>13.10802201234696</v>
       </c>
     </row>
     <row r="43">
@@ -1815,23 +1821,23 @@
       <c r="D43" s="2" t="n">
         <v>14.07326020288738</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="F43" s="2" t="n">
         <v>-39.18550483658505</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>28.49559475949014</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>30.34382104377292</v>
       </c>
-      <c r="H43" s="2" t="n">
-        <v>19.15433845676414</v>
-      </c>
       <c r="I43" s="2" t="n">
+        <v>22.36083694115864</v>
+      </c>
+      <c r="J43" s="2" t="n">
         <v>9.23</v>
       </c>
-      <c r="J43" s="3" t="n">
-        <v>9.924338456764144</v>
+      <c r="K43" s="3" t="n">
+        <v>13.13083694115864</v>
       </c>
     </row>
     <row r="44">
@@ -1849,23 +1855,23 @@
       <c r="D44" s="2" t="n">
         <v>13.0195699517994</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="F44" s="2" t="n">
         <v>-23.91916070437014</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>29.24229235587904</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>29.02949357860009</v>
       </c>
-      <c r="H44" s="2" t="n">
-        <v>19.1710496780323</v>
-      </c>
       <c r="I44" s="2" t="n">
+        <v>21.99379776475309</v>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>8.84</v>
       </c>
-      <c r="J44" s="3" t="n">
-        <v>10.3310496780323</v>
+      <c r="K44" s="3" t="n">
+        <v>13.15379776475309</v>
       </c>
     </row>
     <row r="45">
@@ -1883,23 +1889,23 @@
       <c r="D45" s="2" t="n">
         <v>6.93652977341273</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>-19.77983310289574</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>26.79398253243592</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>27.88902239122681</v>
       </c>
-      <c r="H45" s="2" t="n">
-        <v>18.62159267367483</v>
-      </c>
       <c r="I45" s="2" t="n">
+        <v>21.32424373411878</v>
+      </c>
+      <c r="J45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>9.75159267367483</v>
+      <c r="K45" s="3" t="n">
+        <v>12.45424373411878</v>
       </c>
     </row>
     <row r="46">
@@ -1917,23 +1923,23 @@
       <c r="D46" s="2" t="n">
         <v>7.925584250371538</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="F46" s="2" t="n">
         <v>-27.84420844503734</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>37.34211540214511</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>36.13617804141209</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>22.34298096619347</v>
-      </c>
       <c r="I46" s="2" t="n">
+        <v>25.72573750286871</v>
+      </c>
+      <c r="J46" s="2" t="n">
         <v>9.08</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>13.26298096619347</v>
+      <c r="K46" s="3" t="n">
+        <v>16.64573750286871</v>
       </c>
     </row>
     <row r="47">
@@ -1951,23 +1957,23 @@
       <c r="D47" s="2" t="n">
         <v>7.181426339840471</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="F47" s="2" t="n">
         <v>-21.87164654389704</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>29.53035511211866</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>32.03759727780775</v>
       </c>
-      <c r="H47" s="2" t="n">
-        <v>19.64597110985674</v>
-      </c>
       <c r="I47" s="2" t="n">
+        <v>22.54103948317983</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="J47" s="3" t="n">
-        <v>9.145971109856738</v>
+      <c r="K47" s="3" t="n">
+        <v>12.04103948317983</v>
       </c>
     </row>
     <row r="48">
@@ -1985,23 +1991,23 @@
       <c r="D48" s="2" t="n">
         <v>4.975043205095505</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="F48" s="2" t="n">
         <v>-22.8891441248021</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>24.41325895330124</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>31.84847332693522</v>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>17.93179071801805</v>
-      </c>
       <c r="I48" s="2" t="n">
+        <v>20.65453964374968</v>
+      </c>
+      <c r="J48" s="2" t="n">
         <v>10.23</v>
       </c>
-      <c r="J48" s="3" t="n">
-        <v>7.701790718018053</v>
+      <c r="K48" s="3" t="n">
+        <v>10.42453964374968</v>
       </c>
     </row>
     <row r="49">
@@ -2019,23 +2025,23 @@
       <c r="D49" s="2" t="n">
         <v>5.333481357273647</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="F49" s="2" t="n">
         <v>-23.16668724186461</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>22.46567685563094</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>32.91721404260419</v>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>17.47888782476374</v>
-      </c>
       <c r="I49" s="2" t="n">
+        <v>20.12726302945856</v>
+      </c>
+      <c r="J49" s="2" t="n">
         <v>10.24</v>
       </c>
-      <c r="J49" s="3" t="n">
-        <v>7.238887824763738</v>
+      <c r="K49" s="3" t="n">
+        <v>9.887263029458561</v>
       </c>
     </row>
     <row r="50">
@@ -2053,23 +2059,23 @@
       <c r="D50" s="2" t="n">
         <v>3.746777067002482</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="F50" s="2" t="n">
         <v>-16.2825478218093</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>22.51248721679747</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>31.82968366715531</v>
       </c>
-      <c r="H50" s="2" t="n">
-        <v>15.67562685571748</v>
-      </c>
       <c r="I50" s="2" t="n">
+        <v>18.00397246847833</v>
+      </c>
+      <c r="J50" s="2" t="n">
         <v>10.27</v>
       </c>
-      <c r="J50" s="3" t="n">
-        <v>5.405626855717479</v>
+      <c r="K50" s="3" t="n">
+        <v>7.733972468478335</v>
       </c>
     </row>
     <row r="51">
@@ -2087,23 +2093,23 @@
       <c r="D51" s="2" t="n">
         <v>4.045205853838707</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="F51" s="2" t="n">
         <v>-16.61286203776486</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>21.4038225980015</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>32.77722589053965</v>
       </c>
-      <c r="H51" s="2" t="n">
-        <v>14.6487051213661</v>
-      </c>
       <c r="I51" s="2" t="n">
+        <v>16.84570692315609</v>
+      </c>
+      <c r="J51" s="2" t="n">
         <v>10.65</v>
       </c>
-      <c r="J51" s="3" t="n">
-        <v>3.998705121366095</v>
+      <c r="K51" s="3" t="n">
+        <v>6.195706923156086</v>
       </c>
     </row>
     <row r="52">
@@ -2121,23 +2127,23 @@
       <c r="D52" s="2" t="n">
         <v>4.176982115315055</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="F52" s="2" t="n">
         <v>-15.63344007596514</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>20.13948547945324</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>29.7416283438965</v>
       </c>
-      <c r="H52" s="2" t="n">
-        <v>11.66770787902511</v>
-      </c>
       <c r="I52" s="2" t="n">
+        <v>13.43450295471342</v>
+      </c>
+      <c r="J52" s="2" t="n">
         <v>10.82</v>
       </c>
-      <c r="J52" s="3" t="n">
-        <v>0.8477078790251085</v>
+      <c r="K52" s="3" t="n">
+        <v>2.614502954713416</v>
       </c>
     </row>
     <row r="53">
@@ -2155,23 +2161,23 @@
       <c r="D53" s="2" t="n">
         <v>3.771265806002499</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="F53" s="2" t="n">
         <v>-16.33988073667483</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>19.47976134871442</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>24.28051926904962</v>
       </c>
-      <c r="H53" s="2" t="n">
-        <v>10.34778140930565</v>
-      </c>
       <c r="I53" s="2" t="n">
+        <v>11.96879019331329</v>
+      </c>
+      <c r="J53" s="2" t="n">
         <v>10.82</v>
       </c>
-      <c r="J53" s="4" t="n">
-        <v>-0.4722185906943484</v>
+      <c r="K53" s="3" t="n">
+        <v>1.148790193313294</v>
       </c>
     </row>
     <row r="54">
@@ -2189,23 +2195,23 @@
       <c r="D54" s="2" t="n">
         <v>5.375108383613986</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="F54" s="2" t="n">
         <v>-7.751080530010632</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>19.28624202847321</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>28.94173773377847</v>
       </c>
-      <c r="H54" s="2" t="n">
-        <v>12.10916502064753</v>
-      </c>
       <c r="I54" s="2" t="n">
+        <v>13.54514104474548</v>
+      </c>
+      <c r="J54" s="2" t="n">
         <v>10.91</v>
       </c>
-      <c r="J54" s="3" t="n">
-        <v>1.199165020647529</v>
+      <c r="K54" s="3" t="n">
+        <v>2.635141044745483</v>
       </c>
     </row>
     <row r="55">
@@ -2223,23 +2229,23 @@
       <c r="D55" s="2" t="n">
         <v>5.436561604463231</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="F55" s="2" t="n">
         <v>-6.914986818017099</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>17.9967607277201</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>29.62907898039576</v>
       </c>
-      <c r="H55" s="2" t="n">
-        <v>12.40255946263705</v>
-      </c>
       <c r="I55" s="2" t="n">
+        <v>13.8655586472601</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>10.89</v>
       </c>
-      <c r="J55" s="3" t="n">
-        <v>1.512559462637052</v>
+      <c r="K55" s="3" t="n">
+        <v>2.975558647260101</v>
       </c>
     </row>
     <row r="56">
@@ -2257,23 +2263,23 @@
       <c r="D56" s="2" t="n">
         <v>5.028033853838826</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="F56" s="2" t="n">
         <v>-5.596764187137914</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>17.06287476563301</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>24.88888544218021</v>
       </c>
-      <c r="H56" s="2" t="n">
-        <v>11.21527261677401</v>
-      </c>
       <c r="I56" s="2" t="n">
+        <v>12.505589972537</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>11.08</v>
       </c>
-      <c r="J56" s="3" t="n">
-        <v>0.1352726167740066</v>
+      <c r="K56" s="3" t="n">
+        <v>1.425589972536995</v>
       </c>
     </row>
     <row r="57">
@@ -2291,23 +2297,23 @@
       <c r="D57" s="2" t="n">
         <v>7.231213388542593</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="F57" s="2" t="n">
         <v>-5.813219213001251</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>17.5257728321209</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>25.57528082411689</v>
       </c>
-      <c r="H57" s="2" t="n">
-        <v>12.15898614699934</v>
-      </c>
       <c r="I57" s="2" t="n">
+        <v>13.49128590680891</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>11.21</v>
       </c>
-      <c r="J57" s="3" t="n">
-        <v>0.9489861469993386</v>
+      <c r="K57" s="3" t="n">
+        <v>2.281285906808913</v>
       </c>
     </row>
     <row r="58">
@@ -2325,23 +2331,23 @@
       <c r="D58" s="2" t="n">
         <v>8.145517490454376</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="F58" s="2" t="n">
         <v>-6.238845657655744</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>18.15076082045445</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>28.68511555467585</v>
       </c>
-      <c r="H58" s="2" t="n">
-        <v>12.59937360479131</v>
-      </c>
       <c r="I58" s="2" t="n">
+        <v>13.95182212684851</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>11.47</v>
       </c>
-      <c r="J58" s="3" t="n">
-        <v>1.129373604791311</v>
+      <c r="K58" s="3" t="n">
+        <v>2.481822126848513</v>
       </c>
     </row>
     <row r="59">
@@ -2359,23 +2365,23 @@
       <c r="D59" s="2" t="n">
         <v>7.769955720914984</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="F59" s="2" t="n">
         <v>-6.330098981362794</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>16.96450885142118</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>29.1213695340774</v>
       </c>
-      <c r="H59" s="2" t="n">
-        <v>12.1364739125208</v>
-      </c>
       <c r="I59" s="2" t="n">
+        <v>13.46713598338557</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>11.97</v>
       </c>
-      <c r="J59" s="3" t="n">
-        <v>0.1664739125208019</v>
+      <c r="K59" s="3" t="n">
+        <v>1.497135983385574</v>
       </c>
     </row>
     <row r="60">
@@ -2393,23 +2399,23 @@
       <c r="D60" s="2" t="n">
         <v>10.57800047234397</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="F60" s="2" t="n">
         <v>-6.04876561950741</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>20.8800453075799</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>30.83015344394131</v>
       </c>
-      <c r="H60" s="2" t="n">
-        <v>13.10270596610814</v>
-      </c>
       <c r="I60" s="2" t="n">
+        <v>14.40136179791846</v>
+      </c>
+      <c r="J60" s="2" t="n">
         <v>12.23</v>
       </c>
-      <c r="J60" s="3" t="n">
-        <v>0.8727059661081409</v>
+      <c r="K60" s="3" t="n">
+        <v>2.171361797918458</v>
       </c>
     </row>
     <row r="61">
@@ -2427,23 +2433,23 @@
       <c r="D61" s="2" t="n">
         <v>11.01785814655606</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="F61" s="2" t="n">
         <v>-6.099450587258677</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>20.56677422997123</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>32.46817526492672</v>
       </c>
-      <c r="H61" s="2" t="n">
-        <v>13.41975014385678</v>
-      </c>
       <c r="I61" s="2" t="n">
+        <v>14.75379851354422</v>
+      </c>
+      <c r="J61" s="2" t="n">
         <v>11.88</v>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>1.539750143856779</v>
+      <c r="K61" s="3" t="n">
+        <v>2.873798513544216</v>
       </c>
     </row>
     <row r="62">
@@ -2461,23 +2467,23 @@
       <c r="D62" s="2" t="n">
         <v>12.75242026716855</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="F62" s="2" t="n">
         <v>-7.017370339678965</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>20.79110483818339</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>29.1681710269803</v>
       </c>
-      <c r="H62" s="2" t="n">
-        <v>14.33978866272736</v>
-      </c>
       <c r="I62" s="2" t="n">
+        <v>15.68214450164943</v>
+      </c>
+      <c r="J62" s="2" t="n">
         <v>11.74</v>
       </c>
-      <c r="J62" s="3" t="n">
-        <v>2.599788662727361</v>
+      <c r="K62" s="3" t="n">
+        <v>3.942144501649427</v>
       </c>
     </row>
     <row r="63">
@@ -2495,23 +2501,23 @@
       <c r="D63" s="2" t="n">
         <v>13.27803523401946</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="F63" s="2" t="n">
         <v>-6.348581779631825</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>20.68319252933468</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>30.60011965797399</v>
       </c>
-      <c r="H63" s="2" t="n">
-        <v>13.73092848944418</v>
-      </c>
       <c r="I63" s="2" t="n">
+        <v>15.00624429861198</v>
+      </c>
+      <c r="J63" s="2" t="n">
         <v>11.71</v>
       </c>
-      <c r="J63" s="3" t="n">
-        <v>2.020928489444175</v>
+      <c r="K63" s="3" t="n">
+        <v>3.296244298611976</v>
       </c>
     </row>
     <row r="64">
@@ -2529,23 +2535,23 @@
       <c r="D64" s="2" t="n">
         <v>12.83305523566156</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="F64" s="2" t="n">
         <v>-5.388503299893362</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>21.13103894291727</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>31.26751594277168</v>
       </c>
-      <c r="H64" s="2" t="n">
-        <v>13.28988613690225</v>
-      </c>
       <c r="I64" s="2" t="n">
+        <v>14.55265246851133</v>
+      </c>
+      <c r="J64" s="2" t="n">
         <v>12.3</v>
       </c>
-      <c r="J64" s="3" t="n">
-        <v>0.9898861369022462</v>
+      <c r="K64" s="3" t="n">
+        <v>2.252652468511329</v>
       </c>
     </row>
     <row r="65">
@@ -2563,23 +2569,23 @@
       <c r="D65" s="2" t="n">
         <v>13.16178784383836</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="F65" s="2" t="n">
         <v>-4.678514895347376</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>20.54104000335987</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>30.67869903650935</v>
       </c>
-      <c r="H65" s="2" t="n">
-        <v>13.04221618061323</v>
-      </c>
       <c r="I65" s="2" t="n">
+        <v>14.25229263839632</v>
+      </c>
+      <c r="J65" s="2" t="n">
         <v>13.36</v>
       </c>
-      <c r="J65" s="4" t="n">
-        <v>-0.3177838193867739</v>
+      <c r="K65" s="3" t="n">
+        <v>0.8922926383963254</v>
       </c>
     </row>
     <row r="66">
@@ -2597,23 +2603,23 @@
       <c r="D66" s="2" t="n">
         <v>15.50937293211657</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="F66" s="2" t="n">
         <v>-7.66247156187342</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>22.76473490916588</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>33.83309019395038</v>
       </c>
-      <c r="H66" s="2" t="n">
-        <v>13.74293889595908</v>
-      </c>
       <c r="I66" s="2" t="n">
+        <v>14.97400835054631</v>
+      </c>
+      <c r="J66" s="2" t="n">
         <v>13.61</v>
       </c>
-      <c r="J66" s="3" t="n">
-        <v>0.132938895959084</v>
+      <c r="K66" s="3" t="n">
+        <v>1.364008350546312</v>
       </c>
     </row>
     <row r="67">
@@ -2631,23 +2637,23 @@
       <c r="D67" s="2" t="n">
         <v>14.68126593877297</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="F67" s="2" t="n">
         <v>-7.389447099304347</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>22.41838069382961</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>31.63249894434386</v>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>13.1602752994137</v>
-      </c>
       <c r="I67" s="2" t="n">
+        <v>14.33488263401729</v>
+      </c>
+      <c r="J67" s="2" t="n">
         <v>14.96</v>
       </c>
-      <c r="J67" s="4" t="n">
-        <v>-1.799724700586298</v>
+      <c r="K67" s="4" t="n">
+        <v>-0.6251173659827156</v>
       </c>
     </row>
     <row r="68">
@@ -2665,23 +2671,23 @@
       <c r="D68" s="2" t="n">
         <v>16.53940718757023</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="F68" s="2" t="n">
         <v>-8.247082410311691</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>24.56049944216917</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="H68" s="2" t="n">
         <v>31.88374803839209</v>
       </c>
-      <c r="H68" s="2" t="n">
-        <v>14.42510655425158</v>
-      </c>
       <c r="I68" s="2" t="n">
+        <v>15.77706011002511</v>
+      </c>
+      <c r="J68" s="2" t="n">
         <v>15.14</v>
       </c>
-      <c r="J68" s="4" t="n">
-        <v>-0.714893445748416</v>
+      <c r="K68" s="3" t="n">
+        <v>0.6370601100251108</v>
       </c>
     </row>
     <row r="69">
@@ -2699,23 +2705,23 @@
       <c r="D69" s="2" t="n">
         <v>18.83888561740379</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="F69" s="2" t="n">
         <v>-12.94028361158985</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>27.5225196590493</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="H69" s="2" t="n">
         <v>35.116585278335</v>
       </c>
-      <c r="H69" s="2" t="n">
-        <v>16.42528837616403</v>
-      </c>
       <c r="I69" s="2" t="n">
+        <v>18.05368204767719</v>
+      </c>
+      <c r="J69" s="2" t="n">
         <v>15.42</v>
       </c>
-      <c r="J69" s="3" t="n">
-        <v>1.00528837616403</v>
+      <c r="K69" s="3" t="n">
+        <v>2.633682047677192</v>
       </c>
     </row>
     <row r="70">
@@ -2733,23 +2739,23 @@
       <c r="D70" s="2" t="n">
         <v>17.21242951207047</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="F70" s="2" t="n">
         <v>-11.81418858535387</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>25.81117654662714</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" s="2" t="n">
         <v>36.08295205281462</v>
       </c>
-      <c r="H70" s="2" t="n">
-        <v>15.49427338070218</v>
-      </c>
       <c r="I70" s="2" t="n">
+        <v>17.04912174294473</v>
+      </c>
+      <c r="J70" s="2" t="n">
         <v>15.88</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>-0.3857266192978184</v>
+      <c r="K70" s="3" t="n">
+        <v>1.169121742944727</v>
       </c>
     </row>
     <row r="71">
@@ -2767,23 +2773,23 @@
       <c r="D71" s="2" t="n">
         <v>19.40142162187621</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="F71" s="2" t="n">
         <v>-14.65057114288289</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>30.16952540833589</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>42.6905677244131</v>
       </c>
-      <c r="H71" s="2" t="n">
-        <v>17.3559864014355</v>
-      </c>
       <c r="I71" s="2" t="n">
+        <v>19.14952912982974</v>
+      </c>
+      <c r="J71" s="2" t="n">
         <v>15.87</v>
       </c>
-      <c r="J71" s="3" t="n">
-        <v>1.485986401435499</v>
+      <c r="K71" s="3" t="n">
+        <v>3.279529129829738</v>
       </c>
     </row>
     <row r="72">
@@ -2801,23 +2807,23 @@
       <c r="D72" s="2" t="n">
         <v>16.26634255759164</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="F72" s="2" t="n">
         <v>-10.83363647130832</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>22.14796142562243</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>47.49133104482092</v>
       </c>
-      <c r="H72" s="2" t="n">
-        <v>17.61980755967381</v>
-      </c>
       <c r="I72" s="2" t="n">
+        <v>19.34263091614233</v>
+      </c>
+      <c r="J72" s="2" t="n">
         <v>16.84</v>
       </c>
-      <c r="J72" s="3" t="n">
-        <v>0.779807559673813</v>
+      <c r="K72" s="3" t="n">
+        <v>2.50263091614233</v>
       </c>
     </row>
     <row r="73">
@@ -2835,23 +2841,23 @@
       <c r="D73" s="2" t="n">
         <v>14.11262726510331</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="F73" s="2" t="n">
         <v>-9.629169768802969</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>17.46840287343869</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>41.24262785974076</v>
       </c>
-      <c r="H73" s="2" t="n">
-        <v>14.90155728709435</v>
-      </c>
       <c r="I73" s="2" t="n">
+        <v>16.36960995997031</v>
+      </c>
+      <c r="J73" s="2" t="n">
         <v>16.17</v>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>-1.268442712905657</v>
+      <c r="K73" s="3" t="n">
+        <v>0.1996099599703065</v>
       </c>
     </row>
     <row r="74">
@@ -2869,23 +2875,23 @@
       <c r="D74" s="2" t="n">
         <v>14.97478836197704</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="F74" s="2" t="n">
         <v>-8.093701049402519</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>19.41566696816943</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="H74" s="2" t="n">
         <v>49.35868177913012</v>
       </c>
-      <c r="H74" s="2" t="n">
-        <v>15.39673360368009</v>
-      </c>
       <c r="I74" s="2" t="n">
+        <v>16.831325561031</v>
+      </c>
+      <c r="J74" s="2" t="n">
         <v>15.38</v>
       </c>
-      <c r="J74" s="3" t="n">
-        <v>0.01673360368008581</v>
+      <c r="K74" s="3" t="n">
+        <v>1.451325561031004</v>
       </c>
     </row>
     <row r="75">
@@ -2903,23 +2909,23 @@
       <c r="D75" s="2" t="n">
         <v>13.85518653104446</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="F75" s="2" t="n">
         <v>-7.201231924952639</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>18.3943410823337</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="H75" s="2" t="n">
         <v>45.15485075737434</v>
       </c>
-      <c r="H75" s="2" t="n">
-        <v>14.06567040554057</v>
-      </c>
       <c r="I75" s="2" t="n">
+        <v>15.36081067225093</v>
+      </c>
+      <c r="J75" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>-2.534329594459431</v>
+      <c r="K75" s="4" t="n">
+        <v>-1.239189327749072</v>
       </c>
     </row>
     <row r="76">
@@ -2937,23 +2943,23 @@
       <c r="D76" s="2" t="n">
         <v>13.53488775166749</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="F76" s="2" t="n">
         <v>-7.537104939075248</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>20.85254507407065</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>50.52098358286025</v>
       </c>
-      <c r="H76" s="2" t="n">
-        <v>14.02399691190776</v>
-      </c>
       <c r="I76" s="2" t="n">
+        <v>15.35812081525662</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>15.55</v>
       </c>
-      <c r="J76" s="4" t="n">
-        <v>-1.526003088092239</v>
+      <c r="K76" s="4" t="n">
+        <v>-0.1918791847433852</v>
       </c>
     </row>
     <row r="77">
@@ -2971,23 +2977,23 @@
       <c r="D77" s="2" t="n">
         <v>14.37008998658015</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="F77" s="2" t="n">
         <v>-7.585348843205882</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>22.5042318126109</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>42.20896854690343</v>
       </c>
-      <c r="H77" s="2" t="n">
-        <v>14.34403033634302</v>
-      </c>
       <c r="I77" s="2" t="n">
+        <v>15.62850545858401</v>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>15.22</v>
       </c>
-      <c r="J77" s="4" t="n">
-        <v>-0.875969663656976</v>
+      <c r="K77" s="3" t="n">
+        <v>0.4085054585840133</v>
       </c>
     </row>
     <row r="78">
@@ -3005,23 +3011,23 @@
       <c r="D78" s="2" t="n">
         <v>15.56617972544995</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="F78" s="2" t="n">
         <v>-7.008228794805643</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>18.88663129780421</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" s="2" t="n">
         <v>45.62913925873848</v>
       </c>
-      <c r="H78" s="2" t="n">
-        <v>14.57949073050029</v>
-      </c>
       <c r="I78" s="2" t="n">
+        <v>15.89586518169642</v>
+      </c>
+      <c r="J78" s="2" t="n">
         <v>15.79</v>
       </c>
-      <c r="J78" s="4" t="n">
-        <v>-1.210509269499713</v>
+      <c r="K78" s="3" t="n">
+        <v>0.1058651816964247</v>
       </c>
     </row>
     <row r="79">
@@ -3039,23 +3045,23 @@
       <c r="D79" s="2" t="n">
         <v>15.20322290321027</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="F79" s="2" t="n">
         <v>-6.529471546660362</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>18.23971186718758</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>40.33681205418513</v>
       </c>
-      <c r="H79" s="2" t="n">
-        <v>14.28992234462034</v>
-      </c>
       <c r="I79" s="2" t="n">
+        <v>15.54886274234733</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>15.41</v>
       </c>
-      <c r="J79" s="4" t="n">
-        <v>-1.120077655379664</v>
+      <c r="K79" s="3" t="n">
+        <v>0.1388627423473263</v>
       </c>
     </row>
     <row r="80">
@@ -3073,23 +3079,23 @@
       <c r="D80" s="2" t="n">
         <v>15.73976191081897</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="F80" s="2" t="n">
         <v>-6.199716042508775</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>19.22417385644482</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="H80" s="2" t="n">
         <v>55.09291727395582</v>
       </c>
-      <c r="H80" s="2" t="n">
-        <v>14.88499769340604</v>
-      </c>
       <c r="I80" s="2" t="n">
+        <v>16.24693513128206</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="J80" s="3" t="n">
-        <v>0.1849976934060393</v>
+      <c r="K80" s="3" t="n">
+        <v>1.546935131282062</v>
       </c>
     </row>
     <row r="81">
@@ -3107,23 +3113,23 @@
       <c r="D81" s="2" t="n">
         <v>17.01796598909259</v>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="F81" s="2" t="n">
         <v>-2.807740841835126</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>11.41095129815538</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="H81" s="2" t="n">
         <v>55.41821966877728</v>
       </c>
-      <c r="H81" s="2" t="n">
-        <v>15.24785703697768</v>
-      </c>
       <c r="I81" s="2" t="n">
+        <v>16.49690250186826</v>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="J81" s="3" t="n">
-        <v>1.147857036977676</v>
+      <c r="K81" s="3" t="n">
+        <v>2.396902501868263</v>
       </c>
     </row>
     <row r="82">
@@ -3141,23 +3147,23 @@
       <c r="D82" s="2" t="n">
         <v>18.43778849266601</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="F82" s="2" t="n">
         <v>-2.982588064754726</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>12.7520293128997</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>61.10151420347143</v>
       </c>
-      <c r="H82" s="2" t="n">
-        <v>16.4662097401464</v>
-      </c>
       <c r="I82" s="2" t="n">
+        <v>17.8117751391968</v>
+      </c>
+      <c r="J82" s="2" t="n">
         <v>13.85</v>
       </c>
-      <c r="J82" s="3" t="n">
-        <v>2.616209740146397</v>
+      <c r="K82" s="3" t="n">
+        <v>3.961775139196797</v>
       </c>
     </row>
     <row r="83">
@@ -3175,20 +3181,20 @@
       <c r="D83" s="2" t="n">
         <v>19.30323570762788</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>13.71730908439518</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>61.22727445028835</v>
       </c>
-      <c r="H83" s="2" t="n">
-        <v>18.06735385488424</v>
-      </c>
       <c r="I83" s="2" t="n">
+        <v>19.09243309684751</v>
+      </c>
+      <c r="J83" s="2" t="n">
         <v>14.95</v>
       </c>
-      <c r="J83" s="3" t="n">
-        <v>3.117353854884243</v>
+      <c r="K83" s="3" t="n">
+        <v>4.142433096847512</v>
       </c>
     </row>
     <row r="84">
@@ -3206,23 +3212,23 @@
       <c r="D84" s="2" t="n">
         <v>18.4857121282005</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="F84" s="2" t="n">
         <v>-2.0387029767035</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>10.13451644820684</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" s="2" t="n">
         <v>56.90241575040731</v>
       </c>
-      <c r="H84" s="2" t="n">
-        <v>16.41735913006671</v>
-      </c>
       <c r="I84" s="2" t="n">
+        <v>17.65622699937551</v>
+      </c>
+      <c r="J84" s="2" t="n">
         <v>14.58</v>
       </c>
-      <c r="J84" s="3" t="n">
-        <v>1.837359130066707</v>
+      <c r="K84" s="3" t="n">
+        <v>3.076226999375509</v>
       </c>
     </row>
     <row r="85">
@@ -3240,23 +3246,23 @@
       <c r="D85" s="2" t="n">
         <v>17.56480805449685</v>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="F85" s="2" t="n">
         <v>-1.666286666177114</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>10.03540137291876</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>57.39879517332002</v>
       </c>
-      <c r="H85" s="2" t="n">
-        <v>16.2482868462084</v>
-      </c>
       <c r="I85" s="2" t="n">
+        <v>17.53067384974711</v>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>14.35</v>
       </c>
-      <c r="J85" s="3" t="n">
-        <v>1.898286846208398</v>
+      <c r="K85" s="3" t="n">
+        <v>3.180673849747107</v>
       </c>
     </row>
     <row r="86">
@@ -3274,23 +3280,23 @@
       <c r="D86" s="2" t="n">
         <v>19.80224755118467</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="F86" s="2" t="n">
         <v>-0.09647910097051274</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>6.780199126557799</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="H86" s="2" t="n">
         <v>48.29687542764808</v>
       </c>
-      <c r="H86" s="2" t="n">
-        <v>17.04214099949286</v>
-      </c>
       <c r="I86" s="2" t="n">
+        <v>18.21033073391868</v>
+      </c>
+      <c r="J86" s="2" t="n">
         <v>14.35</v>
       </c>
-      <c r="J86" s="3" t="n">
-        <v>2.692140999492862</v>
+      <c r="K86" s="3" t="n">
+        <v>3.860330733918678</v>
       </c>
     </row>
     <row r="87">
@@ -3308,23 +3314,23 @@
       <c r="D87" s="2" t="n">
         <v>19.04871474507365</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="F87" s="2" t="n">
         <v>-0.09477790681339356</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>7.012368278640311</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" s="2" t="n">
         <v>43.04353108288635</v>
       </c>
-      <c r="H87" s="2" t="n">
-        <v>16.50170408662019</v>
-      </c>
       <c r="I87" s="2" t="n">
+        <v>17.61386555404088</v>
+      </c>
+      <c r="J87" s="2" t="n">
         <v>14.63</v>
       </c>
-      <c r="J87" s="3" t="n">
-        <v>1.871704086620189</v>
+      <c r="K87" s="3" t="n">
+        <v>2.983865554040884</v>
       </c>
     </row>
     <row r="88">
@@ -3342,23 +3348,23 @@
       <c r="D88" s="2" t="n">
         <v>20.42888543195352</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="F88" s="2" t="n">
         <v>-0.1019120748671265</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="G88" s="2" t="n">
         <v>5.73871550358888</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>43.48374617211803</v>
       </c>
-      <c r="H88" s="2" t="n">
-        <v>17.08901464148825</v>
-      </c>
       <c r="I88" s="2" t="n">
+        <v>18.16119820693056</v>
+      </c>
+      <c r="J88" s="2" t="n">
         <v>14.31</v>
       </c>
-      <c r="J88" s="3" t="n">
-        <v>2.779014641488251</v>
+      <c r="K88" s="3" t="n">
+        <v>3.85119820693056</v>
       </c>
     </row>
     <row r="89">
@@ -3376,23 +3382,23 @@
       <c r="D89" s="2" t="n">
         <v>21.60634280555315</v>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="F89" s="2" t="n">
         <v>-0.1081495849915241</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="G89" s="2" t="n">
         <v>6.455636179460461</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="H89" s="2" t="n">
         <v>40.98093033274804</v>
       </c>
-      <c r="H89" s="2" t="n">
-        <v>17.21475277080632</v>
-      </c>
       <c r="I89" s="2" t="n">
+        <v>18.23046146050133</v>
+      </c>
+      <c r="J89" s="2" t="n">
         <v>14.47</v>
       </c>
-      <c r="J89" s="3" t="n">
-        <v>2.74475277080632</v>
+      <c r="K89" s="3" t="n">
+        <v>3.760461460501327</v>
       </c>
     </row>
     <row r="90">
@@ -3411,22 +3417,25 @@
         <v>22.59115118228355</v>
       </c>
       <c r="E90" s="2" t="n">
+        <v>23.28528000950682</v>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>1.379083653123741</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="G90" s="2" t="n">
         <v>5.767738688811785</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="H90" s="2" t="n">
         <v>46.52046352872824</v>
       </c>
-      <c r="H90" s="2" t="n">
-        <v>18.42192842034994</v>
-      </c>
       <c r="I90" s="2" t="n">
+        <v>19.72232554050118</v>
+      </c>
+      <c r="J90" s="2" t="n">
         <v>14.58</v>
       </c>
-      <c r="J90" s="3" t="n">
-        <v>3.841928420349943</v>
+      <c r="K90" s="3" t="n">
+        <v>5.142325540501178</v>
       </c>
     </row>
     <row r="91">
@@ -3445,22 +3454,25 @@
         <v>24.98016915265062</v>
       </c>
       <c r="E91" s="2" t="n">
+        <v>24.7609205051501</v>
+      </c>
+      <c r="F91" s="2" t="n">
         <v>1.604773830895742</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>6.826779323571571</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>49.7594094486424</v>
       </c>
-      <c r="H91" s="2" t="n">
-        <v>19.64870539751299</v>
-      </c>
       <c r="I91" s="2" t="n">
+        <v>20.97827885532184</v>
+      </c>
+      <c r="J91" s="2" t="n">
         <v>14.93</v>
       </c>
-      <c r="J91" s="3" t="n">
-        <v>4.718705397512995</v>
+      <c r="K91" s="3" t="n">
+        <v>6.04827885532184</v>
       </c>
     </row>
     <row r="92">
@@ -3479,22 +3491,25 @@
         <v>25.49696149851162</v>
       </c>
       <c r="E92" s="2" t="n">
+        <v>25.28694579734449</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>1.934305447366598</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="G92" s="2" t="n">
         <v>6.458639800083027</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="H92" s="2" t="n">
         <v>65.14432350675698</v>
       </c>
-      <c r="H92" s="2" t="n">
-        <v>20.90136446361501</v>
-      </c>
       <c r="I92" s="2" t="n">
+        <v>22.40205186534319</v>
+      </c>
+      <c r="J92" s="2" t="n">
         <v>16.45</v>
       </c>
-      <c r="J92" s="3" t="n">
-        <v>4.451364463615015</v>
+      <c r="K92" s="3" t="n">
+        <v>5.952051865343186</v>
       </c>
     </row>
     <row r="93">
@@ -3504,31 +3519,34 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>29.02710335216893</v>
+        <v>31.65944859455749</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>10.39214327297067</v>
+        <v>12.37559509621946</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>24.4856725706625</v>
+        <v>26.93088909072161</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1.687732686703668</v>
+        <v>28.17575444671709</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>6.499765726451138</v>
+        <v>3.486740869985585</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>64.50374719132617</v>
+        <v>7.116682169193054</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>20.32578669531726</v>
+        <v>60.42236054949741</v>
       </c>
       <c r="I93" s="2" t="n">
+        <v>24.16046679071513</v>
+      </c>
+      <c r="J93" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J93" s="3" t="n">
-        <v>5.325786695317262</v>
+      <c r="K93" s="3" t="n">
+        <v>9.16046679071513</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -2678,16 +2678,16 @@
         <v>24.56049944216917</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>31.88374803839209</v>
+        <v>76.75710374430747</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.77706011002511</v>
+        <v>16.30641030179403</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>15.14</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.6370601100251108</v>
+        <v>1.166410301794027</v>
       </c>
     </row>
     <row r="69">
@@ -2712,16 +2712,16 @@
         <v>27.5225196590493</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>35.116585278335</v>
+        <v>84.5398532226926</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.05368204767719</v>
+        <v>18.6367054465879</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>15.42</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>2.633682047677192</v>
+        <v>3.216705446587904</v>
       </c>
     </row>
     <row r="70">
@@ -2746,16 +2746,16 @@
         <v>25.81117654662714</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>36.08295205281462</v>
+        <v>86.86628970922069</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.04912174294473</v>
+        <v>17.64818925425947</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>15.88</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.169121742944727</v>
+        <v>1.768189254259473</v>
       </c>
     </row>
     <row r="71">
@@ -2780,16 +2780,16 @@
         <v>30.16952540833589</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.6905677244131</v>
+        <v>102.7734986420189</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.14952912982974</v>
+        <v>19.85829963524305</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>15.87</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.279529129829738</v>
+        <v>3.988299635243051</v>
       </c>
     </row>
     <row r="72">
@@ -2814,16 +2814,16 @@
         <v>22.14796142562243</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.49133104482092</v>
+        <v>114.3308816633844</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.34263091614233</v>
+        <v>20.1311061344782</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>16.84</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>2.50263091614233</v>
+        <v>3.291106134478198</v>
       </c>
     </row>
     <row r="73">
@@ -2848,16 +2848,16 @@
         <v>17.46840287343869</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.24262785974076</v>
+        <v>99.28772054985896</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.36960995997031</v>
+        <v>17.05434103174768</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>16.17</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.1996099599703065</v>
+        <v>0.8843410317476774</v>
       </c>
     </row>
     <row r="74">
@@ -2882,16 +2882,16 @@
         <v>19.41566696816943</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.35868177913012</v>
+        <v>118.826351702471</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.831325561031</v>
+        <v>17.65080348545137</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.451325561031004</v>
+        <v>2.270803485451369</v>
       </c>
     </row>
     <row r="75">
@@ -2916,16 +2916,16 @@
         <v>18.3943410823337</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.15485075737434</v>
+        <v>108.7060266556194</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.36081067225093</v>
+        <v>16.11049445719776</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>16.6</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-1.239189327749072</v>
+        <v>-0.4895055428022417</v>
       </c>
     </row>
     <row r="76">
@@ -2950,16 +2950,16 @@
         <v>20.85254507407065</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.52098358286025</v>
+        <v>121.6244832152306</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.35812081525662</v>
+        <v>16.19689586503241</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>15.55</v>
       </c>
-      <c r="K76" s="4" t="n">
-        <v>-0.1918791847433852</v>
+      <c r="K76" s="3" t="n">
+        <v>0.6468958650324126</v>
       </c>
     </row>
     <row r="77">
@@ -2984,16 +2984,16 @@
         <v>22.5042318126109</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.20896854690343</v>
+        <v>101.6140942336422</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.62850545858401</v>
+        <v>16.32928020965052</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>15.22</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.4085054585840133</v>
+        <v>1.109280209650519</v>
       </c>
     </row>
     <row r="78">
@@ -3018,16 +3018,16 @@
         <v>18.88663129780421</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.62913925873848</v>
+        <v>109.847831303558</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.89586518169642</v>
+        <v>16.6534233454286</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>15.79</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.1058651816964247</v>
+        <v>0.863423345428604</v>
       </c>
     </row>
     <row r="79">
@@ -3052,16 +3052,16 @@
         <v>18.23971186718758</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.33681205418513</v>
+        <v>97.10705478633119</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.54886274234733</v>
+        <v>16.21855499968541</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>15.41</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.1388627423473263</v>
+        <v>0.8085549996854127</v>
       </c>
     </row>
     <row r="80">
@@ -3086,16 +3086,16 @@
         <v>19.22417385644482</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>55.09291727395582</v>
+        <v>132.6309805761103</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.24693513128206</v>
+        <v>17.16161574815813</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>14.7</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>1.546935131282062</v>
+        <v>2.461615748158128</v>
       </c>
     </row>
     <row r="81">
@@ -3120,16 +3120,16 @@
         <v>11.41095129815538</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>55.41821966877728</v>
+        <v>133.4141152827802</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.49690250186826</v>
+        <v>17.41698395445769</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>2.396902501868263</v>
+        <v>3.316983954457688</v>
       </c>
     </row>
     <row r="82">
@@ -3154,16 +3154,16 @@
         <v>12.7520293128997</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>61.10151420347143</v>
+        <v>119.3211636384267</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.8117751391968</v>
+        <v>18.49856537603772</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>13.85</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>3.961775139196797</v>
+        <v>4.648565376037718</v>
       </c>
     </row>
     <row r="83">
@@ -3185,16 +3185,16 @@
         <v>13.71730908439518</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>61.22727445028835</v>
+        <v>119.5667526256273</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.09243309684751</v>
+        <v>19.82360512411116</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>14.95</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>4.142433096847512</v>
+        <v>4.873605124111158</v>
       </c>
     </row>
     <row r="84">
@@ -3219,16 +3219,16 @@
         <v>10.13451644820684</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>56.90241575040731</v>
+        <v>111.1210180252848</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.65622699937551</v>
+        <v>18.2958187361679</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>14.58</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>3.076226999375509</v>
+        <v>3.715818736167895</v>
       </c>
     </row>
     <row r="85">
@@ -3253,16 +3253,16 @@
         <v>10.03540137291876</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>57.39879517332002</v>
+        <v>112.0903650393519</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.53067384974711</v>
+        <v>18.17584496613211</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>3.180673849747107</v>
+        <v>3.825844966132115</v>
       </c>
     </row>
     <row r="86">
@@ -3287,16 +3287,16 @@
         <v>6.780199126557799</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.29687542764808</v>
+        <v>94.31581935820005</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.21033073391868</v>
+        <v>18.7531948993332</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>3.860330733918678</v>
+        <v>4.403194899333199</v>
       </c>
     </row>
     <row r="87">
@@ -3321,16 +3321,16 @@
         <v>7.012368278640311</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.04353108288635</v>
+        <v>84.05690567362392</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.61386555404088</v>
+        <v>18.09768133655067</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>14.63</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>2.983865554040884</v>
+        <v>3.467681336550667</v>
       </c>
     </row>
     <row r="88">
@@ -3355,16 +3355,16 @@
         <v>5.73871550358888</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.48374617211803</v>
+        <v>84.91657302202056</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.16119820693056</v>
+        <v>18.64996207344997</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>14.31</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>3.85119820693056</v>
+        <v>4.339962073449973</v>
       </c>
     </row>
     <row r="89">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -527,16 +527,16 @@
         <v>19.08913342354207</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.851244304880336</v>
+        <v>18.90112708537118</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.23925949930118</v>
+        <v>12.40712531436369</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.469259499301183</v>
+        <v>3.637125314363692</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +555,16 @@
         <v>19.68507051261704</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.260208841095547</v>
+        <v>19.88567047394066</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12.77733465514106</v>
+        <v>12.95394445555641</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.23</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4.547334655141062</v>
+        <v>4.72394445555641</v>
       </c>
     </row>
     <row r="4">
@@ -583,16 +583,16 @@
         <v>19.05438378745552</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8.319301371730404</v>
+        <v>20.02793014488622</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.3800683677762</v>
+        <v>12.55794161324993</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>8.43</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>3.950068367776199</v>
+        <v>4.127941613249925</v>
       </c>
     </row>
     <row r="5">
@@ -611,16 +611,16 @@
         <v>18.30785009429028</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8.353281616769864</v>
+        <v>20.10973436660478</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11.80558571554623</v>
+        <v>11.98418548554373</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3.415585715546234</v>
+        <v>3.594185485543726</v>
       </c>
     </row>
     <row r="6">
@@ -639,16 +639,16 @@
         <v>20.72341951426353</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7.672385559350714</v>
+        <v>18.47054159493064</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11.73804810697836</v>
+        <v>11.90208978055023</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>8.25</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3.488048106978356</v>
+        <v>3.652089780550233</v>
       </c>
     </row>
     <row r="7">
@@ -667,16 +667,16 @@
         <v>21.64834897388687</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.06155747131314</v>
+        <v>17.00003082351878</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.48402245659083</v>
+        <v>11.63500414235953</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>8.01</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3.474022456590832</v>
+        <v>3.625004142359531</v>
       </c>
     </row>
     <row r="8">
@@ -695,16 +695,16 @@
         <v>21.26612311808534</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6.626233222493365</v>
+        <v>15.95202892333951</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.65037186760847</v>
+        <v>11.79204597651331</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4.200371867608472</v>
+        <v>4.342045976513313</v>
       </c>
     </row>
     <row r="9">
@@ -723,16 +723,16 @@
         <v>21.42395840799424</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6.736086902573284</v>
+        <v>16.21649125406785</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.55957143229307</v>
+        <v>12.70359429979313</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>7.43</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>5.129571432293069</v>
+        <v>5.273594299793126</v>
       </c>
     </row>
     <row r="10">
@@ -751,16 +751,16 @@
         <v>20.7929403151282</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6.116958361111272</v>
+        <v>14.72599792715916</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.46725560875859</v>
+        <v>12.59804101819402</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5.257255608758594</v>
+        <v>5.388041018194024</v>
       </c>
     </row>
     <row r="11">
@@ -782,16 +782,16 @@
         <v>20.4659151974959</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6.046689287341252</v>
+        <v>14.55683178712797</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.29566940986691</v>
+        <v>12.40232751409559</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>7.16</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>5.135669409866914</v>
+        <v>5.242327514095585</v>
       </c>
     </row>
     <row r="12">
@@ -813,16 +813,16 @@
         <v>19.66281621935698</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>6.113764313350083</v>
+        <v>14.71830855967719</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11.64737438454345</v>
+        <v>11.75521563127791</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>6.51</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>5.137374384543445</v>
+        <v>5.245215631277912</v>
       </c>
     </row>
     <row r="13">
@@ -844,16 +844,16 @@
         <v>19.2824148381953</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6.037841749981683</v>
+        <v>14.53553217887074</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10.75212148143339</v>
+        <v>10.85862352314305</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>6.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>4.152121481433392</v>
+        <v>4.258623523143051</v>
       </c>
     </row>
     <row r="14">
@@ -875,16 +875,16 @@
         <v>18.02677704153395</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>7.220235293944389</v>
+        <v>17.38203265338401</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10.92140634135686</v>
+        <v>11.04876473070709</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6.42</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.50140634135686</v>
+        <v>4.628764730707086</v>
       </c>
     </row>
     <row r="15">
@@ -906,16 +906,16 @@
         <v>21.47215262384002</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>7.731800545557801</v>
+        <v>18.61357754712712</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11.71584479325076</v>
+        <v>11.85222672876543</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>6.37</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.34584479325076</v>
+        <v>5.482226728765426</v>
       </c>
     </row>
     <row r="16">
@@ -937,16 +937,16 @@
         <v>27.55484768079231</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.27665391530735</v>
+        <v>24.74007101585946</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15.24672225810425</v>
+        <v>15.42799309448003</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>6.55</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8.696722258104248</v>
+        <v>8.877993094480029</v>
       </c>
     </row>
     <row r="17">
@@ -968,16 +968,16 @@
         <v>25.80624569777168</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.599395920888814</v>
+        <v>23.10963653630424</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.21658726275516</v>
+        <v>14.38591188355317</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>6.89</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7.326587262755161</v>
+        <v>7.495911883553169</v>
       </c>
     </row>
     <row r="18">
@@ -999,16 +999,16 @@
         <v>17.80772152671224</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8.920597742609777</v>
+        <v>21.47549420997321</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12.28282631735969</v>
+        <v>12.44017755513624</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>6.18</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>6.102826317359694</v>
+        <v>6.260177555136238</v>
       </c>
     </row>
     <row r="19">
@@ -1030,16 +1030,16 @@
         <v>18.51648656260129</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.241281142201457</v>
+        <v>22.24750912308494</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.68845373373323</v>
+        <v>11.85146153526437</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5.67</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>6.018453733733232</v>
+        <v>6.181461535264368</v>
       </c>
     </row>
     <row r="20">
@@ -1061,16 +1061,16 @@
         <v>18.77070562720411</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.357809419021057</v>
+        <v>20.1206346217037</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.34673278058047</v>
+        <v>10.49415694375081</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.336732780580475</v>
+        <v>4.48415694375081</v>
       </c>
     </row>
     <row r="21">
@@ -1092,16 +1092,16 @@
         <v>10.71995641599881</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>7.834259684075175</v>
+        <v>18.86023821936868</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9.145835752639334</v>
+        <v>9.284024974249888</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.135835752639334</v>
+        <v>3.274024974249889</v>
       </c>
     </row>
     <row r="22">
@@ -1123,16 +1123,16 @@
         <v>10.44565988107247</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.038779878873365</v>
+        <v>19.35260121856902</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8.920395552516448</v>
+        <v>9.062192324509873</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.700395552516448</v>
+        <v>2.842192324509873</v>
       </c>
     </row>
     <row r="23">
@@ -1154,16 +1154,16 @@
         <v>11.43707185377575</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>8.484216633220857</v>
+        <v>20.42494801806726</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10.06302454718287</v>
+        <v>10.21267841874183</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>6.39</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.673024547182872</v>
+        <v>3.822678418741831</v>
       </c>
     </row>
     <row r="24">
@@ -1188,16 +1188,16 @@
         <v>5.667647954234813</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.932480880226692</v>
+        <v>14.28188586349287</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8.517832735490186</v>
+        <v>8.616326798604472</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.997832735490187</v>
+        <v>2.096326798604473</v>
       </c>
     </row>
     <row r="25">
@@ -1222,16 +1222,16 @@
         <v>5.855223524312912</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>5.825243793461807</v>
+        <v>14.02372273335717</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7.991778046485789</v>
+        <v>8.088491704975896</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>6.16</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.831778046485788</v>
+        <v>1.928491704975896</v>
       </c>
     </row>
     <row r="26">
@@ -1256,16 +1256,16 @@
         <v>3.411173174992418</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>3.395338119139771</v>
+        <v>8.173954954856562</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7.897926171050143</v>
+        <v>7.954297300389227</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1.647926171050143</v>
+        <v>1.704297300389227</v>
       </c>
     </row>
     <row r="27">
@@ -1290,16 +1290,16 @@
         <v>3.082994003575836</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>3.355042804981403</v>
+        <v>8.076947802324213</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7.398964980146275</v>
+        <v>7.45466710619718</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.8189649801462746</v>
+        <v>0.8746671061971796</v>
       </c>
     </row>
     <row r="28">
@@ -1324,16 +1324,16 @@
         <v>2.817822060376203</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2.912049912084408</v>
+        <v>7.010484367813883</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6.815466901936662</v>
+        <v>6.863814234801869</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>7.02</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2045330980633375</v>
+        <v>-0.1561857651981304</v>
       </c>
     </row>
     <row r="29">
@@ -1358,16 +1358,16 @@
         <v>3.072134256990506</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2.410624263462897</v>
+        <v>5.803349607968413</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6.706209647393882</v>
+        <v>6.746232056760884</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5637903526061177</v>
+        <v>-0.5237679432391156</v>
       </c>
     </row>
     <row r="30">
@@ -1392,16 +1392,16 @@
         <v>5.61092328242254</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.092691118758473</v>
+        <v>9.852766256265783</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7.647082482300239</v>
+        <v>7.715031420610661</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>7.17</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.4770824823002391</v>
+        <v>0.5450314206106608</v>
       </c>
     </row>
     <row r="31">
@@ -1426,16 +1426,16 @@
         <v>5.219966092926011</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>4.115909067343487</v>
+        <v>9.90866126854991</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7.631384545223767</v>
+        <v>7.699718959718519</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>7.26</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.3713845452237674</v>
+        <v>0.4397189597185189</v>
       </c>
     </row>
     <row r="32">
@@ -1460,16 +1460,16 @@
         <v>5.475931372413843</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4.117183079642499</v>
+        <v>9.91172833250014</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7.678787980894248</v>
+        <v>7.747143547188781</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.4687879808942483</v>
+        <v>0.5371435471887809</v>
       </c>
     </row>
     <row r="33">
@@ -1494,16 +1494,16 @@
         <v>11.26399397667822</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>6.411812180253669</v>
+        <v>15.43583057161696</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8.270628595767322</v>
+        <v>8.377080760773664</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>6.97</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.300628595767322</v>
+        <v>1.407080760773664</v>
       </c>
     </row>
     <row r="34">
@@ -1528,16 +1528,16 @@
         <v>9.783457615293401</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.538385596624072</v>
+        <v>15.74054408396551</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7.93386177927357</v>
+        <v>8.042415380477056</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>7.09</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.8438617792735696</v>
+        <v>0.9524153804770563</v>
       </c>
     </row>
     <row r="35">
@@ -1562,16 +1562,16 @@
         <v>9.448934422190694</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>6.406948298455638</v>
+        <v>15.42412123683857</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7.519675884255697</v>
+        <v>7.626047296624068</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.06967588425569726</v>
+        <v>0.176047296624068</v>
       </c>
     </row>
     <row r="36">
@@ -1596,16 +1596,16 @@
         <v>14.38422404715066</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.61123734309326</v>
+        <v>23.13814363877954</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8.902873610914304</v>
+        <v>9.062444258774672</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>8.32</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.5828736109143033</v>
+        <v>0.7424442587746718</v>
       </c>
     </row>
     <row r="37">
@@ -1630,16 +1630,16 @@
         <v>13.59417234239063</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.411813391581832</v>
+        <v>22.65804936263514</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.510095029909841</v>
+        <v>9.666354739957981</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>8.35</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.160095029909842</v>
+        <v>1.316354739957982</v>
       </c>
     </row>
     <row r="38">
@@ -1664,16 +1664,16 @@
         <v>17.28644177708432</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>12.32327862399001</v>
+        <v>29.66712616950256</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.61763349983536</v>
+        <v>10.82223083559953</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>2.247633499835365</v>
+        <v>2.452230835599527</v>
       </c>
     </row>
     <row r="39">
@@ -1698,16 +1698,16 @@
         <v>32.38646722938399</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>26.82810234501654</v>
+        <v>64.58611554951874</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.01360330393863</v>
+        <v>22.45901709606967</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>9.42</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>12.59360330393863</v>
+        <v>13.03901709606967</v>
       </c>
     </row>
     <row r="40">
@@ -1732,10 +1732,10 @@
         <v>22.79637161894582</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>27.24813829082235</v>
+        <v>65.59731230812231</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.36024961236827</v>
+        <v>20.81263705478015</v>
       </c>
     </row>
     <row r="41">
@@ -1760,16 +1760,16 @@
         <v>24.3848718417819</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>26.84812829849628</v>
+        <v>64.63432613589559</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.65014683908102</v>
+        <v>23.09589311227112</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>11.36</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.29014683908102</v>
+        <v>11.73589311227112</v>
       </c>
     </row>
     <row r="42">
@@ -1794,16 +1794,16 @@
         <v>27.38071406266658</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>29.46549088794553</v>
+        <v>70.93537868382424</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.42802201234696</v>
+        <v>23.9172230696793</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>13.10802201234696</v>
+        <v>13.5972230696793</v>
       </c>
     </row>
     <row r="43">
@@ -1828,16 +1828,16 @@
         <v>28.49559475949014</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>30.34382104377292</v>
+        <v>73.04987534875264</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.36083694115864</v>
+        <v>22.86462048220223</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>9.23</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>13.13083694115864</v>
+        <v>13.63462048220223</v>
       </c>
     </row>
     <row r="44">
@@ -1862,16 +1862,16 @@
         <v>29.24229235587904</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>29.02949357860009</v>
+        <v>69.8857564541739</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.99379776475309</v>
+        <v>22.47576017313377</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>8.84</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>13.15379776475309</v>
+        <v>13.63576017313377</v>
       </c>
     </row>
     <row r="45">
@@ -1896,16 +1896,16 @@
         <v>26.79398253243592</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>27.88902239122681</v>
+        <v>67.1401800827512</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.32424373411878</v>
+        <v>21.78727146013352</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>12.45424373411878</v>
+        <v>12.91727146013352</v>
       </c>
     </row>
     <row r="46">
@@ -1930,16 +1930,16 @@
         <v>37.34211540214511</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>36.13617804141209</v>
+        <v>86.99442623582196</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.72573750286871</v>
+        <v>26.32568869910147</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>9.08</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>16.64573750286871</v>
+        <v>17.24568869910146</v>
       </c>
     </row>
     <row r="47">
@@ -1964,16 +1964,16 @@
         <v>29.53035511211866</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>32.03759727780775</v>
+        <v>77.12748121738848</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.54103948317983</v>
+        <v>23.07294395822467</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>10.5</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>12.04103948317983</v>
+        <v>12.57294395822467</v>
       </c>
     </row>
     <row r="48">
@@ -1998,16 +1998,16 @@
         <v>24.41325895330124</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>31.84847332693522</v>
+        <v>76.67218321728583</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.65453964374968</v>
+        <v>21.18330418682849</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>10.23</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>10.42453964374968</v>
+        <v>10.95330418682849</v>
       </c>
     </row>
     <row r="49">
@@ -2032,16 +2032,16 @@
         <v>22.46567685563094</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>32.91721404260419</v>
+        <v>79.24507527155717</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.12726302945856</v>
+        <v>20.67377134915075</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>10.24</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>9.887263029458561</v>
+        <v>10.43377134915075</v>
       </c>
     </row>
     <row r="50">
@@ -2066,16 +2066,16 @@
         <v>22.51248721679747</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>31.82968366715531</v>
+        <v>76.62694889090395</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.00397246847833</v>
+        <v>18.5324250560745</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>10.27</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>7.733972468478335</v>
+        <v>8.262425056074502</v>
       </c>
     </row>
     <row r="51">
@@ -2100,16 +2100,16 @@
         <v>21.4038225980015</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>32.77722589053965</v>
+        <v>78.90806705351288</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.84570692315609</v>
+        <v>17.3898910883903</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>10.65</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>6.195706923156086</v>
+        <v>6.739891088390296</v>
       </c>
     </row>
     <row r="52">
@@ -2134,16 +2134,16 @@
         <v>20.13948547945324</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>29.7416283438965</v>
+        <v>71.60015345649514</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.43450295471342</v>
+        <v>13.92828858645295</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>2.614502954713416</v>
+        <v>3.108288586452947</v>
       </c>
     </row>
     <row r="53">
@@ -2168,16 +2168,16 @@
         <v>19.47976134871442</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>24.28051926904962</v>
+        <v>58.45305057159415</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.96879019331329</v>
+        <v>12.37190771625457</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1.148790193313294</v>
+        <v>1.551907716254567</v>
       </c>
     </row>
     <row r="54">
@@ -2202,16 +2202,16 @@
         <v>19.28624202847321</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>28.94173773377847</v>
+        <v>69.67449256897976</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.54514104474548</v>
+        <v>14.02564648598325</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>10.91</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2.635141044745483</v>
+        <v>3.115646485983246</v>
       </c>
     </row>
     <row r="55">
@@ -2236,16 +2236,16 @@
         <v>17.9967607277201</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>29.62907898039576</v>
+        <v>71.32920152323499</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.8655586472601</v>
+        <v>14.3574756772568</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>10.89</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>2.975558647260101</v>
+        <v>3.467475677256797</v>
       </c>
     </row>
     <row r="56">
@@ -2270,16 +2270,16 @@
         <v>17.06287476563301</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>24.88888544218021</v>
+        <v>59.91763451603141</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.505589972537</v>
+        <v>12.91880789992334</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>11.08</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.425589972536995</v>
+        <v>1.838807899923335</v>
       </c>
     </row>
     <row r="57">
@@ -2304,16 +2304,16 @@
         <v>17.5257728321209</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>25.57528082411689</v>
+        <v>61.57006639064937</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.49128590680891</v>
+        <v>13.91589971922797</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>2.281285906808913</v>
+        <v>2.705899719227965</v>
       </c>
     </row>
     <row r="58">
@@ -2338,16 +2338,16 @@
         <v>18.15076082045445</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>28.68511555467585</v>
+        <v>69.05669897706102</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13.95182212684851</v>
+        <v>14.42806699622514</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>11.47</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>2.481822126848513</v>
+        <v>2.958066996225135</v>
       </c>
     </row>
     <row r="59">
@@ -2372,16 +2372,16 @@
         <v>16.96450885142118</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>29.1213695340774</v>
+        <v>70.10693911556264</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.46713598338557</v>
+        <v>13.95062376308058</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>11.97</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1.497135983385574</v>
+        <v>1.980623763080583</v>
       </c>
     </row>
     <row r="60">
@@ -2406,16 +2406,16 @@
         <v>20.8800453075799</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>30.83015344394131</v>
+        <v>74.22067454240432</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.40136179791846</v>
+        <v>14.91321967667738</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>12.23</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>2.171361797918458</v>
+        <v>2.683219676677382</v>
       </c>
     </row>
     <row r="61">
@@ -2440,16 +2440,16 @@
         <v>20.56677422997123</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>32.46817526492672</v>
+        <v>78.16405694203382</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.75379851354422</v>
+        <v>15.2928516631984</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>2.873798513544216</v>
+        <v>3.412851663198401</v>
       </c>
     </row>
     <row r="62">
@@ -2474,16 +2474,16 @@
         <v>20.79110483818339</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>29.1681710269803</v>
+        <v>70.21960927723281</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.68214450164943</v>
+        <v>16.16640930351929</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>11.74</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>3.942144501649427</v>
+        <v>4.426409303519288</v>
       </c>
     </row>
     <row r="63">
@@ -2508,16 +2508,16 @@
         <v>20.68319252933468</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>30.60011965797399</v>
+        <v>73.6668899888152</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.00624429861198</v>
+        <v>15.51428303952775</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>11.71</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>3.296244298611976</v>
+        <v>3.804283039527744</v>
       </c>
     </row>
     <row r="64">
@@ -2542,16 +2542,16 @@
         <v>21.13103894291727</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>31.26751594277168</v>
+        <v>75.27358333644474</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.55265246851133</v>
+        <v>15.07177166179167</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>12.3</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>2.252652468511329</v>
+        <v>2.771771661791671</v>
       </c>
     </row>
     <row r="65">
@@ -2576,16 +2576,16 @@
         <v>20.54104000335987</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>30.67869903650935</v>
+        <v>73.85606240051342</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.25229263839632</v>
+        <v>14.76163599409724</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>13.36</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.8922926383963254</v>
+        <v>1.401635994097241</v>
       </c>
     </row>
     <row r="66">
@@ -2610,16 +2610,16 @@
         <v>22.76473490916588</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.83309019395038</v>
+        <v>81.44996036477664</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.97400835054631</v>
+        <v>15.53572251165238</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>13.61</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.364008350546312</v>
+        <v>1.92572251165238</v>
       </c>
     </row>
     <row r="67">
@@ -2644,16 +2644,16 @@
         <v>22.41838069382961</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>31.63249894434386</v>
+        <v>76.15224534578101</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.33488263401729</v>
+        <v>14.86006146061433</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>14.96</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-0.6251173659827156</v>
+        <v>-0.09993853938567554</v>
       </c>
     </row>
     <row r="68">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -527,16 +527,16 @@
         <v>19.08913342354207</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>18.90112708537118</v>
+        <v>36.52560246505649</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.40712531436369</v>
+        <v>12.67486995776239</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.637125314363692</v>
+        <v>3.904869957762395</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +555,16 @@
         <v>19.68507051261704</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19.88567047394066</v>
+        <v>38.42818955724745</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12.95394445555641</v>
+        <v>13.23563568622964</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.23</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4.72394445555641</v>
+        <v>5.005635686229642</v>
       </c>
     </row>
     <row r="4">
@@ -583,16 +583,16 @@
         <v>19.05438378745552</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20.02793014488622</v>
+        <v>38.7031001572502</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.55794161324993</v>
+        <v>12.84164802876876</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>8.43</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4.127941613249925</v>
+        <v>4.411648028768765</v>
       </c>
     </row>
     <row r="5">
@@ -611,16 +611,16 @@
         <v>18.30785009429028</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20.10973436660478</v>
+        <v>38.86118324239953</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11.98418548554373</v>
+        <v>12.26905070191468</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3.594185485543726</v>
+        <v>3.879050701914684</v>
       </c>
     </row>
     <row r="6">
@@ -639,16 +639,16 @@
         <v>20.72341951426353</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>18.47054159493064</v>
+        <v>35.69351481335104</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11.90208978055023</v>
+        <v>12.16373494860707</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>8.25</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3.652089780550233</v>
+        <v>3.913734948607072</v>
       </c>
     </row>
     <row r="7">
@@ -667,16 +667,16 @@
         <v>21.64834897388687</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>17.00003082351878</v>
+        <v>32.85181698154589</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.63500414235953</v>
+        <v>11.87581873347102</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>8.01</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3.625004142359531</v>
+        <v>3.865818733471022</v>
       </c>
     </row>
     <row r="8">
@@ -695,16 +695,16 @@
         <v>21.26612311808534</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>15.95202892333951</v>
+        <v>30.82659908762471</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.79204597651331</v>
+        <v>12.01801505636099</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4.342045976513313</v>
+        <v>4.56801505636099</v>
       </c>
     </row>
     <row r="9">
@@ -723,16 +723,16 @@
         <v>21.42395840799424</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>16.21649125406785</v>
+        <v>31.33766098967614</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.70359429979313</v>
+        <v>12.93330963096822</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>7.43</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>5.273594299793126</v>
+        <v>5.503309630968221</v>
       </c>
     </row>
     <row r="10">
@@ -751,16 +751,16 @@
         <v>20.7929403151282</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>14.72599792715916</v>
+        <v>28.45734774223907</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.59804101819402</v>
+        <v>12.80664270876458</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5.388041018194024</v>
+        <v>5.596642708764576</v>
       </c>
     </row>
     <row r="11">
@@ -782,16 +782,16 @@
         <v>20.4659151974959</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>14.55683178712797</v>
+        <v>28.13044156604022</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.40232751409559</v>
+        <v>12.57244634425558</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>7.16</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>5.242327514095585</v>
+        <v>5.412446344255576</v>
       </c>
     </row>
     <row r="12">
@@ -813,16 +813,16 @@
         <v>19.66281621935698</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.71830855967719</v>
+        <v>28.44248837546238</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11.75521563127791</v>
+        <v>11.92722156434915</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>6.51</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>5.245215631277912</v>
+        <v>5.417221564349154</v>
       </c>
     </row>
     <row r="13">
@@ -844,16 +844,16 @@
         <v>19.2824148381953</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14.53553217887074</v>
+        <v>28.08928100347952</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10.85862352314305</v>
+        <v>11.02849343482321</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>6.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>4.258623523143051</v>
+        <v>4.428493434823212</v>
       </c>
     </row>
     <row r="14">
@@ -875,16 +875,16 @@
         <v>18.02677704153395</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.38203265338401</v>
+        <v>33.59001883139116</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11.04876473070709</v>
+        <v>11.25190035142719</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6.42</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.628764730707086</v>
+        <v>4.831900351427194</v>
       </c>
     </row>
     <row r="15">
@@ -906,16 +906,16 @@
         <v>21.47215262384002</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>18.61357754712712</v>
+        <v>35.96992554296213</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11.85222672876543</v>
+        <v>12.0697548340369</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>6.37</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.482226728765426</v>
+        <v>5.699754834036901</v>
       </c>
     </row>
     <row r="16">
@@ -937,16 +937,16 @@
         <v>27.55484768079231</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>24.74007101585946</v>
+        <v>47.80910655756287</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15.42799309448003</v>
+        <v>15.71711864053564</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>6.55</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8.877993094480029</v>
+        <v>9.167118640535644</v>
       </c>
     </row>
     <row r="17">
@@ -968,16 +968,16 @@
         <v>25.80624569777168</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>23.10963653630424</v>
+        <v>44.65836314545987</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.38591188355317</v>
+        <v>14.65598331052775</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>6.89</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7.495911883553169</v>
+        <v>7.765983310527754</v>
       </c>
     </row>
     <row r="18">
@@ -999,16 +999,16 @@
         <v>17.80772152671224</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>21.47549420997321</v>
+        <v>41.50045448142646</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12.44017755513624</v>
+        <v>12.69115153117262</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>6.18</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>6.260177555136238</v>
+        <v>6.51115153117262</v>
       </c>
     </row>
     <row r="19">
@@ -1030,16 +1030,16 @@
         <v>18.51648656260129</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>22.24750912308494</v>
+        <v>42.99233957833366</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.85146153526437</v>
+        <v>12.11145768561761</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5.67</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>6.181461535264368</v>
+        <v>6.441457685617607</v>
       </c>
     </row>
     <row r="20">
@@ -1061,16 +1061,16 @@
         <v>18.77070562720411</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20.1206346217037</v>
+        <v>38.88224750923997</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.49415694375081</v>
+        <v>10.7292973145386</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.48415694375081</v>
+        <v>4.719297314538604</v>
       </c>
     </row>
     <row r="21">
@@ -1092,16 +1092,16 @@
         <v>10.71995641599881</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>18.86023821936868</v>
+        <v>36.44658651758898</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9.284024974249888</v>
+        <v>9.50443568650768</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.274024974249889</v>
+        <v>3.49443568650768</v>
       </c>
     </row>
     <row r="22">
@@ -1123,16 +1123,16 @@
         <v>10.44565988107247</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>19.35260121856902</v>
+        <v>37.39805650644554</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9.062192324509873</v>
+        <v>9.288357051010799</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.842192324509873</v>
+        <v>3.068357051010799</v>
       </c>
     </row>
     <row r="23">
@@ -1154,16 +1154,16 @@
         <v>11.43707185377575</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>20.42494801806726</v>
+        <v>39.47031985488167</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10.21267841874183</v>
+        <v>10.45137515672191</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>6.39</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.822678418741831</v>
+        <v>4.061375156721913</v>
       </c>
     </row>
     <row r="24">
@@ -1188,16 +1188,16 @@
         <v>5.667647954234813</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>14.28188586349287</v>
+        <v>27.59912057863434</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8.616326798604472</v>
+        <v>8.773424047949756</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.096326798604473</v>
+        <v>2.253424047949757</v>
       </c>
     </row>
     <row r="25">
@@ -1222,16 +1222,16 @@
         <v>5.855223524312912</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>14.02372273335717</v>
+        <v>27.10023160657036</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8.088491704975896</v>
+        <v>8.242749223068996</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>6.16</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.928491704975896</v>
+        <v>2.082749223068996</v>
       </c>
     </row>
     <row r="26">
@@ -1256,16 +1256,16 @@
         <v>3.411173174992418</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.173954954856562</v>
+        <v>15.79581090058082</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7.954297300389227</v>
+        <v>8.044208804510866</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1.704297300389227</v>
+        <v>1.794208804510866</v>
       </c>
     </row>
     <row r="27">
@@ -1290,16 +1290,16 @@
         <v>3.082994003575836</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>8.076947802324213</v>
+        <v>15.6083488157189</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7.45466710619718</v>
+        <v>7.543511555381165</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.8746671061971796</v>
+        <v>0.9635115553811646</v>
       </c>
     </row>
     <row r="28">
@@ -1324,16 +1324,16 @@
         <v>2.817822060376203</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>7.010484367813883</v>
+        <v>13.54745481312837</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6.863814234801869</v>
+        <v>6.940927847197894</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>7.02</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1561857651981304</v>
+        <v>-0.07907215280210522</v>
       </c>
     </row>
     <row r="29">
@@ -1358,16 +1358,16 @@
         <v>3.072134256990506</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5.803349607968413</v>
+        <v>11.21471961904609</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6.746232056760884</v>
+        <v>6.810067482216238</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5237679432391156</v>
+        <v>-0.4599325177837619</v>
       </c>
     </row>
     <row r="30">
@@ -1392,16 +1392,16 @@
         <v>5.61092328242254</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.852766256265783</v>
+        <v>19.04004040775008</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7.715031420610661</v>
+        <v>7.823409438198516</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>7.17</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.5450314206106608</v>
+        <v>0.6534094381985165</v>
       </c>
     </row>
     <row r="31">
@@ -1426,16 +1426,16 @@
         <v>5.219966092926011</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.90866126854991</v>
+        <v>19.14805507741756</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7.699718959718519</v>
+        <v>7.80871180876252</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>7.26</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.4397189597185189</v>
+        <v>0.54871180876252</v>
       </c>
     </row>
     <row r="32">
@@ -1460,16 +1460,16 @@
         <v>5.475931372413843</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.91172833250014</v>
+        <v>19.15398204452778</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7.747143547188781</v>
+        <v>7.856170133185644</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.5371435471887809</v>
+        <v>0.6461701331856435</v>
       </c>
     </row>
     <row r="33">
@@ -1494,16 +1494,16 @@
         <v>11.26399397667822</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>15.43583057161696</v>
+        <v>29.82906832118022</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8.377080760773664</v>
+        <v>8.54687111950769</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>6.97</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.407080760773664</v>
+        <v>1.576871119507691</v>
       </c>
     </row>
     <row r="34">
@@ -1528,16 +1528,16 @@
         <v>9.783457615293401</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>15.74054408396551</v>
+        <v>30.4179138734853</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8.042415380477056</v>
+        <v>8.215557513275504</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>7.09</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.9524153804770563</v>
+        <v>1.125557513275504</v>
       </c>
     </row>
     <row r="35">
@@ -1562,16 +1562,16 @@
         <v>9.448934422190694</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>15.42412123683857</v>
+        <v>29.80644054320095</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7.626047296624068</v>
+        <v>7.795708855541113</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.176047296624068</v>
+        <v>0.3457088555411127</v>
       </c>
     </row>
     <row r="36">
@@ -1596,16 +1596,16 @@
         <v>14.38422404715066</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>23.13814363877954</v>
+        <v>44.71345187576364</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9.062444258774672</v>
+        <v>9.31695817628888</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>8.32</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.7424442587746718</v>
+        <v>0.9969581762888797</v>
       </c>
     </row>
     <row r="37">
@@ -1630,16 +1630,16 @@
         <v>13.59417234239063</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>22.65804936263514</v>
+        <v>43.78569065829785</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.666354739957981</v>
+        <v>9.915587737926296</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>8.35</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.316354739957982</v>
+        <v>1.565587737926297</v>
       </c>
     </row>
     <row r="38">
@@ -1664,16 +1664,16 @@
         <v>17.28644177708432</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>29.66712616950256</v>
+        <v>57.33042542138138</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.82223083559953</v>
+        <v>11.14856196313792</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>2.452230835599527</v>
+        <v>2.778561963137925</v>
       </c>
     </row>
     <row r="39">
@@ -1698,16 +1698,16 @@
         <v>32.38646722938399</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>64.58611554951874</v>
+        <v>124.8098470884176</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.45901709606967</v>
+        <v>23.16944856119304</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>9.42</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>13.03901709606967</v>
+        <v>13.74944856119304</v>
       </c>
     </row>
     <row r="40">
@@ -1732,10 +1732,10 @@
         <v>22.79637161894582</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>65.59731230812231</v>
+        <v>126.7639406539433</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.81263705478015</v>
+        <v>21.53419143678171</v>
       </c>
     </row>
     <row r="41">
@@ -1760,16 +1760,16 @@
         <v>24.3848718417819</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.63432613589559</v>
+        <v>124.9030119406856</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.09589311227112</v>
+        <v>23.80685488204624</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>11.36</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.73589311227112</v>
+        <v>12.44685488204624</v>
       </c>
     </row>
     <row r="42">
@@ -1794,16 +1794,16 @@
         <v>27.38071406266658</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>70.93537868382424</v>
+        <v>137.0795207508507</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.9172230696793</v>
+        <v>24.69749487544833</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>13.5972230696793</v>
+        <v>14.37749487544833</v>
       </c>
     </row>
     <row r="43">
@@ -1828,16 +1828,16 @@
         <v>28.49559475949014</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>73.04987534875264</v>
+        <v>141.1656931916804</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.86462048220223</v>
+        <v>23.66815123381252</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>9.23</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>13.63462048220223</v>
+        <v>14.43815123381252</v>
       </c>
     </row>
     <row r="44">
@@ -1862,16 +1862,16 @@
         <v>29.24229235587904</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>69.8857564541739</v>
+        <v>135.0511716410049</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.47576017313377</v>
+        <v>23.24448639124682</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>8.84</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>13.63576017313377</v>
+        <v>14.40448639124682</v>
       </c>
     </row>
     <row r="45">
@@ -1896,16 +1896,16 @@
         <v>26.79398253243592</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>67.1401800827512</v>
+        <v>129.7454652338112</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.78727146013352</v>
+        <v>22.52579701007567</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>12.91727146013352</v>
+        <v>13.65579701007568</v>
       </c>
     </row>
     <row r="46">
@@ -1930,16 +1930,16 @@
         <v>37.34211540214511</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>86.99442623582196</v>
+        <v>168.1129286636354</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.32568869910147</v>
+        <v>27.28260609787113</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>9.08</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>17.24568869910146</v>
+        <v>18.20260609787113</v>
       </c>
     </row>
     <row r="47">
@@ -1964,16 +1964,16 @@
         <v>29.53035511211866</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>77.12748121738848</v>
+        <v>149.0454884173442</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.07294395822467</v>
+        <v>23.92132737649255</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>10.5</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>12.57294395822467</v>
+        <v>13.42132737649255</v>
       </c>
     </row>
     <row r="48">
@@ -1998,16 +1998,16 @@
         <v>24.41325895330124</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>76.67218321728583</v>
+        <v>148.1656449201934</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.18330418682849</v>
+        <v>22.02667943851863</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>10.23</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>10.95330418682849</v>
+        <v>11.79667943851863</v>
       </c>
     </row>
     <row r="49">
@@ -2032,16 +2032,16 @@
         <v>22.46567685563094</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>79.24507527155717</v>
+        <v>153.1376464275825</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.67377134915075</v>
+        <v>21.54544778378352</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>10.24</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>10.43377134915075</v>
+        <v>11.30544778378352</v>
       </c>
     </row>
     <row r="50">
@@ -2066,16 +2066,16 @@
         <v>22.51248721679747</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>76.62694889090395</v>
+        <v>71.4776179254352</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.5324250560745</v>
+        <v>18.4716807838628</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>10.27</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>8.262425056074502</v>
+        <v>8.201680783862805</v>
       </c>
     </row>
     <row r="51">
@@ -2100,16 +2100,16 @@
         <v>21.4038225980015</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>78.90806705351288</v>
+        <v>73.6054449475168</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.3898910883903</v>
+        <v>17.32733851159878</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>10.65</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>6.739891088390296</v>
+        <v>6.677338511598782</v>
       </c>
     </row>
     <row r="52">
@@ -2134,16 +2134,16 @@
         <v>20.13948547945324</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>71.60015345649514</v>
+        <v>66.78862314421866</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.92828858645295</v>
+        <v>13.87152919207652</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>3.108288586452947</v>
+        <v>3.051529192076524</v>
       </c>
     </row>
     <row r="53">
@@ -2168,16 +2168,16 @@
         <v>19.47976134871442</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>58.45305057159415</v>
+        <v>54.52500557318302</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.37190771625457</v>
+        <v>12.32557038889236</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1.551907716254567</v>
+        <v>1.505570388892357</v>
       </c>
     </row>
     <row r="54">
@@ -2202,16 +2202,16 @@
         <v>19.28624202847321</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>69.67449256897976</v>
+        <v>64.99236666834432</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.02564648598325</v>
+        <v>13.97041361551038</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>10.91</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>3.115646485983246</v>
+        <v>3.060413615510383</v>
       </c>
     </row>
     <row r="55">
@@ -2236,16 +2236,16 @@
         <v>17.9967607277201</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>71.32920152323499</v>
+        <v>66.53587918087359</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.3574756772568</v>
+        <v>14.30093107386747</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>10.89</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>3.467475677256797</v>
+        <v>3.410931073867468</v>
       </c>
     </row>
     <row r="56">
@@ -2270,16 +2270,16 @@
         <v>17.06287476563301</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>59.91763451603141</v>
+        <v>55.89116947655409</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.91880789992334</v>
+        <v>12.87130955692517</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>11.08</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.838807899923335</v>
+        <v>1.791309556925173</v>
       </c>
     </row>
     <row r="57">
@@ -2304,16 +2304,16 @@
         <v>17.5257728321209</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>61.57006639064937</v>
+        <v>57.43255792919773</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.91589971922797</v>
+        <v>13.86709144841647</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>2.705899719227965</v>
+        <v>2.657091448416468</v>
       </c>
     </row>
     <row r="58">
@@ -2338,16 +2338,16 @@
         <v>18.15076082045445</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>69.05669897706102</v>
+        <v>64.41608880580253</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.42806699622514</v>
+        <v>14.3733238675815</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>11.47</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>2.958066996225135</v>
+        <v>2.903323867581502</v>
       </c>
     </row>
     <row r="59">
@@ -2372,16 +2372,16 @@
         <v>16.96450885142118</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>70.10693911556264</v>
+        <v>65.39575280699682</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.95062376308058</v>
+        <v>13.89504808043625</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>11.97</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1.980623763080583</v>
+        <v>1.925048080436246</v>
       </c>
     </row>
     <row r="60">
@@ -2406,16 +2406,16 @@
         <v>20.8800453075799</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>74.22067454240432</v>
+        <v>69.23304521315475</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.91321967667738</v>
+        <v>14.8543829237674</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>12.23</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>2.683219676677382</v>
+        <v>2.624382923767405</v>
       </c>
     </row>
     <row r="61">
@@ -2440,16 +2440,16 @@
         <v>20.56677422997123</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>78.16405694203382</v>
+        <v>72.91143231552915</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.2928516631984</v>
+        <v>15.23088888351344</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>3.412851663198401</v>
+        <v>3.350888883513443</v>
       </c>
     </row>
     <row r="62">
@@ -2474,16 +2474,16 @@
         <v>20.79110483818339</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>70.21960927723281</v>
+        <v>65.50085153380275</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.16640930351929</v>
+        <v>16.11074430416497</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>11.74</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>4.426409303519288</v>
+        <v>4.370744304164974</v>
       </c>
     </row>
     <row r="63">
@@ -2508,16 +2508,16 @@
         <v>20.68319252933468</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>73.6668899888152</v>
+        <v>68.71647498156682</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.51428303952775</v>
+        <v>15.45588528673661</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>11.71</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>3.804283039527744</v>
+        <v>3.745885286736611</v>
       </c>
     </row>
     <row r="64">
@@ -2542,16 +2542,16 @@
         <v>21.13103894291727</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>75.27358333644474</v>
+        <v>70.21519853623566</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.07177166179167</v>
+        <v>15.01210023936496</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>12.3</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>2.771771661791671</v>
+        <v>2.712100239364963</v>
       </c>
     </row>
     <row r="65">
@@ -2576,16 +2576,16 @@
         <v>20.54104000335987</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>73.85606240051342</v>
+        <v>68.89293500719891</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.76163599409724</v>
+        <v>14.70308827917611</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>13.36</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>1.401635994097241</v>
+        <v>1.343088279176106</v>
       </c>
     </row>
     <row r="66">
@@ -2610,16 +2610,16 @@
         <v>22.76473490916588</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>81.44996036477664</v>
+        <v>75.97652302826364</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.53572251165238</v>
+        <v>15.47115490670867</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>13.61</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.92572251165238</v>
+        <v>1.861154906708666</v>
       </c>
     </row>
     <row r="67">
@@ -2644,16 +2644,16 @@
         <v>22.41838069382961</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>76.15224534578101</v>
+        <v>71.03481445854452</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.86006146061433</v>
+        <v>14.79969349884931</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>14.96</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-0.09993853938567554</v>
+        <v>-0.1603065011506946</v>
       </c>
     </row>
     <row r="68">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -2066,16 +2066,16 @@
         <v>22.51248721679747</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>71.4776179254352</v>
+        <v>148.0782315603585</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.4716807838628</v>
+        <v>19.37530274124448</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>10.27</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>8.201680783862805</v>
+        <v>9.105302741244476</v>
       </c>
     </row>
     <row r="51">
@@ -2100,16 +2100,16 @@
         <v>21.4038225980015</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>73.6054449475168</v>
+        <v>152.4863927671979</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.32733851159878</v>
+        <v>18.25786051509935</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>10.65</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>6.677338511598782</v>
+        <v>7.607860515099349</v>
       </c>
     </row>
     <row r="52">
@@ -2134,16 +2134,16 @@
         <v>20.13948547945324</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>66.78862314421866</v>
+        <v>82.6249415966674</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.87152919207652</v>
+        <v>14.05834290542251</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>3.051529192076524</v>
+        <v>3.23834290542251</v>
       </c>
     </row>
     <row r="53">
@@ -2168,16 +2168,16 @@
         <v>19.47976134871442</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.52500557318302</v>
+        <v>67.45348517387698</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.32557038889236</v>
+        <v>12.47808167422522</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1.505570388892357</v>
+        <v>1.658081674225219</v>
       </c>
     </row>
     <row r="54">
@@ -2202,16 +2202,16 @@
         <v>19.28624202847321</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>64.99236666834432</v>
+        <v>80.40277291845889</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.97041361551038</v>
+        <v>14.15220303988944</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>10.91</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>3.060413615510383</v>
+        <v>3.242203039889441</v>
       </c>
     </row>
     <row r="55">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -527,16 +527,16 @@
         <v>19.08913342354207</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>36.52560246505649</v>
+        <v>7.851244304880336</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.67486995776239</v>
+        <v>12.23925949930118</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.904869957762395</v>
+        <v>3.469259499301183</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +555,16 @@
         <v>19.68507051261704</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>38.42818955724745</v>
+        <v>8.260208841095547</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13.23563568622964</v>
+        <v>12.77733465514106</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.23</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>5.005635686229642</v>
+        <v>4.547334655141062</v>
       </c>
     </row>
     <row r="4">
@@ -583,16 +583,16 @@
         <v>19.05438378745552</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>38.7031001572502</v>
+        <v>8.319301371730404</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.84164802876876</v>
+        <v>12.3800683677762</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>8.43</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4.411648028768765</v>
+        <v>3.950068367776199</v>
       </c>
     </row>
     <row r="5">
@@ -611,16 +611,16 @@
         <v>18.30785009429028</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>38.86118324239953</v>
+        <v>8.353281616769864</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12.26905070191468</v>
+        <v>11.80558571554623</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3.879050701914684</v>
+        <v>3.415585715546234</v>
       </c>
     </row>
     <row r="6">
@@ -639,16 +639,16 @@
         <v>20.72341951426353</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>35.69351481335104</v>
+        <v>7.672385559350714</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12.16373494860707</v>
+        <v>11.73804810697836</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>8.25</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3.913734948607072</v>
+        <v>3.488048106978356</v>
       </c>
     </row>
     <row r="7">
@@ -667,16 +667,16 @@
         <v>21.64834897388687</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>32.85181698154589</v>
+        <v>7.06155747131314</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.87581873347102</v>
+        <v>11.48402245659083</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>8.01</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3.865818733471022</v>
+        <v>3.474022456590832</v>
       </c>
     </row>
     <row r="8">
@@ -695,16 +695,16 @@
         <v>21.26612311808534</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30.82659908762471</v>
+        <v>6.626233222493365</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>12.01801505636099</v>
+        <v>11.65037186760847</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4.56801505636099</v>
+        <v>4.200371867608472</v>
       </c>
     </row>
     <row r="9">
@@ -723,16 +723,16 @@
         <v>21.42395840799424</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>31.33766098967614</v>
+        <v>6.736086902573284</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.93330963096822</v>
+        <v>12.55957143229307</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>7.43</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>5.503309630968221</v>
+        <v>5.129571432293069</v>
       </c>
     </row>
     <row r="10">
@@ -751,16 +751,16 @@
         <v>20.7929403151282</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>28.45734774223907</v>
+        <v>6.116958361111272</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.80664270876458</v>
+        <v>12.46725560875859</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5.596642708764576</v>
+        <v>5.257255608758594</v>
       </c>
     </row>
     <row r="11">
@@ -782,16 +782,16 @@
         <v>20.4659151974959</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>28.13044156604022</v>
+        <v>6.046689287341252</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.57244634425558</v>
+        <v>12.29566940986691</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>7.16</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>5.412446344255576</v>
+        <v>5.135669409866914</v>
       </c>
     </row>
     <row r="12">
@@ -813,16 +813,16 @@
         <v>19.66281621935698</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>28.44248837546238</v>
+        <v>6.113764313350083</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11.92722156434915</v>
+        <v>11.64737438454345</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>6.51</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>5.417221564349154</v>
+        <v>5.137374384543445</v>
       </c>
     </row>
     <row r="13">
@@ -844,16 +844,16 @@
         <v>19.2824148381953</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>28.08928100347952</v>
+        <v>6.037841749981683</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11.02849343482321</v>
+        <v>10.75212148143339</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>6.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>4.428493434823212</v>
+        <v>4.152121481433392</v>
       </c>
     </row>
     <row r="14">
@@ -875,16 +875,16 @@
         <v>18.02677704153395</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>33.59001883139116</v>
+        <v>7.220235293944389</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11.25190035142719</v>
+        <v>10.92140634135686</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6.42</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.831900351427194</v>
+        <v>4.50140634135686</v>
       </c>
     </row>
     <row r="15">
@@ -906,16 +906,16 @@
         <v>21.47215262384002</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>35.96992554296213</v>
+        <v>7.731800545557801</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12.0697548340369</v>
+        <v>11.71584479325076</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>6.37</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.699754834036901</v>
+        <v>5.34584479325076</v>
       </c>
     </row>
     <row r="16">
@@ -937,16 +937,16 @@
         <v>27.55484768079231</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>47.80910655756287</v>
+        <v>10.27665391530735</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15.71711864053564</v>
+        <v>15.24672225810425</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>6.55</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>9.167118640535644</v>
+        <v>8.696722258104248</v>
       </c>
     </row>
     <row r="17">
@@ -968,16 +968,16 @@
         <v>25.80624569777168</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>44.65836314545987</v>
+        <v>9.599395920888814</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.65598331052775</v>
+        <v>14.21658726275516</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>6.89</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7.765983310527754</v>
+        <v>7.326587262755161</v>
       </c>
     </row>
     <row r="18">
@@ -999,16 +999,16 @@
         <v>17.80772152671224</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>41.50045448142646</v>
+        <v>8.920597742609777</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12.69115153117262</v>
+        <v>12.28282631735969</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>6.18</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>6.51115153117262</v>
+        <v>6.102826317359694</v>
       </c>
     </row>
     <row r="19">
@@ -1030,16 +1030,16 @@
         <v>18.51648656260129</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.99233957833366</v>
+        <v>9.241281142201457</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12.11145768561761</v>
+        <v>11.68845373373323</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5.67</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>6.441457685617607</v>
+        <v>6.018453733733232</v>
       </c>
     </row>
     <row r="20">
@@ -1061,16 +1061,16 @@
         <v>18.77070562720411</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>38.88224750923997</v>
+        <v>8.357809419021057</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.7292973145386</v>
+        <v>10.34673278058047</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.719297314538604</v>
+        <v>4.336732780580475</v>
       </c>
     </row>
     <row r="21">
@@ -1092,16 +1092,16 @@
         <v>10.71995641599881</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>36.44658651758898</v>
+        <v>7.834259684075175</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9.50443568650768</v>
+        <v>9.145835752639334</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.49443568650768</v>
+        <v>3.135835752639334</v>
       </c>
     </row>
     <row r="22">
@@ -1123,16 +1123,16 @@
         <v>10.44565988107247</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>37.39805650644554</v>
+        <v>8.038779878873365</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9.288357051010799</v>
+        <v>8.920395552516448</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>3.068357051010799</v>
+        <v>2.700395552516448</v>
       </c>
     </row>
     <row r="23">
@@ -1154,16 +1154,16 @@
         <v>11.43707185377575</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>39.47031985488167</v>
+        <v>8.484216633220857</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10.45137515672191</v>
+        <v>10.06302454718287</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>6.39</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.061375156721913</v>
+        <v>3.673024547182872</v>
       </c>
     </row>
     <row r="24">
@@ -1188,16 +1188,16 @@
         <v>5.667647954234813</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>27.59912057863434</v>
+        <v>5.932480880226692</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8.773424047949756</v>
+        <v>8.517832735490186</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.253424047949757</v>
+        <v>1.997832735490187</v>
       </c>
     </row>
     <row r="25">
@@ -1222,16 +1222,16 @@
         <v>5.855223524312912</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>27.10023160657036</v>
+        <v>5.825243793461807</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8.242749223068996</v>
+        <v>7.991778046485789</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>6.16</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2.082749223068996</v>
+        <v>1.831778046485788</v>
       </c>
     </row>
     <row r="26">
@@ -1256,16 +1256,16 @@
         <v>3.411173174992418</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>15.79581090058082</v>
+        <v>3.395338119139771</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8.044208804510866</v>
+        <v>7.897926171050143</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1.794208804510866</v>
+        <v>1.647926171050143</v>
       </c>
     </row>
     <row r="27">
@@ -1290,16 +1290,16 @@
         <v>3.082994003575836</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>15.6083488157189</v>
+        <v>3.355042804981403</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7.543511555381165</v>
+        <v>7.398964980146275</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.9635115553811646</v>
+        <v>0.8189649801462746</v>
       </c>
     </row>
     <row r="28">
@@ -1324,16 +1324,16 @@
         <v>2.817822060376203</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>13.54745481312837</v>
+        <v>2.912049912084408</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6.940927847197894</v>
+        <v>6.815466901936662</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>7.02</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.07907215280210522</v>
+        <v>-0.2045330980633375</v>
       </c>
     </row>
     <row r="29">
@@ -1358,16 +1358,16 @@
         <v>3.072134256990506</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>11.21471961904609</v>
+        <v>2.410624263462897</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6.810067482216238</v>
+        <v>6.706209647393882</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4599325177837619</v>
+        <v>-0.5637903526061177</v>
       </c>
     </row>
     <row r="30">
@@ -1392,16 +1392,16 @@
         <v>5.61092328242254</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>19.04004040775008</v>
+        <v>4.092691118758473</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7.823409438198516</v>
+        <v>7.647082482300239</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>7.17</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.6534094381985165</v>
+        <v>0.4770824823002391</v>
       </c>
     </row>
     <row r="31">
@@ -1426,16 +1426,16 @@
         <v>5.219966092926011</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>19.14805507741756</v>
+        <v>4.115909067343487</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7.80871180876252</v>
+        <v>7.631384545223767</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>7.26</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.54871180876252</v>
+        <v>0.3713845452237674</v>
       </c>
     </row>
     <row r="32">
@@ -1460,16 +1460,16 @@
         <v>5.475931372413843</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>19.15398204452778</v>
+        <v>4.117183079642499</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7.856170133185644</v>
+        <v>7.678787980894248</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.6461701331856435</v>
+        <v>0.4687879808942483</v>
       </c>
     </row>
     <row r="33">
@@ -1494,16 +1494,16 @@
         <v>11.26399397667822</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>29.82906832118022</v>
+        <v>6.411812180253669</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8.54687111950769</v>
+        <v>8.270628595767322</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>6.97</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.576871119507691</v>
+        <v>1.300628595767322</v>
       </c>
     </row>
     <row r="34">
@@ -1528,16 +1528,16 @@
         <v>9.783457615293401</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>30.4179138734853</v>
+        <v>6.538385596624072</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8.215557513275504</v>
+        <v>7.93386177927357</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>7.09</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.125557513275504</v>
+        <v>0.8438617792735696</v>
       </c>
     </row>
     <row r="35">
@@ -1562,16 +1562,16 @@
         <v>9.448934422190694</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>29.80644054320095</v>
+        <v>6.406948298455638</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7.795708855541113</v>
+        <v>7.519675884255697</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.3457088555411127</v>
+        <v>0.06967588425569726</v>
       </c>
     </row>
     <row r="36">
@@ -1596,16 +1596,16 @@
         <v>14.38422404715066</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.71345187576364</v>
+        <v>9.61123734309326</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9.31695817628888</v>
+        <v>8.902873610914304</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>8.32</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.9969581762888797</v>
+        <v>0.5828736109143033</v>
       </c>
     </row>
     <row r="37">
@@ -1630,16 +1630,16 @@
         <v>13.59417234239063</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.78569065829785</v>
+        <v>9.411813391581832</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.915587737926296</v>
+        <v>9.510095029909841</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>8.35</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.565587737926297</v>
+        <v>1.160095029909842</v>
       </c>
     </row>
     <row r="38">
@@ -1664,16 +1664,16 @@
         <v>17.28644177708432</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.33042542138138</v>
+        <v>12.32327862399001</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.14856196313792</v>
+        <v>10.61763349983536</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>2.778561963137925</v>
+        <v>2.247633499835365</v>
       </c>
     </row>
     <row r="39">
@@ -1698,16 +1698,16 @@
         <v>32.38646722938399</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>124.8098470884176</v>
+        <v>26.82810234501654</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.16944856119304</v>
+        <v>22.01360330393863</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>9.42</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>13.74944856119304</v>
+        <v>12.59360330393863</v>
       </c>
     </row>
     <row r="40">
@@ -1732,10 +1732,10 @@
         <v>22.79637161894582</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>126.7639406539433</v>
+        <v>27.24813829082235</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.53419143678171</v>
+        <v>20.36024961236827</v>
       </c>
     </row>
     <row r="41">
@@ -1760,16 +1760,16 @@
         <v>24.3848718417819</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>124.9030119406856</v>
+        <v>26.84812829849628</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.80685488204624</v>
+        <v>22.65014683908102</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>11.36</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>12.44685488204624</v>
+        <v>11.29014683908102</v>
       </c>
     </row>
     <row r="42">
@@ -1794,16 +1794,16 @@
         <v>27.38071406266658</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>137.0795207508507</v>
+        <v>29.46549088794553</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.69749487544833</v>
+        <v>23.42802201234696</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>14.37749487544833</v>
+        <v>13.10802201234696</v>
       </c>
     </row>
     <row r="43">
@@ -1828,16 +1828,16 @@
         <v>28.49559475949014</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>141.1656931916804</v>
+        <v>30.34382104377292</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.66815123381252</v>
+        <v>22.36083694115864</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>9.23</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>14.43815123381252</v>
+        <v>13.13083694115864</v>
       </c>
     </row>
     <row r="44">
@@ -1862,16 +1862,16 @@
         <v>29.24229235587904</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>135.0511716410049</v>
+        <v>29.02949357860009</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.24448639124682</v>
+        <v>21.99379776475309</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>8.84</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>14.40448639124682</v>
+        <v>13.15379776475309</v>
       </c>
     </row>
     <row r="45">
@@ -1896,16 +1896,16 @@
         <v>26.79398253243592</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>129.7454652338112</v>
+        <v>27.88902239122681</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.52579701007567</v>
+        <v>21.32424373411878</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>13.65579701007568</v>
+        <v>12.45424373411878</v>
       </c>
     </row>
     <row r="46">
@@ -1930,16 +1930,16 @@
         <v>37.34211540214511</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>168.1129286636354</v>
+        <v>36.13617804141209</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.28260609787113</v>
+        <v>25.72573750286871</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>9.08</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>18.20260609787113</v>
+        <v>16.64573750286871</v>
       </c>
     </row>
     <row r="47">
@@ -1964,16 +1964,16 @@
         <v>29.53035511211866</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>149.0454884173442</v>
+        <v>32.03759727780775</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.92132737649255</v>
+        <v>22.54103948317983</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>10.5</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>13.42132737649255</v>
+        <v>12.04103948317983</v>
       </c>
     </row>
     <row r="48">
@@ -1998,16 +1998,16 @@
         <v>24.41325895330124</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>148.1656449201934</v>
+        <v>31.84847332693522</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.02667943851863</v>
+        <v>20.65453964374968</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>10.23</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.79667943851863</v>
+        <v>10.42453964374968</v>
       </c>
     </row>
     <row r="49">
@@ -2032,16 +2032,16 @@
         <v>22.46567685563094</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>153.1376464275825</v>
+        <v>32.91721404260419</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.54544778378352</v>
+        <v>20.12726302945856</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>10.24</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>11.30544778378352</v>
+        <v>9.887263029458561</v>
       </c>
     </row>
     <row r="50">
@@ -2066,16 +2066,16 @@
         <v>22.51248721679747</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>148.0782315603585</v>
+        <v>31.82968366715531</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.37530274124448</v>
+        <v>18.00397246847833</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>10.27</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>9.105302741244476</v>
+        <v>7.733972468478335</v>
       </c>
     </row>
     <row r="51">
@@ -2100,16 +2100,16 @@
         <v>21.4038225980015</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>152.4863927671979</v>
+        <v>32.77722589053965</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.25786051509935</v>
+        <v>16.84570692315609</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>10.65</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>7.607860515099349</v>
+        <v>6.195706923156086</v>
       </c>
     </row>
     <row r="52">
@@ -2134,16 +2134,16 @@
         <v>20.13948547945324</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>82.6249415966674</v>
+        <v>29.7416283438965</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.05834290542251</v>
+        <v>13.43450295471342</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>3.23834290542251</v>
+        <v>2.614502954713416</v>
       </c>
     </row>
     <row r="53">
@@ -2168,16 +2168,16 @@
         <v>19.47976134871442</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>67.45348517387698</v>
+        <v>24.28051926904962</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.47808167422522</v>
+        <v>11.96879019331329</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1.658081674225219</v>
+        <v>1.148790193313294</v>
       </c>
     </row>
     <row r="54">
@@ -2202,16 +2202,16 @@
         <v>19.28624202847321</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>80.40277291845889</v>
+        <v>28.94173773377847</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.15220303988944</v>
+        <v>13.54514104474548</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>10.91</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>3.242203039889441</v>
+        <v>2.635141044745483</v>
       </c>
     </row>
     <row r="55">
@@ -2236,16 +2236,16 @@
         <v>17.9967607277201</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>66.53587918087359</v>
+        <v>29.62907898039576</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.30093107386747</v>
+        <v>13.8655586472601</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>10.89</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>3.410931073867468</v>
+        <v>2.975558647260101</v>
       </c>
     </row>
     <row r="56">
@@ -2270,16 +2270,16 @@
         <v>17.06287476563301</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.89116947655409</v>
+        <v>24.88888544218021</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.87130955692517</v>
+        <v>12.505589972537</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>11.08</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.791309556925173</v>
+        <v>1.425589972536995</v>
       </c>
     </row>
     <row r="57">
@@ -2304,16 +2304,16 @@
         <v>17.5257728321209</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>57.43255792919773</v>
+        <v>25.57528082411689</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.86709144841647</v>
+        <v>13.49128590680891</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>2.657091448416468</v>
+        <v>2.281285906808913</v>
       </c>
     </row>
     <row r="58">
@@ -2338,16 +2338,16 @@
         <v>18.15076082045445</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>64.41608880580253</v>
+        <v>28.68511555467585</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.3733238675815</v>
+        <v>13.95182212684851</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>11.47</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>2.903323867581502</v>
+        <v>2.481822126848513</v>
       </c>
     </row>
     <row r="59">
@@ -2372,16 +2372,16 @@
         <v>16.96450885142118</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>65.39575280699682</v>
+        <v>29.1213695340774</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.89504808043625</v>
+        <v>13.46713598338557</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>11.97</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1.925048080436246</v>
+        <v>1.497135983385574</v>
       </c>
     </row>
     <row r="60">
@@ -2406,16 +2406,16 @@
         <v>20.8800453075799</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>69.23304521315475</v>
+        <v>30.83015344394131</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.8543829237674</v>
+        <v>14.40136179791846</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>12.23</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>2.624382923767405</v>
+        <v>2.171361797918458</v>
       </c>
     </row>
     <row r="61">
@@ -2440,16 +2440,16 @@
         <v>20.56677422997123</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>72.91143231552915</v>
+        <v>32.46817526492672</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.23088888351344</v>
+        <v>14.75379851354422</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>3.350888883513443</v>
+        <v>2.873798513544216</v>
       </c>
     </row>
     <row r="62">
@@ -2474,16 +2474,16 @@
         <v>20.79110483818339</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>65.50085153380275</v>
+        <v>29.1681710269803</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.11074430416497</v>
+        <v>15.68214450164943</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>11.74</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>4.370744304164974</v>
+        <v>3.942144501649427</v>
       </c>
     </row>
     <row r="63">
@@ -2508,16 +2508,16 @@
         <v>20.68319252933468</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>68.71647498156682</v>
+        <v>30.60011965797399</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.45588528673661</v>
+        <v>15.00624429861198</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>11.71</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>3.745885286736611</v>
+        <v>3.296244298611976</v>
       </c>
     </row>
     <row r="64">
@@ -2542,16 +2542,16 @@
         <v>21.13103894291727</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>70.21519853623566</v>
+        <v>31.26751594277168</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.01210023936496</v>
+        <v>14.55265246851133</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>12.3</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>2.712100239364963</v>
+        <v>2.252652468511329</v>
       </c>
     </row>
     <row r="65">
@@ -2576,16 +2576,16 @@
         <v>20.54104000335987</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>68.89293500719891</v>
+        <v>30.67869903650935</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.70308827917611</v>
+        <v>14.25229263839632</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>13.36</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>1.343088279176106</v>
+        <v>0.8922926383963254</v>
       </c>
     </row>
     <row r="66">
@@ -2610,16 +2610,16 @@
         <v>22.76473490916588</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>75.97652302826364</v>
+        <v>33.83309019395038</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.47115490670867</v>
+        <v>14.97400835054631</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>13.61</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.861154906708666</v>
+        <v>1.364008350546312</v>
       </c>
     </row>
     <row r="67">
@@ -2644,16 +2644,16 @@
         <v>22.41838069382961</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>71.03481445854452</v>
+        <v>31.63249894434386</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.79969349884931</v>
+        <v>14.33488263401729</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>14.96</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-0.1603065011506946</v>
+        <v>-0.6251173659827156</v>
       </c>
     </row>
     <row r="68">
@@ -2678,16 +2678,16 @@
         <v>24.56049944216917</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>76.75710374430747</v>
+        <v>31.88374803839209</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.30641030179403</v>
+        <v>15.77706011002511</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>15.14</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.166410301794027</v>
+        <v>0.6370601100251108</v>
       </c>
     </row>
     <row r="69">
@@ -2712,16 +2712,16 @@
         <v>27.5225196590493</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>84.5398532226926</v>
+        <v>35.116585278335</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.6367054465879</v>
+        <v>18.05368204767719</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>15.42</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>3.216705446587904</v>
+        <v>2.633682047677192</v>
       </c>
     </row>
     <row r="70">
@@ -2746,16 +2746,16 @@
         <v>25.81117654662714</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>86.86628970922069</v>
+        <v>36.08295205281462</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.64818925425947</v>
+        <v>17.04912174294473</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>15.88</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.768189254259473</v>
+        <v>1.169121742944727</v>
       </c>
     </row>
     <row r="71">
@@ -2780,16 +2780,16 @@
         <v>30.16952540833589</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>102.7734986420189</v>
+        <v>42.6905677244131</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.85829963524305</v>
+        <v>19.14952912982974</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>15.87</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.988299635243051</v>
+        <v>3.279529129829738</v>
       </c>
     </row>
     <row r="72">
@@ -2814,16 +2814,16 @@
         <v>22.14796142562243</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>114.3308816633844</v>
+        <v>47.49133104482092</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.1311061344782</v>
+        <v>19.34263091614233</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>16.84</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>3.291106134478198</v>
+        <v>2.50263091614233</v>
       </c>
     </row>
     <row r="73">
@@ -2848,16 +2848,16 @@
         <v>17.46840287343869</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>99.28772054985896</v>
+        <v>41.24262785974076</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.05434103174768</v>
+        <v>16.36960995997031</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>16.17</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.8843410317476774</v>
+        <v>0.1996099599703065</v>
       </c>
     </row>
     <row r="74">
@@ -2882,16 +2882,16 @@
         <v>19.41566696816943</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>118.826351702471</v>
+        <v>49.35868177913012</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.65080348545137</v>
+        <v>16.831325561031</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>2.270803485451369</v>
+        <v>1.451325561031004</v>
       </c>
     </row>
     <row r="75">
@@ -2916,16 +2916,16 @@
         <v>18.3943410823337</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>108.7060266556194</v>
+        <v>45.15485075737434</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.11049445719776</v>
+        <v>15.36081067225093</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>16.6</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-0.4895055428022417</v>
+        <v>-1.239189327749072</v>
       </c>
     </row>
     <row r="76">
@@ -2950,16 +2950,16 @@
         <v>20.85254507407065</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>121.6244832152306</v>
+        <v>50.52098358286025</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.19689586503241</v>
+        <v>15.35812081525662</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>15.55</v>
       </c>
-      <c r="K76" s="3" t="n">
-        <v>0.6468958650324126</v>
+      <c r="K76" s="4" t="n">
+        <v>-0.1918791847433852</v>
       </c>
     </row>
     <row r="77">
@@ -2984,16 +2984,16 @@
         <v>22.5042318126109</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>101.6140942336422</v>
+        <v>42.20896854690343</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.32928020965052</v>
+        <v>15.62850545858401</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>15.22</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1.109280209650519</v>
+        <v>0.4085054585840133</v>
       </c>
     </row>
     <row r="78">
@@ -3018,16 +3018,16 @@
         <v>18.88663129780421</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>109.847831303558</v>
+        <v>45.62913925873848</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.6534233454286</v>
+        <v>15.89586518169642</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>15.79</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.863423345428604</v>
+        <v>0.1058651816964247</v>
       </c>
     </row>
     <row r="79">
@@ -3052,16 +3052,16 @@
         <v>18.23971186718758</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>97.10705478633119</v>
+        <v>40.33681205418513</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.21855499968541</v>
+        <v>15.54886274234733</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>15.41</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.8085549996854127</v>
+        <v>0.1388627423473263</v>
       </c>
     </row>
     <row r="80">
@@ -3086,16 +3086,16 @@
         <v>19.22417385644482</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>132.6309805761103</v>
+        <v>55.09291727395582</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.16161574815813</v>
+        <v>16.24693513128206</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>14.7</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>2.461615748158128</v>
+        <v>1.546935131282062</v>
       </c>
     </row>
     <row r="81">
@@ -3120,16 +3120,16 @@
         <v>11.41095129815538</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>133.4141152827802</v>
+        <v>55.41821966877728</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.41698395445769</v>
+        <v>16.49690250186826</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>3.316983954457688</v>
+        <v>2.396902501868263</v>
       </c>
     </row>
     <row r="82">
@@ -3154,16 +3154,16 @@
         <v>12.7520293128997</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>119.3211636384267</v>
+        <v>61.10151420347143</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.49856537603772</v>
+        <v>17.8117751391968</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>13.85</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>4.648565376037718</v>
+        <v>3.961775139196797</v>
       </c>
     </row>
     <row r="83">
@@ -3185,16 +3185,16 @@
         <v>13.71730908439518</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>119.5667526256273</v>
+        <v>61.22727445028835</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.82360512411116</v>
+        <v>19.09243309684751</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>14.95</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>4.873605124111158</v>
+        <v>4.142433096847512</v>
       </c>
     </row>
     <row r="84">
@@ -3219,16 +3219,16 @@
         <v>10.13451644820684</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>111.1210180252848</v>
+        <v>56.90241575040731</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.2958187361679</v>
+        <v>17.65622699937551</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>14.58</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>3.715818736167895</v>
+        <v>3.076226999375509</v>
       </c>
     </row>
     <row r="85">
@@ -3253,16 +3253,16 @@
         <v>10.03540137291876</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>112.0903650393519</v>
+        <v>57.39879517332002</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.17584496613211</v>
+        <v>17.53067384974711</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>3.825844966132115</v>
+        <v>3.180673849747107</v>
       </c>
     </row>
     <row r="86">
@@ -3287,16 +3287,16 @@
         <v>6.780199126557799</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>94.31581935820005</v>
+        <v>48.29687542764808</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.7531948993332</v>
+        <v>18.21033073391868</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>4.403194899333199</v>
+        <v>3.860330733918678</v>
       </c>
     </row>
     <row r="87">
@@ -3321,16 +3321,16 @@
         <v>7.012368278640311</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>84.05690567362392</v>
+        <v>43.04353108288635</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.09768133655067</v>
+        <v>17.61386555404088</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>14.63</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>3.467681336550667</v>
+        <v>2.983865554040884</v>
       </c>
     </row>
     <row r="88">
@@ -3355,16 +3355,16 @@
         <v>5.73871550358888</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>84.91657302202056</v>
+        <v>43.48374617211803</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.64996207344997</v>
+        <v>18.16119820693056</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>14.31</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>4.339962073449973</v>
+        <v>3.85119820693056</v>
       </c>
     </row>
     <row r="89">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,15 +500,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>GMKN EY%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PLZL EY%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>IRAO EY%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Portfolio EY%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>OFZ 10Y%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ERP Proxy%</t>
         </is>
@@ -529,13 +547,13 @@
       <c r="H2" s="2" t="n">
         <v>7.851244304880336</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>12.23925949930118</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>8.77</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>3.469259499301183</v>
       </c>
     </row>
@@ -557,13 +575,13 @@
       <c r="H3" s="2" t="n">
         <v>8.260208841095547</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>12.77733465514106</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>8.23</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>4.547334655141062</v>
       </c>
     </row>
@@ -585,13 +603,13 @@
       <c r="H4" s="2" t="n">
         <v>8.319301371730404</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>12.3800683677762</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>8.43</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>3.950068367776199</v>
       </c>
     </row>
@@ -613,13 +631,13 @@
       <c r="H5" s="2" t="n">
         <v>8.353281616769864</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>11.80558571554623</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>3.415585715546234</v>
       </c>
     </row>
@@ -641,13 +659,13 @@
       <c r="H6" s="2" t="n">
         <v>7.672385559350714</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>11.73804810697836</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>8.25</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>3.488048106978356</v>
       </c>
     </row>
@@ -669,13 +687,13 @@
       <c r="H7" s="2" t="n">
         <v>7.06155747131314</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>11.48402245659083</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>8.01</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>3.474022456590832</v>
       </c>
     </row>
@@ -697,13 +715,13 @@
       <c r="H8" s="2" t="n">
         <v>6.626233222493365</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>11.65037186760847</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>7.45</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>4.200371867608472</v>
       </c>
     </row>
@@ -725,13 +743,13 @@
       <c r="H9" s="2" t="n">
         <v>6.736086902573284</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>12.55957143229307</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>7.43</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>5.129571432293069</v>
       </c>
     </row>
@@ -753,13 +771,13 @@
       <c r="H10" s="2" t="n">
         <v>6.116958361111272</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>12.46725560875859</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>7.21</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>5.257255608758594</v>
       </c>
     </row>
@@ -784,13 +802,13 @@
       <c r="H11" s="2" t="n">
         <v>6.046689287341252</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>12.29566940986691</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>7.16</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>5.135669409866914</v>
       </c>
     </row>
@@ -815,13 +833,13 @@
       <c r="H12" s="2" t="n">
         <v>6.113764313350083</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>11.64737438454345</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>6.51</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>5.137374384543445</v>
       </c>
     </row>
@@ -846,13 +864,13 @@
       <c r="H13" s="2" t="n">
         <v>6.037841749981683</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>10.75212148143339</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>6.6</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="N13" s="3" t="n">
         <v>4.152121481433392</v>
       </c>
     </row>
@@ -877,13 +895,13 @@
       <c r="H14" s="2" t="n">
         <v>7.220235293944389</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>10.92140634135686</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>6.42</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="N14" s="3" t="n">
         <v>4.50140634135686</v>
       </c>
     </row>
@@ -908,13 +926,13 @@
       <c r="H15" s="2" t="n">
         <v>7.731800545557801</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>11.71584479325076</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>5.34584479325076</v>
       </c>
     </row>
@@ -939,13 +957,13 @@
       <c r="H16" s="2" t="n">
         <v>10.27665391530735</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>15.24672225810425</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>6.55</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="N16" s="3" t="n">
         <v>8.696722258104248</v>
       </c>
     </row>
@@ -970,13 +988,13 @@
       <c r="H17" s="2" t="n">
         <v>9.599395920888814</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>14.21658726275516</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>6.89</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="N17" s="3" t="n">
         <v>7.326587262755161</v>
       </c>
     </row>
@@ -1001,13 +1019,13 @@
       <c r="H18" s="2" t="n">
         <v>8.920597742609777</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>12.28282631735969</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>6.18</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="N18" s="3" t="n">
         <v>6.102826317359694</v>
       </c>
     </row>
@@ -1032,13 +1050,13 @@
       <c r="H19" s="2" t="n">
         <v>9.241281142201457</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>11.68845373373323</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="M19" s="2" t="n">
         <v>5.67</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>6.018453733733232</v>
       </c>
     </row>
@@ -1063,13 +1081,13 @@
       <c r="H20" s="2" t="n">
         <v>8.357809419021057</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>10.34673278058047</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>6.01</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="N20" s="3" t="n">
         <v>4.336732780580475</v>
       </c>
     </row>
@@ -1094,13 +1112,13 @@
       <c r="H21" s="2" t="n">
         <v>7.834259684075175</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>9.145835752639334</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>6.01</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="N21" s="3" t="n">
         <v>3.135835752639334</v>
       </c>
     </row>
@@ -1125,13 +1143,13 @@
       <c r="H22" s="2" t="n">
         <v>8.038779878873365</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>8.920395552516448</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>6.22</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="N22" s="3" t="n">
         <v>2.700395552516448</v>
       </c>
     </row>
@@ -1156,13 +1174,13 @@
       <c r="H23" s="2" t="n">
         <v>8.484216633220857</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>10.06302454718287</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="M23" s="2" t="n">
         <v>6.39</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="N23" s="3" t="n">
         <v>3.673024547182872</v>
       </c>
     </row>
@@ -1190,14 +1208,14 @@
       <c r="H24" s="2" t="n">
         <v>5.932480880226692</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>8.517832735490186</v>
-      </c>
-      <c r="J24" s="2" t="n">
+      <c r="L24" s="2" t="n">
+        <v>8.938674985534409</v>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>6.52</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>1.997832735490187</v>
+      <c r="N24" s="3" t="n">
+        <v>2.418674985534409</v>
       </c>
     </row>
     <row r="25">
@@ -1224,14 +1242,14 @@
       <c r="H25" s="2" t="n">
         <v>5.825243793461807</v>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>7.991778046485789</v>
-      </c>
-      <c r="J25" s="2" t="n">
+      <c r="L25" s="2" t="n">
+        <v>8.386119462220041</v>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>6.16</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>1.831778046485788</v>
+      <c r="N25" s="3" t="n">
+        <v>2.226119462220041</v>
       </c>
     </row>
     <row r="26">
@@ -1258,14 +1276,14 @@
       <c r="H26" s="2" t="n">
         <v>3.395338119139771</v>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>7.897926171050143</v>
-      </c>
-      <c r="J26" s="2" t="n">
+      <c r="L26" s="2" t="n">
+        <v>8.293137311786296</v>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>6.25</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>1.647926171050143</v>
+      <c r="N26" s="3" t="n">
+        <v>2.043137311786296</v>
       </c>
     </row>
     <row r="27">
@@ -1292,14 +1310,14 @@
       <c r="H27" s="2" t="n">
         <v>3.355042804981403</v>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>7.398964980146275</v>
-      </c>
-      <c r="J27" s="2" t="n">
+      <c r="L27" s="2" t="n">
+        <v>7.756506124230873</v>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>6.58</v>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>0.8189649801462746</v>
+      <c r="N27" s="3" t="n">
+        <v>1.176506124230873</v>
       </c>
     </row>
     <row r="28">
@@ -1326,14 +1344,14 @@
       <c r="H28" s="2" t="n">
         <v>2.912049912084408</v>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>6.815466901936662</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="L28" s="2" t="n">
+        <v>7.156698618220659</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>7.02</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>-0.2045330980633375</v>
+      <c r="N28" s="3" t="n">
+        <v>0.1366986182206595</v>
       </c>
     </row>
     <row r="29">
@@ -1360,14 +1378,14 @@
       <c r="H29" s="2" t="n">
         <v>2.410624263462897</v>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>6.706209647393882</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="L29" s="2" t="n">
+        <v>7.034886972750911</v>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>7.27</v>
       </c>
-      <c r="K29" s="4" t="n">
-        <v>-0.5637903526061177</v>
+      <c r="N29" s="4" t="n">
+        <v>-0.2351130272490884</v>
       </c>
     </row>
     <row r="30">
@@ -1394,14 +1412,14 @@
       <c r="H30" s="2" t="n">
         <v>4.092691118758473</v>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>7.647082482300239</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="L30" s="2" t="n">
+        <v>8.030205339848305</v>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>7.17</v>
       </c>
-      <c r="K30" s="3" t="n">
-        <v>0.4770824823002391</v>
+      <c r="N30" s="3" t="n">
+        <v>0.8602053398483047</v>
       </c>
     </row>
     <row r="31">
@@ -1428,14 +1446,14 @@
       <c r="H31" s="2" t="n">
         <v>4.115909067343487</v>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>7.631384545223767</v>
-      </c>
-      <c r="J31" s="2" t="n">
+      <c r="L31" s="2" t="n">
+        <v>8.004999761972888</v>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>7.26</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.3713845452237674</v>
+      <c r="N31" s="3" t="n">
+        <v>0.7449997619728883</v>
       </c>
     </row>
     <row r="32">
@@ -1462,14 +1480,14 @@
       <c r="H32" s="2" t="n">
         <v>4.117183079642499</v>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>7.678787980894248</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="L32" s="2" t="n">
+        <v>8.066267802383548</v>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>7.21</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>0.4687879808942483</v>
+      <c r="N32" s="3" t="n">
+        <v>0.8562678023835479</v>
       </c>
     </row>
     <row r="33">
@@ -1496,14 +1514,14 @@
       <c r="H33" s="2" t="n">
         <v>6.411812180253669</v>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>8.270628595767322</v>
-      </c>
-      <c r="J33" s="2" t="n">
+      <c r="L33" s="2" t="n">
+        <v>8.73300914599989</v>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>6.97</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>1.300628595767322</v>
+      <c r="N33" s="3" t="n">
+        <v>1.763009145999891</v>
       </c>
     </row>
     <row r="34">
@@ -1530,14 +1548,14 @@
       <c r="H34" s="2" t="n">
         <v>6.538385596624072</v>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>7.93386177927357</v>
-      </c>
-      <c r="J34" s="2" t="n">
+      <c r="L34" s="2" t="n">
+        <v>8.391540948462069</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>7.09</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>0.8438617792735696</v>
+      <c r="N34" s="3" t="n">
+        <v>1.301540948462069</v>
       </c>
     </row>
     <row r="35">
@@ -1564,14 +1582,14 @@
       <c r="H35" s="2" t="n">
         <v>6.406948298455638</v>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>7.519675884255697</v>
-      </c>
-      <c r="J35" s="2" t="n">
+      <c r="L35" s="2" t="n">
+        <v>7.987677599492896</v>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>7.45</v>
       </c>
-      <c r="K35" s="3" t="n">
-        <v>0.06967588425569726</v>
+      <c r="N35" s="3" t="n">
+        <v>0.5376775994928957</v>
       </c>
     </row>
     <row r="36">
@@ -1598,14 +1616,14 @@
       <c r="H36" s="2" t="n">
         <v>9.61123734309326</v>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>8.902873610914304</v>
-      </c>
-      <c r="J36" s="2" t="n">
+      <c r="L36" s="2" t="n">
+        <v>9.493294020186729</v>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>8.32</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>0.5828736109143033</v>
+      <c r="N36" s="3" t="n">
+        <v>1.173294020186729</v>
       </c>
     </row>
     <row r="37">
@@ -1632,14 +1650,14 @@
       <c r="H37" s="2" t="n">
         <v>9.411813391581832</v>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>9.510095029909841</v>
-      </c>
-      <c r="J37" s="2" t="n">
+      <c r="L37" s="2" t="n">
+        <v>10.20011866260336</v>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>8.35</v>
       </c>
-      <c r="K37" s="3" t="n">
-        <v>1.160095029909842</v>
+      <c r="N37" s="3" t="n">
+        <v>1.850118662603357</v>
       </c>
     </row>
     <row r="38">
@@ -1666,14 +1684,14 @@
       <c r="H38" s="2" t="n">
         <v>12.32327862399001</v>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>10.61763349983536</v>
-      </c>
-      <c r="J38" s="2" t="n">
+      <c r="L38" s="2" t="n">
+        <v>11.62464191689264</v>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>2.247633499835365</v>
+      <c r="N38" s="3" t="n">
+        <v>3.254641916892639</v>
       </c>
     </row>
     <row r="39">
@@ -1700,14 +1718,14 @@
       <c r="H39" s="2" t="n">
         <v>26.82810234501654</v>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>22.01360330393863</v>
-      </c>
-      <c r="J39" s="2" t="n">
+      <c r="L39" s="2" t="n">
+        <v>23.80718850579489</v>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>9.42</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>12.59360330393863</v>
+      <c r="N39" s="3" t="n">
+        <v>14.38718850579489</v>
       </c>
     </row>
     <row r="40">
@@ -1734,8 +1752,8 @@
       <c r="H40" s="2" t="n">
         <v>27.24813829082235</v>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>20.36024961236827</v>
+      <c r="L40" s="2" t="n">
+        <v>21.8023652263369</v>
       </c>
     </row>
     <row r="41">
@@ -1762,14 +1780,14 @@
       <c r="H41" s="2" t="n">
         <v>26.84812829849628</v>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>22.65014683908102</v>
-      </c>
-      <c r="J41" s="2" t="n">
+      <c r="L41" s="2" t="n">
+        <v>24.45105219013728</v>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>11.36</v>
       </c>
-      <c r="K41" s="3" t="n">
-        <v>11.29014683908102</v>
+      <c r="N41" s="3" t="n">
+        <v>13.09105219013728</v>
       </c>
     </row>
     <row r="42">
@@ -1796,14 +1814,14 @@
       <c r="H42" s="2" t="n">
         <v>29.46549088794553</v>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>23.42802201234696</v>
-      </c>
-      <c r="J42" s="2" t="n">
+      <c r="L42" s="2" t="n">
+        <v>25.61768329355147</v>
+      </c>
+      <c r="M42" s="2" t="n">
         <v>10.32</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>13.10802201234696</v>
+      <c r="N42" s="3" t="n">
+        <v>15.29768329355147</v>
       </c>
     </row>
     <row r="43">
@@ -1830,14 +1848,14 @@
       <c r="H43" s="2" t="n">
         <v>30.34382104377292</v>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>22.36083694115864</v>
-      </c>
-      <c r="J43" s="2" t="n">
+      <c r="L43" s="2" t="n">
+        <v>24.61169036493522</v>
+      </c>
+      <c r="M43" s="2" t="n">
         <v>9.23</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>13.13083694115864</v>
+      <c r="N43" s="3" t="n">
+        <v>15.38169036493522</v>
       </c>
     </row>
     <row r="44">
@@ -1864,14 +1882,14 @@
       <c r="H44" s="2" t="n">
         <v>29.02949357860009</v>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>21.99379776475309</v>
-      </c>
-      <c r="J44" s="2" t="n">
+      <c r="L44" s="2" t="n">
+        <v>23.67291201884037</v>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>8.84</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>13.15379776475309</v>
+      <c r="N44" s="3" t="n">
+        <v>14.83291201884037</v>
       </c>
     </row>
     <row r="45">
@@ -1898,14 +1916,14 @@
       <c r="H45" s="2" t="n">
         <v>27.88902239122681</v>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>21.32424373411878</v>
-      </c>
-      <c r="J45" s="2" t="n">
+      <c r="L45" s="2" t="n">
+        <v>22.82748908400286</v>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="K45" s="3" t="n">
-        <v>12.45424373411878</v>
+      <c r="N45" s="3" t="n">
+        <v>13.95748908400286</v>
       </c>
     </row>
     <row r="46">
@@ -1932,14 +1950,14 @@
       <c r="H46" s="2" t="n">
         <v>36.13617804141209</v>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>25.72573750286871</v>
-      </c>
-      <c r="J46" s="2" t="n">
+      <c r="L46" s="2" t="n">
+        <v>27.68488069100168</v>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>9.08</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>16.64573750286871</v>
+      <c r="N46" s="3" t="n">
+        <v>18.60488069100168</v>
       </c>
     </row>
     <row r="47">
@@ -1966,14 +1984,14 @@
       <c r="H47" s="2" t="n">
         <v>32.03759727780775</v>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>22.54103948317983</v>
-      </c>
-      <c r="J47" s="2" t="n">
+      <c r="L47" s="2" t="n">
+        <v>24.16528624611758</v>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="K47" s="3" t="n">
-        <v>12.04103948317983</v>
+      <c r="N47" s="3" t="n">
+        <v>13.66528624611758</v>
       </c>
     </row>
     <row r="48">
@@ -2000,14 +2018,14 @@
       <c r="H48" s="2" t="n">
         <v>31.84847332693522</v>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>20.65453964374968</v>
-      </c>
-      <c r="J48" s="2" t="n">
+      <c r="L48" s="2" t="n">
+        <v>22.24700552983313</v>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>10.23</v>
       </c>
-      <c r="K48" s="3" t="n">
-        <v>10.42453964374968</v>
+      <c r="N48" s="3" t="n">
+        <v>12.01700552983313</v>
       </c>
     </row>
     <row r="49">
@@ -2034,14 +2052,14 @@
       <c r="H49" s="2" t="n">
         <v>32.91721404260419</v>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>20.12726302945856</v>
-      </c>
-      <c r="J49" s="2" t="n">
+      <c r="L49" s="2" t="n">
+        <v>21.71059574074994</v>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>10.24</v>
       </c>
-      <c r="K49" s="3" t="n">
-        <v>9.887263029458561</v>
+      <c r="N49" s="3" t="n">
+        <v>11.47059574074994</v>
       </c>
     </row>
     <row r="50">
@@ -2068,14 +2086,14 @@
       <c r="H50" s="2" t="n">
         <v>31.82968366715531</v>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>18.00397246847833</v>
-      </c>
-      <c r="J50" s="2" t="n">
+      <c r="L50" s="2" t="n">
+        <v>19.25788828793466</v>
+      </c>
+      <c r="M50" s="2" t="n">
         <v>10.27</v>
       </c>
-      <c r="K50" s="3" t="n">
-        <v>7.733972468478335</v>
+      <c r="N50" s="3" t="n">
+        <v>8.987888287934663</v>
       </c>
     </row>
     <row r="51">
@@ -2102,14 +2120,14 @@
       <c r="H51" s="2" t="n">
         <v>32.77722589053965</v>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>16.84570692315609</v>
-      </c>
-      <c r="J51" s="2" t="n">
+      <c r="L51" s="2" t="n">
+        <v>18.06934316740785</v>
+      </c>
+      <c r="M51" s="2" t="n">
         <v>10.65</v>
       </c>
-      <c r="K51" s="3" t="n">
-        <v>6.195706923156086</v>
+      <c r="N51" s="3" t="n">
+        <v>7.419343167407854</v>
       </c>
     </row>
     <row r="52">
@@ -2136,14 +2154,14 @@
       <c r="H52" s="2" t="n">
         <v>29.7416283438965</v>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>13.43450295471342</v>
-      </c>
-      <c r="J52" s="2" t="n">
+      <c r="L52" s="2" t="n">
+        <v>14.49756661053585</v>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>10.82</v>
       </c>
-      <c r="K52" s="3" t="n">
-        <v>2.614502954713416</v>
+      <c r="N52" s="3" t="n">
+        <v>3.677566610535854</v>
       </c>
     </row>
     <row r="53">
@@ -2170,14 +2188,14 @@
       <c r="H53" s="2" t="n">
         <v>24.28051926904962</v>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>11.96879019331329</v>
-      </c>
-      <c r="J53" s="2" t="n">
+      <c r="L53" s="2" t="n">
+        <v>13.00408598904766</v>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>10.82</v>
       </c>
-      <c r="K53" s="3" t="n">
-        <v>1.148790193313294</v>
+      <c r="N53" s="3" t="n">
+        <v>2.184085989047661</v>
       </c>
     </row>
     <row r="54">
@@ -2204,14 +2222,14 @@
       <c r="H54" s="2" t="n">
         <v>28.94173773377847</v>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>13.54514104474548</v>
-      </c>
-      <c r="J54" s="2" t="n">
+      <c r="L54" s="2" t="n">
+        <v>14.32397975165265</v>
+      </c>
+      <c r="M54" s="2" t="n">
         <v>10.91</v>
       </c>
-      <c r="K54" s="3" t="n">
-        <v>2.635141044745483</v>
+      <c r="N54" s="3" t="n">
+        <v>3.413979751652652</v>
       </c>
     </row>
     <row r="55">
@@ -2238,14 +2256,14 @@
       <c r="H55" s="2" t="n">
         <v>29.62907898039576</v>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>13.8655586472601</v>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="L55" s="2" t="n">
+        <v>14.62553820993459</v>
+      </c>
+      <c r="M55" s="2" t="n">
         <v>10.89</v>
       </c>
-      <c r="K55" s="3" t="n">
-        <v>2.975558647260101</v>
+      <c r="N55" s="3" t="n">
+        <v>3.735538209934587</v>
       </c>
     </row>
     <row r="56">
@@ -2272,14 +2290,14 @@
       <c r="H56" s="2" t="n">
         <v>24.88888544218021</v>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>12.505589972537</v>
-      </c>
-      <c r="J56" s="2" t="n">
+      <c r="L56" s="2" t="n">
+        <v>13.1676235664403</v>
+      </c>
+      <c r="M56" s="2" t="n">
         <v>11.08</v>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>1.425589972536995</v>
+      <c r="N56" s="3" t="n">
+        <v>2.087623566440296</v>
       </c>
     </row>
     <row r="57">
@@ -2306,14 +2324,14 @@
       <c r="H57" s="2" t="n">
         <v>25.57528082411689</v>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>13.49128590680891</v>
-      </c>
-      <c r="J57" s="2" t="n">
+      <c r="L57" s="2" t="n">
+        <v>14.19728418693659</v>
+      </c>
+      <c r="M57" s="2" t="n">
         <v>11.21</v>
       </c>
-      <c r="K57" s="3" t="n">
-        <v>2.281285906808913</v>
+      <c r="N57" s="3" t="n">
+        <v>2.98728418693659</v>
       </c>
     </row>
     <row r="58">
@@ -2340,14 +2358,14 @@
       <c r="H58" s="2" t="n">
         <v>28.68511555467585</v>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>13.95182212684851</v>
-      </c>
-      <c r="J58" s="2" t="n">
+      <c r="L58" s="2" t="n">
+        <v>14.6902288687992</v>
+      </c>
+      <c r="M58" s="2" t="n">
         <v>11.47</v>
       </c>
-      <c r="K58" s="3" t="n">
-        <v>2.481822126848513</v>
+      <c r="N58" s="3" t="n">
+        <v>3.220228868799197</v>
       </c>
     </row>
     <row r="59">
@@ -2374,14 +2392,14 @@
       <c r="H59" s="2" t="n">
         <v>29.1213695340774</v>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>13.46713598338557</v>
-      </c>
-      <c r="J59" s="2" t="n">
+      <c r="L59" s="2" t="n">
+        <v>14.19115422418746</v>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>11.97</v>
       </c>
-      <c r="K59" s="3" t="n">
-        <v>1.497135983385574</v>
+      <c r="N59" s="3" t="n">
+        <v>2.221154224187455</v>
       </c>
     </row>
     <row r="60">
@@ -2408,14 +2426,14 @@
       <c r="H60" s="2" t="n">
         <v>30.83015344394131</v>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>14.40136179791846</v>
-      </c>
-      <c r="J60" s="2" t="n">
+      <c r="L60" s="2" t="n">
+        <v>15.14925741583195</v>
+      </c>
+      <c r="M60" s="2" t="n">
         <v>12.23</v>
       </c>
-      <c r="K60" s="3" t="n">
-        <v>2.171361797918458</v>
+      <c r="N60" s="3" t="n">
+        <v>2.919257415831947</v>
       </c>
     </row>
     <row r="61">
@@ -2442,14 +2460,14 @@
       <c r="H61" s="2" t="n">
         <v>32.46817526492672</v>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>14.75379851354422</v>
-      </c>
-      <c r="J61" s="2" t="n">
+      <c r="L61" s="2" t="n">
+        <v>15.51643697067477</v>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>11.88</v>
       </c>
-      <c r="K61" s="3" t="n">
-        <v>2.873798513544216</v>
+      <c r="N61" s="3" t="n">
+        <v>3.636436970674767</v>
       </c>
     </row>
     <row r="62">
@@ -2476,14 +2494,14 @@
       <c r="H62" s="2" t="n">
         <v>29.1681710269803</v>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>15.68214450164943</v>
-      </c>
-      <c r="J62" s="2" t="n">
+      <c r="L62" s="2" t="n">
+        <v>16.51230400785013</v>
+      </c>
+      <c r="M62" s="2" t="n">
         <v>11.74</v>
       </c>
-      <c r="K62" s="3" t="n">
-        <v>3.942144501649427</v>
+      <c r="N62" s="3" t="n">
+        <v>4.77230400785013</v>
       </c>
     </row>
     <row r="63">
@@ -2510,14 +2528,14 @@
       <c r="H63" s="2" t="n">
         <v>30.60011965797399</v>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>15.00624429861198</v>
-      </c>
-      <c r="J63" s="2" t="n">
+      <c r="L63" s="2" t="n">
+        <v>15.78722627095969</v>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>11.71</v>
       </c>
-      <c r="K63" s="3" t="n">
-        <v>3.296244298611976</v>
+      <c r="N63" s="3" t="n">
+        <v>4.077226270959688</v>
       </c>
     </row>
     <row r="64">
@@ -2544,14 +2562,14 @@
       <c r="H64" s="2" t="n">
         <v>31.26751594277168</v>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>14.55265246851133</v>
-      </c>
-      <c r="J64" s="2" t="n">
+      <c r="L64" s="2" t="n">
+        <v>15.28193413560802</v>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>12.3</v>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>2.252652468511329</v>
+      <c r="N64" s="3" t="n">
+        <v>2.98193413560802</v>
       </c>
     </row>
     <row r="65">
@@ -2578,14 +2596,14 @@
       <c r="H65" s="2" t="n">
         <v>30.67869903650935</v>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>14.25229263839632</v>
-      </c>
-      <c r="J65" s="2" t="n">
+      <c r="L65" s="2" t="n">
+        <v>14.94462416812489</v>
+      </c>
+      <c r="M65" s="2" t="n">
         <v>13.36</v>
       </c>
-      <c r="K65" s="3" t="n">
-        <v>0.8922926383963254</v>
+      <c r="N65" s="3" t="n">
+        <v>1.584624168124893</v>
       </c>
     </row>
     <row r="66">
@@ -2612,14 +2630,14 @@
       <c r="H66" s="2" t="n">
         <v>33.83309019395038</v>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>14.97400835054631</v>
-      </c>
-      <c r="J66" s="2" t="n">
+      <c r="L66" s="2" t="n">
+        <v>15.80186256318361</v>
+      </c>
+      <c r="M66" s="2" t="n">
         <v>13.61</v>
       </c>
-      <c r="K66" s="3" t="n">
-        <v>1.364008350546312</v>
+      <c r="N66" s="3" t="n">
+        <v>2.191862563183607</v>
       </c>
     </row>
     <row r="67">
@@ -2646,14 +2664,14 @@
       <c r="H67" s="2" t="n">
         <v>31.63249894434386</v>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>14.33488263401729</v>
-      </c>
-      <c r="J67" s="2" t="n">
+      <c r="L67" s="2" t="n">
+        <v>15.12937797764112</v>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>14.96</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v>-0.6251173659827156</v>
+      <c r="N67" s="3" t="n">
+        <v>0.1693779776411191</v>
       </c>
     </row>
     <row r="68">
@@ -2680,14 +2698,14 @@
       <c r="H68" s="2" t="n">
         <v>31.88374803839209</v>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>15.77706011002511</v>
-      </c>
-      <c r="J68" s="2" t="n">
+      <c r="L68" s="2" t="n">
+        <v>16.65566348243142</v>
+      </c>
+      <c r="M68" s="2" t="n">
         <v>15.14</v>
       </c>
-      <c r="K68" s="3" t="n">
-        <v>0.6370601100251108</v>
+      <c r="N68" s="3" t="n">
+        <v>1.515663482431417</v>
       </c>
     </row>
     <row r="69">
@@ -2714,14 +2732,14 @@
       <c r="H69" s="2" t="n">
         <v>35.116585278335</v>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>18.05368204767719</v>
-      </c>
-      <c r="J69" s="2" t="n">
+      <c r="L69" s="2" t="n">
+        <v>19.1871835963558</v>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>15.42</v>
       </c>
-      <c r="K69" s="3" t="n">
-        <v>2.633682047677192</v>
+      <c r="N69" s="3" t="n">
+        <v>3.767183596355801</v>
       </c>
     </row>
     <row r="70">
@@ -2748,14 +2766,14 @@
       <c r="H70" s="2" t="n">
         <v>36.08295205281462</v>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>17.04912174294473</v>
-      </c>
-      <c r="J70" s="2" t="n">
+      <c r="L70" s="2" t="n">
+        <v>18.1047016360371</v>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>15.88</v>
       </c>
-      <c r="K70" s="3" t="n">
-        <v>1.169121742944727</v>
+      <c r="N70" s="3" t="n">
+        <v>2.224701636037098</v>
       </c>
     </row>
     <row r="71">
@@ -2782,14 +2800,14 @@
       <c r="H71" s="2" t="n">
         <v>42.6905677244131</v>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>19.14952912982974</v>
-      </c>
-      <c r="J71" s="2" t="n">
+      <c r="L71" s="2" t="n">
+        <v>20.38565574963054</v>
+      </c>
+      <c r="M71" s="2" t="n">
         <v>15.87</v>
       </c>
-      <c r="K71" s="3" t="n">
-        <v>3.279529129829738</v>
+      <c r="N71" s="3" t="n">
+        <v>4.515655749630538</v>
       </c>
     </row>
     <row r="72">
@@ -2816,14 +2834,14 @@
       <c r="H72" s="2" t="n">
         <v>47.49133104482092</v>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>19.34263091614233</v>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="L72" s="2" t="n">
+        <v>20.44622786120727</v>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>16.84</v>
       </c>
-      <c r="K72" s="3" t="n">
-        <v>2.50263091614233</v>
+      <c r="N72" s="3" t="n">
+        <v>3.606227861207273</v>
       </c>
     </row>
     <row r="73">
@@ -2850,14 +2868,14 @@
       <c r="H73" s="2" t="n">
         <v>41.24262785974076</v>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>16.36960995997031</v>
-      </c>
-      <c r="J73" s="2" t="n">
+      <c r="L73" s="2" t="n">
+        <v>17.32042914233289</v>
+      </c>
+      <c r="M73" s="2" t="n">
         <v>16.17</v>
       </c>
-      <c r="K73" s="3" t="n">
-        <v>0.1996099599703065</v>
+      <c r="N73" s="3" t="n">
+        <v>1.150429142332893</v>
       </c>
     </row>
     <row r="74">
@@ -2884,14 +2902,14 @@
       <c r="H74" s="2" t="n">
         <v>49.35868177913012</v>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>16.831325561031</v>
-      </c>
-      <c r="J74" s="2" t="n">
+      <c r="L74" s="2" t="n">
+        <v>17.74287578259274</v>
+      </c>
+      <c r="M74" s="2" t="n">
         <v>15.38</v>
       </c>
-      <c r="K74" s="3" t="n">
-        <v>1.451325561031004</v>
+      <c r="N74" s="3" t="n">
+        <v>2.362875782592743</v>
       </c>
     </row>
     <row r="75">
@@ -2918,14 +2936,14 @@
       <c r="H75" s="2" t="n">
         <v>45.15485075737434</v>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>15.36081067225093</v>
-      </c>
-      <c r="J75" s="2" t="n">
+      <c r="L75" s="2" t="n">
+        <v>16.18594258684464</v>
+      </c>
+      <c r="M75" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="K75" s="4" t="n">
-        <v>-1.239189327749072</v>
+      <c r="N75" s="4" t="n">
+        <v>-0.4140574131553585</v>
       </c>
     </row>
     <row r="76">
@@ -2952,14 +2970,14 @@
       <c r="H76" s="2" t="n">
         <v>50.52098358286025</v>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>15.35812081525662</v>
-      </c>
-      <c r="J76" s="2" t="n">
+      <c r="L76" s="2" t="n">
+        <v>16.19543779931677</v>
+      </c>
+      <c r="M76" s="2" t="n">
         <v>15.55</v>
       </c>
-      <c r="K76" s="4" t="n">
-        <v>-0.1918791847433852</v>
+      <c r="N76" s="3" t="n">
+        <v>0.6454377993167668</v>
       </c>
     </row>
     <row r="77">
@@ -2986,14 +3004,14 @@
       <c r="H77" s="2" t="n">
         <v>42.20896854690343</v>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>15.62850545858401</v>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="L77" s="2" t="n">
+        <v>16.47747522551059</v>
+      </c>
+      <c r="M77" s="2" t="n">
         <v>15.22</v>
       </c>
-      <c r="K77" s="3" t="n">
-        <v>0.4085054585840133</v>
+      <c r="N77" s="3" t="n">
+        <v>1.257475225510591</v>
       </c>
     </row>
     <row r="78">
@@ -3020,14 +3038,14 @@
       <c r="H78" s="2" t="n">
         <v>45.62913925873848</v>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>15.89586518169642</v>
-      </c>
-      <c r="J78" s="2" t="n">
+      <c r="L78" s="2" t="n">
+        <v>16.7335064915842</v>
+      </c>
+      <c r="M78" s="2" t="n">
         <v>15.79</v>
       </c>
-      <c r="K78" s="3" t="n">
-        <v>0.1058651816964247</v>
+      <c r="N78" s="3" t="n">
+        <v>0.9435064915842055</v>
       </c>
     </row>
     <row r="79">
@@ -3054,14 +3072,14 @@
       <c r="H79" s="2" t="n">
         <v>40.33681205418513</v>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>15.54886274234733</v>
-      </c>
-      <c r="J79" s="2" t="n">
+      <c r="L79" s="2" t="n">
+        <v>16.35630462906671</v>
+      </c>
+      <c r="M79" s="2" t="n">
         <v>15.41</v>
       </c>
-      <c r="K79" s="3" t="n">
-        <v>0.1388627423473263</v>
+      <c r="N79" s="3" t="n">
+        <v>0.9463046290667059</v>
       </c>
     </row>
     <row r="80">
@@ -3088,14 +3106,14 @@
       <c r="H80" s="2" t="n">
         <v>55.09291727395582</v>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>16.24693513128206</v>
-      </c>
-      <c r="J80" s="2" t="n">
+      <c r="L80" s="2" t="n">
+        <v>17.06784698708819</v>
+      </c>
+      <c r="M80" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="K80" s="3" t="n">
-        <v>1.546935131282062</v>
+      <c r="N80" s="3" t="n">
+        <v>2.367846987088189</v>
       </c>
     </row>
     <row r="81">
@@ -3122,14 +3140,14 @@
       <c r="H81" s="2" t="n">
         <v>55.41821966877728</v>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>16.49690250186826</v>
-      </c>
-      <c r="J81" s="2" t="n">
+      <c r="L81" s="2" t="n">
+        <v>17.20290583707662</v>
+      </c>
+      <c r="M81" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="K81" s="3" t="n">
-        <v>2.396902501868263</v>
+      <c r="N81" s="3" t="n">
+        <v>3.102905837076625</v>
       </c>
     </row>
     <row r="82">
@@ -3156,14 +3174,14 @@
       <c r="H82" s="2" t="n">
         <v>61.10151420347143</v>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>17.8117751391968</v>
-      </c>
-      <c r="J82" s="2" t="n">
+      <c r="L82" s="2" t="n">
+        <v>18.57226003985735</v>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>13.85</v>
       </c>
-      <c r="K82" s="3" t="n">
-        <v>3.961775139196797</v>
+      <c r="N82" s="3" t="n">
+        <v>4.722260039857348</v>
       </c>
     </row>
     <row r="83">
@@ -3187,13 +3205,13 @@
       <c r="H83" s="2" t="n">
         <v>61.22727445028835</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>19.09243309684751</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="M83" s="2" t="n">
         <v>14.95</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="N83" s="3" t="n">
         <v>4.142433096847512</v>
       </c>
     </row>
@@ -3221,14 +3239,14 @@
       <c r="H84" s="2" t="n">
         <v>56.90241575040731</v>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>17.65622699937551</v>
-      </c>
-      <c r="J84" s="2" t="n">
+      <c r="L84" s="2" t="n">
+        <v>18.37650377435888</v>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>14.58</v>
       </c>
-      <c r="K84" s="3" t="n">
-        <v>3.076226999375509</v>
+      <c r="N84" s="3" t="n">
+        <v>3.796503774358877</v>
       </c>
     </row>
     <row r="85">
@@ -3255,14 +3273,14 @@
       <c r="H85" s="2" t="n">
         <v>57.39879517332002</v>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>17.53067384974711</v>
-      </c>
-      <c r="J85" s="2" t="n">
+      <c r="L85" s="2" t="n">
+        <v>18.2327390424991</v>
+      </c>
+      <c r="M85" s="2" t="n">
         <v>14.35</v>
       </c>
-      <c r="K85" s="3" t="n">
-        <v>3.180673849747107</v>
+      <c r="N85" s="3" t="n">
+        <v>3.882739042499102</v>
       </c>
     </row>
     <row r="86">
@@ -3289,14 +3307,14 @@
       <c r="H86" s="2" t="n">
         <v>48.29687542764808</v>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>18.21033073391868</v>
-      </c>
-      <c r="J86" s="2" t="n">
+      <c r="L86" s="2" t="n">
+        <v>18.87984161637031</v>
+      </c>
+      <c r="M86" s="2" t="n">
         <v>14.35</v>
       </c>
-      <c r="K86" s="3" t="n">
-        <v>3.860330733918678</v>
+      <c r="N86" s="3" t="n">
+        <v>4.529841616370311</v>
       </c>
     </row>
     <row r="87">
@@ -3323,14 +3341,14 @@
       <c r="H87" s="2" t="n">
         <v>43.04353108288635</v>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>17.61386555404088</v>
-      </c>
-      <c r="J87" s="2" t="n">
+      <c r="L87" s="2" t="n">
+        <v>18.26150048428976</v>
+      </c>
+      <c r="M87" s="2" t="n">
         <v>14.63</v>
       </c>
-      <c r="K87" s="3" t="n">
-        <v>2.983865554040884</v>
+      <c r="N87" s="3" t="n">
+        <v>3.631500484289761</v>
       </c>
     </row>
     <row r="88">
@@ -3357,14 +3375,14 @@
       <c r="H88" s="2" t="n">
         <v>43.48374617211803</v>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>18.16119820693056</v>
-      </c>
-      <c r="J88" s="2" t="n">
+      <c r="L88" s="2" t="n">
+        <v>18.82911092309233</v>
+      </c>
+      <c r="M88" s="2" t="n">
         <v>14.31</v>
       </c>
-      <c r="K88" s="3" t="n">
-        <v>3.85119820693056</v>
+      <c r="N88" s="3" t="n">
+        <v>4.519110923092329</v>
       </c>
     </row>
     <row r="89">
@@ -3391,14 +3409,14 @@
       <c r="H89" s="2" t="n">
         <v>40.98093033274804</v>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>18.23046146050133</v>
-      </c>
-      <c r="J89" s="2" t="n">
+      <c r="L89" s="2" t="n">
+        <v>18.90113536680946</v>
+      </c>
+      <c r="M89" s="2" t="n">
         <v>14.47</v>
       </c>
-      <c r="K89" s="3" t="n">
-        <v>3.760461460501327</v>
+      <c r="N89" s="3" t="n">
+        <v>4.431135366809459</v>
       </c>
     </row>
     <row r="90">
@@ -3429,13 +3447,19 @@
         <v>46.52046352872824</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.72232554050118</v>
-      </c>
-      <c r="J90" s="2" t="n">
+        <v>26.49871237873908</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>39.32133308968581</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>20.61738415199558</v>
+      </c>
+      <c r="M90" s="2" t="n">
         <v>14.58</v>
       </c>
-      <c r="K90" s="3" t="n">
-        <v>5.142325540501178</v>
+      <c r="N90" s="3" t="n">
+        <v>6.03738415199558</v>
       </c>
     </row>
     <row r="91">
@@ -3466,13 +3490,19 @@
         <v>49.7594094486424</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.97827885532184</v>
-      </c>
-      <c r="J91" s="2" t="n">
+        <v>26.07204872780737</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>48.03084582172159</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>21.97087092581626</v>
+      </c>
+      <c r="M91" s="2" t="n">
         <v>14.93</v>
       </c>
-      <c r="K91" s="3" t="n">
-        <v>6.04827885532184</v>
+      <c r="N91" s="3" t="n">
+        <v>7.040870925816265</v>
       </c>
     </row>
     <row r="92">
@@ -3503,13 +3533,19 @@
         <v>65.14432350675698</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.40205186534319</v>
-      </c>
-      <c r="J92" s="2" t="n">
+        <v>27.80178291578326</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>48.50649109102406</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>23.42362670536719</v>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>16.45</v>
       </c>
-      <c r="K92" s="3" t="n">
-        <v>5.952051865343186</v>
+      <c r="N92" s="3" t="n">
+        <v>6.973626705367192</v>
       </c>
     </row>
     <row r="93">
@@ -3519,34 +3555,40 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>31.65944859455749</v>
+        <v>32.38194255799483</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>12.37559509621946</v>
+        <v>13.18845970468064</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>26.93088909072161</v>
+        <v>27.6370884024635</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>28.17575444671709</v>
+        <v>27.74386139790303</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>3.486740869985585</v>
+        <v>4.595119269985524</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>7.116682169193054</v>
+        <v>7.37009864945477</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>60.42236054949741</v>
+        <v>65.45303327569097</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.16046679071513</v>
-      </c>
-      <c r="J93" s="2" t="n">
+        <v>28.5391676440424</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>49.61732955933127</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>25.86030780760359</v>
+      </c>
+      <c r="M93" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K93" s="3" t="n">
-        <v>9.16046679071513</v>
+      <c r="N93" s="3" t="n">
+        <v>10.86030780760359</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -895,14 +895,17 @@
       <c r="H14" s="2" t="n">
         <v>7.220235293944389</v>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>13.56063541263076</v>
+      </c>
       <c r="L14" s="2" t="n">
-        <v>10.92140634135686</v>
+        <v>10.95407451859611</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>6.42</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>4.50140634135686</v>
+        <v>4.534074518596114</v>
       </c>
     </row>
     <row r="15">
@@ -926,14 +929,17 @@
       <c r="H15" s="2" t="n">
         <v>7.731800545557801</v>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>15.07461104190411</v>
+      </c>
       <c r="L15" s="2" t="n">
-        <v>11.71584479325076</v>
+        <v>11.75741934708942</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>6.37</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5.34584479325076</v>
+        <v>5.387419347089417</v>
       </c>
     </row>
     <row r="16">
@@ -957,14 +963,17 @@
       <c r="H16" s="2" t="n">
         <v>10.27665391530735</v>
       </c>
+      <c r="K16" s="2" t="n">
+        <v>15.93667361342183</v>
+      </c>
       <c r="L16" s="2" t="n">
-        <v>15.24672225810425</v>
+        <v>15.25526242364247</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>6.55</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>8.696722258104248</v>
+        <v>8.705262423642473</v>
       </c>
     </row>
     <row r="17">
@@ -988,14 +997,17 @@
       <c r="H17" s="2" t="n">
         <v>9.599395920888814</v>
       </c>
+      <c r="K17" s="2" t="n">
+        <v>15.68965517241379</v>
+      </c>
       <c r="L17" s="2" t="n">
-        <v>14.21658726275516</v>
+        <v>14.23482078559786</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>6.89</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>7.326587262755161</v>
+        <v>7.344820785597856</v>
       </c>
     </row>
     <row r="18">
@@ -1019,14 +1031,17 @@
       <c r="H18" s="2" t="n">
         <v>8.920597742609777</v>
       </c>
+      <c r="K18" s="2" t="n">
+        <v>16.52608835819415</v>
+      </c>
       <c r="L18" s="2" t="n">
-        <v>12.28282631735969</v>
+        <v>12.33534909301844</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>6.18</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>6.102826317359694</v>
+        <v>6.155349093018442</v>
       </c>
     </row>
     <row r="19">
@@ -1050,14 +1065,17 @@
       <c r="H19" s="2" t="n">
         <v>9.241281142201457</v>
       </c>
+      <c r="K19" s="2" t="n">
+        <v>16.79444621642588</v>
+      </c>
       <c r="L19" s="2" t="n">
-        <v>11.68845373373323</v>
+        <v>11.75165532135684</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>5.67</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6.018453733733232</v>
+        <v>6.081655321356839</v>
       </c>
     </row>
     <row r="20">
@@ -1081,14 +1099,17 @@
       <c r="H20" s="2" t="n">
         <v>8.357809419021057</v>
       </c>
+      <c r="K20" s="2" t="n">
+        <v>14.08706566257102</v>
+      </c>
       <c r="L20" s="2" t="n">
-        <v>10.34673278058047</v>
+        <v>10.39303033726194</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4.336732780580475</v>
+        <v>4.383030337261941</v>
       </c>
     </row>
     <row r="21">
@@ -1112,14 +1133,17 @@
       <c r="H21" s="2" t="n">
         <v>7.834259684075175</v>
       </c>
+      <c r="K21" s="2" t="n">
+        <v>13.95379238372635</v>
+      </c>
       <c r="L21" s="2" t="n">
-        <v>9.145835752639334</v>
+        <v>9.205348275099984</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>6.01</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>3.135835752639334</v>
+        <v>3.195348275099985</v>
       </c>
     </row>
     <row r="22">
@@ -1143,14 +1167,17 @@
       <c r="H22" s="2" t="n">
         <v>8.038779878873365</v>
       </c>
+      <c r="K22" s="2" t="n">
+        <v>12.95319125727765</v>
+      </c>
       <c r="L22" s="2" t="n">
-        <v>8.920395552516448</v>
+        <v>8.970313191832707</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2.700395552516448</v>
+        <v>2.750313191832707</v>
       </c>
     </row>
     <row r="23">
@@ -1174,14 +1201,17 @@
       <c r="H23" s="2" t="n">
         <v>8.484216633220857</v>
       </c>
+      <c r="K23" s="2" t="n">
+        <v>14.30195184005902</v>
+      </c>
       <c r="L23" s="2" t="n">
-        <v>10.06302454718287</v>
+        <v>10.11549366766022</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>6.39</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.673024547182872</v>
+        <v>3.725493667660216</v>
       </c>
     </row>
     <row r="24">
@@ -1208,14 +1238,17 @@
       <c r="H24" s="2" t="n">
         <v>5.932480880226692</v>
       </c>
+      <c r="K24" s="2" t="n">
+        <v>13.85610601072678</v>
+      </c>
       <c r="L24" s="2" t="n">
-        <v>8.938674985534409</v>
+        <v>8.998078729493843</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2.418674985534409</v>
+        <v>2.478078729493843</v>
       </c>
     </row>
     <row r="25">
@@ -1242,14 +1275,17 @@
       <c r="H25" s="2" t="n">
         <v>5.825243793461807</v>
       </c>
+      <c r="K25" s="2" t="n">
+        <v>13.48225258439962</v>
+      </c>
       <c r="L25" s="2" t="n">
-        <v>8.386119462220041</v>
+        <v>8.447681970290256</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>6.16</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>2.226119462220041</v>
+        <v>2.287681970290256</v>
       </c>
     </row>
     <row r="26">
@@ -1276,14 +1312,17 @@
       <c r="H26" s="2" t="n">
         <v>3.395338119139771</v>
       </c>
+      <c r="K26" s="2" t="n">
+        <v>13.76961303557411</v>
+      </c>
       <c r="L26" s="2" t="n">
-        <v>8.293137311786296</v>
+        <v>8.359294449533481</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2.043137311786296</v>
+        <v>2.109294449533481</v>
       </c>
     </row>
     <row r="27">
@@ -1310,14 +1349,17 @@
       <c r="H27" s="2" t="n">
         <v>3.355042804981403</v>
       </c>
+      <c r="K27" s="2" t="n">
+        <v>14.11771745492148</v>
+      </c>
       <c r="L27" s="2" t="n">
-        <v>7.756506124230873</v>
+        <v>7.833351079904737</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.176506124230873</v>
+        <v>1.253351079904736</v>
       </c>
     </row>
     <row r="28">
@@ -1344,14 +1386,17 @@
       <c r="H28" s="2" t="n">
         <v>2.912049912084408</v>
       </c>
+      <c r="K28" s="2" t="n">
+        <v>14.12461087164751</v>
+      </c>
       <c r="L28" s="2" t="n">
-        <v>7.156698618220659</v>
+        <v>7.240872666278238</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>7.02</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.1366986182206595</v>
+        <v>0.2208726662782388</v>
       </c>
     </row>
     <row r="29">
@@ -1378,14 +1423,17 @@
       <c r="H29" s="2" t="n">
         <v>2.410624263462897</v>
       </c>
+      <c r="K29" s="2" t="n">
+        <v>14.63630999045441</v>
+      </c>
       <c r="L29" s="2" t="n">
-        <v>7.034886972750911</v>
+        <v>7.126713982495971</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2351130272490884</v>
+        <v>-0.1432860175040283</v>
       </c>
     </row>
     <row r="30">
@@ -1412,14 +1460,17 @@
       <c r="H30" s="2" t="n">
         <v>4.092691118758473</v>
       </c>
+      <c r="K30" s="2" t="n">
+        <v>14.25766898079602</v>
+      </c>
       <c r="L30" s="2" t="n">
-        <v>8.030205339848305</v>
+        <v>8.10543459141245</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>7.17</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8602053398483047</v>
+        <v>0.9354345914124504</v>
       </c>
     </row>
     <row r="31">
@@ -1446,14 +1497,17 @@
       <c r="H31" s="2" t="n">
         <v>4.115909067343487</v>
       </c>
+      <c r="K31" s="2" t="n">
+        <v>15.3126730037575</v>
+      </c>
       <c r="L31" s="2" t="n">
-        <v>8.004999761972888</v>
+        <v>8.093278204104607</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>7.26</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.7449997619728883</v>
+        <v>0.833278204104607</v>
       </c>
     </row>
     <row r="32">
@@ -1480,14 +1534,17 @@
       <c r="H32" s="2" t="n">
         <v>4.117183079642499</v>
       </c>
+      <c r="K32" s="2" t="n">
+        <v>16.5154864445969</v>
+      </c>
       <c r="L32" s="2" t="n">
-        <v>8.066267802383548</v>
+        <v>8.168336386224983</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>7.21</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>0.8562678023835479</v>
+        <v>0.9583363862249827</v>
       </c>
     </row>
     <row r="33">
@@ -1514,14 +1571,17 @@
       <c r="H33" s="2" t="n">
         <v>6.411812180253669</v>
       </c>
+      <c r="K33" s="2" t="n">
+        <v>18.08412451378081</v>
+      </c>
       <c r="L33" s="2" t="n">
-        <v>8.73300914599989</v>
+        <v>8.845972858189642</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>6.97</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.763009145999891</v>
+        <v>1.875972858189642</v>
       </c>
     </row>
     <row r="34">
@@ -1548,14 +1608,17 @@
       <c r="H34" s="2" t="n">
         <v>6.538385596624072</v>
       </c>
+      <c r="K34" s="2" t="n">
+        <v>17.95136833684709</v>
+      </c>
       <c r="L34" s="2" t="n">
-        <v>8.391540948462069</v>
+        <v>8.507025951823918</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>7.09</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.301540948462069</v>
+        <v>1.417025951823918</v>
       </c>
     </row>
     <row r="35">
@@ -1582,14 +1645,17 @@
       <c r="H35" s="2" t="n">
         <v>6.406948298455638</v>
       </c>
+      <c r="K35" s="2" t="n">
+        <v>17.40824171945295</v>
+      </c>
       <c r="L35" s="2" t="n">
-        <v>7.987677599492896</v>
+        <v>8.101480269234184</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>7.45</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.5376775994928957</v>
+        <v>0.6514802692341837</v>
       </c>
     </row>
     <row r="36">
@@ -1616,14 +1682,17 @@
       <c r="H36" s="2" t="n">
         <v>9.61123734309326</v>
       </c>
+      <c r="K36" s="2" t="n">
+        <v>21.62789047047023</v>
+      </c>
       <c r="L36" s="2" t="n">
-        <v>9.493294020186729</v>
+        <v>9.639882850185721</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>8.32</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.173294020186729</v>
+        <v>1.319882850185721</v>
       </c>
     </row>
     <row r="37">
@@ -1650,14 +1719,17 @@
       <c r="H37" s="2" t="n">
         <v>9.411813391581832</v>
       </c>
+      <c r="K37" s="2" t="n">
+        <v>21.78781501268145</v>
+      </c>
       <c r="L37" s="2" t="n">
-        <v>10.20011866260336</v>
+        <v>10.34010080847042</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>8.35</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.850118662603357</v>
+        <v>1.990100808470419</v>
       </c>
     </row>
     <row r="38">
@@ -1684,14 +1756,17 @@
       <c r="H38" s="2" t="n">
         <v>12.32327862399001</v>
       </c>
+      <c r="K38" s="2" t="n">
+        <v>24.13375309351952</v>
+      </c>
       <c r="L38" s="2" t="n">
-        <v>11.62464191689264</v>
+        <v>11.77575497444028</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>3.254641916892639</v>
+        <v>3.405754974440276</v>
       </c>
     </row>
     <row r="39">
@@ -1718,14 +1793,17 @@
       <c r="H39" s="2" t="n">
         <v>26.82810234501654</v>
       </c>
+      <c r="K39" s="2" t="n">
+        <v>36.47200569290124</v>
+      </c>
       <c r="L39" s="2" t="n">
-        <v>23.80718850579489</v>
+        <v>23.96018252922331</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>9.42</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.38718850579489</v>
+        <v>14.54018252922331</v>
       </c>
     </row>
     <row r="40">
@@ -1752,8 +1830,11 @@
       <c r="H40" s="2" t="n">
         <v>27.24813829082235</v>
       </c>
+      <c r="K40" s="2" t="n">
+        <v>34.51157684167761</v>
+      </c>
       <c r="L40" s="2" t="n">
-        <v>21.8023652263369</v>
+        <v>21.95589554508589</v>
       </c>
     </row>
     <row r="41">
@@ -1780,14 +1861,17 @@
       <c r="H41" s="2" t="n">
         <v>26.84812829849628</v>
       </c>
+      <c r="K41" s="2" t="n">
+        <v>34.8439720992748</v>
+      </c>
       <c r="L41" s="2" t="n">
-        <v>24.45105219013728</v>
+        <v>24.57660115058236</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>11.36</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>13.09105219013728</v>
+        <v>13.21660115058236</v>
       </c>
     </row>
     <row r="42">
@@ -1814,14 +1898,17 @@
       <c r="H42" s="2" t="n">
         <v>29.46549088794553</v>
       </c>
+      <c r="K42" s="2" t="n">
+        <v>29.76623502594694</v>
+      </c>
       <c r="L42" s="2" t="n">
-        <v>25.61768329355147</v>
+        <v>25.66779879159326</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>15.29768329355147</v>
+        <v>15.34779879159326</v>
       </c>
     </row>
     <row r="43">
@@ -1848,14 +1935,17 @@
       <c r="H43" s="2" t="n">
         <v>30.34382104377292</v>
       </c>
+      <c r="K43" s="2" t="n">
+        <v>28.24663744203974</v>
+      </c>
       <c r="L43" s="2" t="n">
-        <v>24.61169036493522</v>
+        <v>24.65560139579018</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>9.23</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.38169036493522</v>
+        <v>15.42560139579018</v>
       </c>
     </row>
     <row r="44">
@@ -1882,14 +1972,17 @@
       <c r="H44" s="2" t="n">
         <v>29.02949357860009</v>
       </c>
+      <c r="K44" s="2" t="n">
+        <v>29.09412393504248</v>
+      </c>
       <c r="L44" s="2" t="n">
-        <v>23.67291201884037</v>
+        <v>23.73840155656242</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>8.84</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>14.83291201884037</v>
+        <v>14.89840155656242</v>
       </c>
     </row>
     <row r="45">
@@ -1916,14 +2009,17 @@
       <c r="H45" s="2" t="n">
         <v>27.88902239122681</v>
       </c>
+      <c r="K45" s="2" t="n">
+        <v>29.30258650529356</v>
+      </c>
       <c r="L45" s="2" t="n">
-        <v>22.82748908400286</v>
+        <v>22.90570981091417</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>13.95748908400286</v>
+        <v>14.03570981091417</v>
       </c>
     </row>
     <row r="46">
@@ -1950,14 +2046,17 @@
       <c r="H46" s="2" t="n">
         <v>36.13617804141209</v>
       </c>
+      <c r="K46" s="2" t="n">
+        <v>36.41552562214182</v>
+      </c>
       <c r="L46" s="2" t="n">
-        <v>27.68488069100168</v>
+        <v>27.79034897178349</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>9.08</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>18.60488069100168</v>
+        <v>18.71034897178349</v>
       </c>
     </row>
     <row r="47">
@@ -1984,14 +2083,17 @@
       <c r="H47" s="2" t="n">
         <v>32.03759727780775</v>
       </c>
+      <c r="K47" s="2" t="n">
+        <v>30.46026641256228</v>
+      </c>
       <c r="L47" s="2" t="n">
-        <v>24.16528624611758</v>
+        <v>24.24133111347239</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>10.5</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>13.66528624611758</v>
+        <v>13.74133111347239</v>
       </c>
     </row>
     <row r="48">
@@ -2018,14 +2120,17 @@
       <c r="H48" s="2" t="n">
         <v>31.84847332693522</v>
       </c>
+      <c r="K48" s="2" t="n">
+        <v>28.61615536415951</v>
+      </c>
       <c r="L48" s="2" t="n">
-        <v>22.24700552983313</v>
+        <v>22.32394638453129</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>10.23</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.01700552983313</v>
+        <v>12.09394638453129</v>
       </c>
     </row>
     <row r="49">
@@ -2052,14 +2157,17 @@
       <c r="H49" s="2" t="n">
         <v>32.91721404260419</v>
       </c>
+      <c r="K49" s="2" t="n">
+        <v>27.7099138848114</v>
+      </c>
       <c r="L49" s="2" t="n">
-        <v>21.71059574074994</v>
+        <v>21.78306894009635</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>10.24</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>11.47059574074994</v>
+        <v>11.54306894009635</v>
       </c>
     </row>
     <row r="50">
@@ -2086,14 +2194,17 @@
       <c r="H50" s="2" t="n">
         <v>31.82968366715531</v>
       </c>
+      <c r="K50" s="2" t="n">
+        <v>26.88618055795122</v>
+      </c>
       <c r="L50" s="2" t="n">
-        <v>19.25788828793466</v>
+        <v>19.35003988467984</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>10.27</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>8.987888287934663</v>
+        <v>9.080039884679845</v>
       </c>
     </row>
     <row r="51">
@@ -2120,14 +2231,17 @@
       <c r="H51" s="2" t="n">
         <v>32.77722589053965</v>
       </c>
+      <c r="K51" s="2" t="n">
+        <v>27.4912473131645</v>
+      </c>
       <c r="L51" s="2" t="n">
-        <v>18.06934316740785</v>
+        <v>18.18316202498155</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>10.65</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>7.419343167407854</v>
+        <v>7.533162024981548</v>
       </c>
     </row>
     <row r="52">
@@ -2154,14 +2268,17 @@
       <c r="H52" s="2" t="n">
         <v>29.7416283438965</v>
       </c>
+      <c r="K52" s="2" t="n">
+        <v>25.38766604102357</v>
+      </c>
       <c r="L52" s="2" t="n">
-        <v>14.49756661053585</v>
+        <v>14.62912161861777</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3.677566610535854</v>
+        <v>3.809121618617773</v>
       </c>
     </row>
     <row r="53">
@@ -2188,14 +2305,17 @@
       <c r="H53" s="2" t="n">
         <v>24.28051926904962</v>
       </c>
+      <c r="K53" s="2" t="n">
+        <v>23.11088517985069</v>
+      </c>
       <c r="L53" s="2" t="n">
-        <v>13.00408598904766</v>
+        <v>13.12617854272133</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>10.82</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>2.184085989047661</v>
+        <v>2.30617854272133</v>
       </c>
     </row>
     <row r="54">
@@ -2222,14 +2342,17 @@
       <c r="H54" s="2" t="n">
         <v>28.94173773377847</v>
       </c>
+      <c r="K54" s="2" t="n">
+        <v>23.02320467066267</v>
+      </c>
       <c r="L54" s="2" t="n">
-        <v>14.32397975165265</v>
+        <v>14.42906847116635</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>10.91</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>3.413979751652652</v>
+        <v>3.519068471166349</v>
       </c>
     </row>
     <row r="55">
@@ -2256,14 +2379,17 @@
       <c r="H55" s="2" t="n">
         <v>29.62907898039576</v>
       </c>
+      <c r="K55" s="2" t="n">
+        <v>23.29980249739716</v>
+      </c>
       <c r="L55" s="2" t="n">
-        <v>14.62553820993459</v>
+        <v>14.73032539904391</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>10.89</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3.735538209934587</v>
+        <v>3.840325399043907</v>
       </c>
     </row>
     <row r="56">
@@ -2290,14 +2416,17 @@
       <c r="H56" s="2" t="n">
         <v>24.88888544218021</v>
       </c>
+      <c r="K56" s="2" t="n">
+        <v>22.60817273933237</v>
+      </c>
       <c r="L56" s="2" t="n">
-        <v>13.1676235664403</v>
+        <v>13.28166766040519</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>11.08</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>2.087623566440296</v>
+        <v>2.201667660405189</v>
       </c>
     </row>
     <row r="57">
@@ -2324,14 +2453,17 @@
       <c r="H57" s="2" t="n">
         <v>25.57528082411689</v>
       </c>
+      <c r="K57" s="2" t="n">
+        <v>22.43828785352871</v>
+      </c>
       <c r="L57" s="2" t="n">
-        <v>14.19728418693659</v>
+        <v>14.29683748402831</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>2.98728418693659</v>
+        <v>3.086837484028305</v>
       </c>
     </row>
     <row r="58">
@@ -2358,14 +2490,17 @@
       <c r="H58" s="2" t="n">
         <v>28.68511555467585</v>
       </c>
+      <c r="K58" s="2" t="n">
+        <v>21.91294180127952</v>
+      </c>
       <c r="L58" s="2" t="n">
-        <v>14.6902288687992</v>
+        <v>14.77748097005603</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>11.47</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3.220228868799197</v>
+        <v>3.307480970056025</v>
       </c>
     </row>
     <row r="59">
@@ -2392,14 +2527,17 @@
       <c r="H59" s="2" t="n">
         <v>29.1213695340774</v>
       </c>
+      <c r="K59" s="2" t="n">
+        <v>21.97437277934641</v>
+      </c>
       <c r="L59" s="2" t="n">
-        <v>14.19115422418746</v>
+        <v>14.28517736754469</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>11.97</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2.221154224187455</v>
+        <v>2.31517736754469</v>
       </c>
     </row>
     <row r="60">
@@ -2426,14 +2564,17 @@
       <c r="H60" s="2" t="n">
         <v>30.83015344394131</v>
       </c>
+      <c r="K60" s="2" t="n">
+        <v>21.50379677133542</v>
+      </c>
       <c r="L60" s="2" t="n">
-        <v>15.14925741583195</v>
+        <v>15.22602177244836</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>12.23</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2.919257415831947</v>
+        <v>2.996021772448355</v>
       </c>
     </row>
     <row r="61">
@@ -2460,14 +2601,17 @@
       <c r="H61" s="2" t="n">
         <v>32.46817526492672</v>
       </c>
+      <c r="K61" s="2" t="n">
+        <v>22.48518537839838</v>
+      </c>
       <c r="L61" s="2" t="n">
-        <v>15.51643697067477</v>
+        <v>15.60062111967642</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>3.636436970674767</v>
+        <v>3.720621119676418</v>
       </c>
     </row>
     <row r="62">
@@ -2494,14 +2638,17 @@
       <c r="H62" s="2" t="n">
         <v>29.1681710269803</v>
       </c>
+      <c r="K62" s="2" t="n">
+        <v>26.50282759371213</v>
+      </c>
       <c r="L62" s="2" t="n">
-        <v>16.51230400785013</v>
+        <v>16.6329919243811</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>11.74</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>4.77230400785013</v>
+        <v>4.892991924381098</v>
       </c>
     </row>
     <row r="63">
@@ -2528,14 +2675,17 @@
       <c r="H63" s="2" t="n">
         <v>30.60011965797399</v>
       </c>
+      <c r="K63" s="2" t="n">
+        <v>26.55484491970567</v>
+      </c>
       <c r="L63" s="2" t="n">
-        <v>15.78722627095969</v>
+        <v>15.91730168187771</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>11.71</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>4.077226270959688</v>
+        <v>4.207301681877707</v>
       </c>
     </row>
     <row r="64">
@@ -2562,14 +2712,17 @@
       <c r="H64" s="2" t="n">
         <v>31.26751594277168</v>
       </c>
+      <c r="K64" s="2" t="n">
+        <v>26.5515878554447</v>
+      </c>
       <c r="L64" s="2" t="n">
-        <v>15.28193413560802</v>
+        <v>15.41807425036611</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>12.3</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>2.98193413560802</v>
+        <v>3.118074250366107</v>
       </c>
     </row>
     <row r="65">
@@ -2596,14 +2749,17 @@
       <c r="H65" s="2" t="n">
         <v>30.67869903650935</v>
       </c>
+      <c r="K65" s="2" t="n">
+        <v>25.30392703511871</v>
+      </c>
       <c r="L65" s="2" t="n">
-        <v>14.94462416812489</v>
+        <v>15.06976702665336</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>13.36</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>1.584624168124893</v>
+        <v>1.709767026653356</v>
       </c>
     </row>
     <row r="66">
@@ -2630,14 +2786,17 @@
       <c r="H66" s="2" t="n">
         <v>33.83309019395038</v>
       </c>
+      <c r="K66" s="2" t="n">
+        <v>26.66277814822523</v>
+      </c>
       <c r="L66" s="2" t="n">
-        <v>15.80186256318361</v>
+        <v>15.93306502342627</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>13.61</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.191862563183607</v>
+        <v>2.323065023426267</v>
       </c>
     </row>
     <row r="67">
@@ -2664,14 +2823,17 @@
       <c r="H67" s="2" t="n">
         <v>31.63249894434386</v>
       </c>
+      <c r="K67" s="2" t="n">
+        <v>27.57644532298606</v>
+      </c>
       <c r="L67" s="2" t="n">
-        <v>15.12937797764112</v>
+        <v>15.27974153085431</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>14.96</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0.1693779776411191</v>
+        <v>0.319741530854305</v>
       </c>
     </row>
     <row r="68">
@@ -2698,14 +2860,17 @@
       <c r="H68" s="2" t="n">
         <v>31.88374803839209</v>
       </c>
+      <c r="K68" s="2" t="n">
+        <v>28.04808185869923</v>
+      </c>
       <c r="L68" s="2" t="n">
-        <v>16.65566348243142</v>
+        <v>16.7932866236276</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>15.14</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1.515663482431417</v>
+        <v>1.653286623627601</v>
       </c>
     </row>
     <row r="69">
@@ -2732,14 +2897,17 @@
       <c r="H69" s="2" t="n">
         <v>35.116585278335</v>
       </c>
+      <c r="K69" s="2" t="n">
+        <v>29.29297642563473</v>
+      </c>
       <c r="L69" s="2" t="n">
-        <v>19.1871835963558</v>
+        <v>19.30926399294134</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>15.42</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>3.767183596355801</v>
+        <v>3.889263992941343</v>
       </c>
     </row>
     <row r="70">
@@ -2766,14 +2934,17 @@
       <c r="H70" s="2" t="n">
         <v>36.08295205281462</v>
       </c>
+      <c r="K70" s="2" t="n">
+        <v>28.34927917567321</v>
+      </c>
       <c r="L70" s="2" t="n">
-        <v>18.1047016360371</v>
+        <v>18.22845858514718</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>15.88</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>2.224701636037098</v>
+        <v>2.348458585147183</v>
       </c>
     </row>
     <row r="71">
@@ -2800,14 +2971,17 @@
       <c r="H71" s="2" t="n">
         <v>42.6905677244131</v>
       </c>
+      <c r="K71" s="2" t="n">
+        <v>28.63048482812335</v>
+      </c>
       <c r="L71" s="2" t="n">
-        <v>20.38565574963054</v>
+        <v>20.48525525861376</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>15.87</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.515655749630538</v>
+        <v>4.615255258613763</v>
       </c>
     </row>
     <row r="72">
@@ -2834,14 +3008,17 @@
       <c r="H72" s="2" t="n">
         <v>47.49133104482092</v>
       </c>
+      <c r="K72" s="2" t="n">
+        <v>29.80604262991073</v>
+      </c>
       <c r="L72" s="2" t="n">
-        <v>20.44622786120727</v>
+        <v>20.55929666424271</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>16.84</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>3.606227861207273</v>
+        <v>3.719296664242705</v>
       </c>
     </row>
     <row r="73">
@@ -2868,14 +3045,17 @@
       <c r="H73" s="2" t="n">
         <v>41.24262785974076</v>
       </c>
+      <c r="K73" s="2" t="n">
+        <v>30.54140222281815</v>
+      </c>
       <c r="L73" s="2" t="n">
-        <v>17.32042914233289</v>
+        <v>17.4801416620905</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>16.17</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>1.150429142332893</v>
+        <v>1.310141662090498</v>
       </c>
     </row>
     <row r="74">
@@ -2902,14 +3082,17 @@
       <c r="H74" s="2" t="n">
         <v>49.35868177913012</v>
       </c>
+      <c r="K74" s="2" t="n">
+        <v>35.24303451590416</v>
+      </c>
       <c r="L74" s="2" t="n">
-        <v>17.74287578259274</v>
+        <v>17.95428188942317</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>2.362875782592743</v>
+        <v>2.574281889423167</v>
       </c>
     </row>
     <row r="75">
@@ -2936,14 +3119,17 @@
       <c r="H75" s="2" t="n">
         <v>45.15485075737434</v>
       </c>
+      <c r="K75" s="2" t="n">
+        <v>34.51978940138475</v>
+      </c>
       <c r="L75" s="2" t="n">
-        <v>16.18594258684464</v>
+        <v>16.40741984527142</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>16.6</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>-0.4140574131553585</v>
+        <v>-0.1925801547285779</v>
       </c>
     </row>
     <row r="76">
@@ -2970,14 +3156,17 @@
       <c r="H76" s="2" t="n">
         <v>50.52098358286025</v>
       </c>
+      <c r="K76" s="2" t="n">
+        <v>35.6673008684896</v>
+      </c>
       <c r="L76" s="2" t="n">
-        <v>16.19543779931677</v>
+        <v>16.43066256652721</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>15.55</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.6454377993167668</v>
+        <v>0.8806625665272101</v>
       </c>
     </row>
     <row r="77">
@@ -3004,14 +3193,17 @@
       <c r="H77" s="2" t="n">
         <v>42.20896854690343</v>
       </c>
+      <c r="K77" s="2" t="n">
+        <v>36.96171949938461</v>
+      </c>
       <c r="L77" s="2" t="n">
-        <v>16.47747522551059</v>
+        <v>16.72492980002597</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>15.22</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>1.257475225510591</v>
+        <v>1.504929800025968</v>
       </c>
     </row>
     <row r="78">
@@ -3038,14 +3230,17 @@
       <c r="H78" s="2" t="n">
         <v>45.62913925873848</v>
       </c>
+      <c r="K78" s="2" t="n">
+        <v>41.54841970221202</v>
+      </c>
       <c r="L78" s="2" t="n">
-        <v>16.7335064915842</v>
+        <v>17.03327658356674</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>15.79</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0.9435064915842055</v>
+        <v>1.243276583566743</v>
       </c>
     </row>
     <row r="79">
@@ -3072,14 +3267,17 @@
       <c r="H79" s="2" t="n">
         <v>40.33681205418513</v>
       </c>
+      <c r="K79" s="2" t="n">
+        <v>44.93637954685209</v>
+      </c>
       <c r="L79" s="2" t="n">
-        <v>16.35630462906671</v>
+        <v>16.7015587758071</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>15.41</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0.9463046290667059</v>
+        <v>1.291558775807101</v>
       </c>
     </row>
     <row r="80">
@@ -3106,14 +3304,17 @@
       <c r="H80" s="2" t="n">
         <v>55.09291727395582</v>
       </c>
+      <c r="K80" s="2" t="n">
+        <v>47.65275354887611</v>
+      </c>
       <c r="L80" s="2" t="n">
-        <v>17.06784698708819</v>
+        <v>17.43731998002124</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>14.7</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.367846987088189</v>
+        <v>2.737319980021237</v>
       </c>
     </row>
     <row r="81">
@@ -3140,14 +3341,17 @@
       <c r="H81" s="2" t="n">
         <v>55.41821966877728</v>
       </c>
+      <c r="K81" s="2" t="n">
+        <v>45.50830322155186</v>
+      </c>
       <c r="L81" s="2" t="n">
-        <v>17.20290583707662</v>
+        <v>17.54484181346006</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>3.102905837076625</v>
+        <v>3.44484181346006</v>
       </c>
     </row>
     <row r="82">
@@ -3174,14 +3378,17 @@
       <c r="H82" s="2" t="n">
         <v>61.10151420347143</v>
       </c>
+      <c r="K82" s="2" t="n">
+        <v>47.58404139526668</v>
+      </c>
       <c r="L82" s="2" t="n">
-        <v>18.57226003985735</v>
+        <v>18.92272930370968</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>13.85</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>4.722260039857348</v>
+        <v>5.072729303709684</v>
       </c>
     </row>
     <row r="83">
@@ -3205,14 +3412,17 @@
       <c r="H83" s="2" t="n">
         <v>61.22727445028835</v>
       </c>
+      <c r="K83" s="2" t="n">
+        <v>52.57093928843503</v>
+      </c>
       <c r="L83" s="2" t="n">
-        <v>19.09243309684751</v>
+        <v>19.50682750689555</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>14.95</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>4.142433096847512</v>
+        <v>4.556827506895551</v>
       </c>
     </row>
     <row r="84">
@@ -3239,14 +3449,17 @@
       <c r="H84" s="2" t="n">
         <v>56.90241575040731</v>
       </c>
+      <c r="K84" s="2" t="n">
+        <v>49.44299531037667</v>
+      </c>
       <c r="L84" s="2" t="n">
-        <v>18.37650377435888</v>
+        <v>18.7517944290664</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>14.58</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>3.796503774358877</v>
+        <v>4.171794429066397</v>
       </c>
     </row>
     <row r="85">
@@ -3273,14 +3486,17 @@
       <c r="H85" s="2" t="n">
         <v>57.39879517332002</v>
       </c>
+      <c r="K85" s="2" t="n">
+        <v>46.1441331030769</v>
+      </c>
       <c r="L85" s="2" t="n">
-        <v>18.2327390424991</v>
+        <v>18.5699153644101</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3.882739042499102</v>
+        <v>4.219915364410104</v>
       </c>
     </row>
     <row r="86">
@@ -3307,14 +3523,17 @@
       <c r="H86" s="2" t="n">
         <v>48.29687542764808</v>
       </c>
+      <c r="K86" s="2" t="n">
+        <v>35.86163295782171</v>
+      </c>
       <c r="L86" s="2" t="n">
-        <v>18.87984161637031</v>
+        <v>19.08498572101602</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>4.529841616370311</v>
+        <v>4.734985721016022</v>
       </c>
     </row>
     <row r="87">
@@ -3341,14 +3560,17 @@
       <c r="H87" s="2" t="n">
         <v>43.04353108288635</v>
       </c>
+      <c r="K87" s="2" t="n">
+        <v>39.0379807515464</v>
+      </c>
       <c r="L87" s="2" t="n">
-        <v>18.26150048428976</v>
+        <v>18.51248533956306</v>
       </c>
       <c r="M87" s="2" t="n">
         <v>14.63</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>3.631500484289761</v>
+        <v>3.882485339563056</v>
       </c>
     </row>
     <row r="88">
@@ -3375,14 +3597,17 @@
       <c r="H88" s="2" t="n">
         <v>43.48374617211803</v>
       </c>
+      <c r="K88" s="2" t="n">
+        <v>39.49667549639458</v>
+      </c>
       <c r="L88" s="2" t="n">
-        <v>18.82911092309233</v>
+        <v>19.07878005070953</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>14.31</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>4.519110923092329</v>
+        <v>4.768780050709525</v>
       </c>
     </row>
     <row r="89">
@@ -3409,14 +3634,17 @@
       <c r="H89" s="2" t="n">
         <v>40.98093033274804</v>
       </c>
+      <c r="K89" s="2" t="n">
+        <v>40.25343760074831</v>
+      </c>
       <c r="L89" s="2" t="n">
-        <v>18.90113536680946</v>
+        <v>19.15907628928528</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>14.47</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>4.431135366809459</v>
+        <v>4.689076289285284</v>
       </c>
     </row>
     <row r="90">

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3783,40 +3783,40 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>32.38194255799483</v>
+        <v>32.28049990956968</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>13.18845970468064</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>27.6370884024635</v>
+        <v>27.58605243030319</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>27.74386139790303</v>
+        <v>27.7542377836526</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>4.595119269985524</v>
+        <v>4.642350966456367</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>7.37009864945477</v>
+        <v>7.246431295543299</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>65.45303327569097</v>
+        <v>65.35516689818547</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.5391676440424</v>
+        <v>27.92280189381948</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>49.61732955933127</v>
+        <v>49.72855423890834</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>25.86030780760359</v>
+        <v>25.80169957645877</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>10.86030780760359</v>
+        <v>10.80169957645877</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3523,17 +3523,20 @@
       <c r="H86" s="2" t="n">
         <v>48.29687542764808</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>19.48332331204153</v>
+      </c>
       <c r="K86" s="2" t="n">
         <v>35.86163295782171</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>19.08498572101602</v>
+        <v>19.08974029804425</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>14.35</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>4.734985721016022</v>
+        <v>4.739740298044248</v>
       </c>
     </row>
     <row r="87">
@@ -3560,17 +3563,20 @@
       <c r="H87" s="2" t="n">
         <v>43.04353108288635</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.22831507914202</v>
+      </c>
       <c r="K87" s="2" t="n">
         <v>39.0379807515464</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>18.51248533956306</v>
+        <v>18.53296556751029</v>
       </c>
       <c r="M87" s="2" t="n">
         <v>14.63</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>3.882485339563056</v>
+        <v>3.902965567510288</v>
       </c>
     </row>
     <row r="88">
@@ -3597,17 +3603,20 @@
       <c r="H88" s="2" t="n">
         <v>43.48374617211803</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>23.95765368217945</v>
+      </c>
       <c r="K88" s="2" t="n">
         <v>39.49667549639458</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>19.07878005070953</v>
+        <v>19.13701452572379</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>14.31</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>4.768780050709525</v>
+        <v>4.827014525723785</v>
       </c>
     </row>
     <row r="89">
@@ -3634,17 +3643,20 @@
       <c r="H89" s="2" t="n">
         <v>40.98093033274804</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>24.1448406856991</v>
+      </c>
       <c r="K89" s="2" t="n">
         <v>40.25343760074831</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>19.15907628928528</v>
+        <v>19.21858661771379</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>14.47</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>4.689076289285284</v>
+        <v>4.748586617713785</v>
       </c>
     </row>
     <row r="90">
@@ -3677,17 +3689,20 @@
       <c r="I90" s="2" t="n">
         <v>26.49871237873908</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>25.35175097720487</v>
+      </c>
       <c r="K90" s="2" t="n">
         <v>39.32133308968581</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>20.61738415199558</v>
+        <v>20.66897843153444</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>14.58</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>6.03738415199558</v>
+        <v>6.088978431534445</v>
       </c>
     </row>
     <row r="91">
@@ -3720,17 +3735,20 @@
       <c r="I91" s="2" t="n">
         <v>26.07204872780737</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>26.7189328618572</v>
+      </c>
       <c r="K91" s="2" t="n">
         <v>48.03084582172159</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>21.97087092581626</v>
+        <v>22.02261445221383</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>14.93</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>7.040870925816265</v>
+        <v>7.092614452213834</v>
       </c>
     </row>
     <row r="92">
@@ -3763,17 +3781,20 @@
       <c r="I92" s="2" t="n">
         <v>27.80178291578326</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>41.1463255362535</v>
+      </c>
       <c r="K92" s="2" t="n">
         <v>48.50649109102406</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>23.42362670536719</v>
+        <v>23.61676549486596</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>16.45</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>6.973626705367192</v>
+        <v>7.166765494865956</v>
       </c>
     </row>
     <row r="93">
@@ -3783,40 +3804,53 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>32.28049990956968</v>
+        <v>31.3782608147617</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>13.18845970468064</v>
+        <v>12.77984487295003</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>27.58605243030319</v>
+        <v>26.92877835405801</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>27.7542377836526</v>
+        <v>27.14260909803992</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>4.642350966456367</v>
+        <v>4.441480011177005</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>7.246431295543299</v>
+        <v>7.099807330031199</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>65.35516689818547</v>
+        <v>63.20669375519103</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>27.92280189381948</v>
+        <v>26.10060965755615</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>50.69378677871431</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>49.72855423890834</v>
+        <v>47.98595727012115</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>25.80169957645877</v>
+        <v>25.35939690155034</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>10.80169957645877</v>
+        <v>10.35939690155034</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/erp_valuation/erp_portfolio.xlsx
+++ b/erp_valuation/erp_portfolio.xlsx
@@ -3819,7 +3819,7 @@
         <v>4.441480011177005</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>7.099807330031199</v>
+        <v>7.39811856238545</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>63.20669375519103</v>
@@ -3834,13 +3834,13 @@
         <v>47.98595727012115</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>25.35939690155034</v>
+        <v>25.36264784379456</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>10.35939690155034</v>
+        <v>10.36264784379456</v>
       </c>
     </row>
     <row r="94">
@@ -3849,8 +3849,44 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="B94" s="2" t="n">
+        <v>30.83829715602115</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>11.90371291182457</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>25.9799079787846</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>27.42093054006139</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>3.734695430199554</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>7.268286694463483</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>61.97589888671864</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>25.59983050065752</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>52.69286460826729</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>46.41956067373302</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>24.745264159472</v>
+      </c>
       <c r="M94" s="2" t="n">
         <v>15</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>9.745264159472004</v>
       </c>
     </row>
   </sheetData>
